--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-06-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-06-week02/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Sienna Spiro - The Visitor (Live at Capital's Summertime Ball 2026)</v>
+        <v>Jason Derulo - The Other Side (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B2" t="str">
-        <v>14 hours ago</v>
+        <v>8h ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=MibVDrnrQ10</v>
+        <v>https://www.youtube.com/watch?v=ym-h0EIlL3A</v>
       </c>
       <c r="D2" t="str">
         <v>2026-06-08</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>14 hours ago</v>
+        <v>8h ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Sienna Spiro - The Visitor (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Jason Derulo - The Other Side (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Sienna Spiro - Die On This Hill (Live at Capital's Summertime Ball 2026)</v>
+        <v>Stephen Sanchez - Be More (Live at Capital's Summertime Ball 2026) | Capital</v>
       </c>
       <c r="B3" t="str">
-        <v>14 hours ago</v>
+        <v>8h ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=UhWumamExiI</v>
+        <v>https://www.youtube.com/watch?v=bIwcNmu-rAg</v>
       </c>
       <c r="D3" t="str">
         <v>2026-06-08</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>14 hours ago</v>
+        <v>8h ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Sienna Spiro - Die On This Hill (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Stephen Sanchez - Be More (Live at Capital's Summertime Ball 2026) | Capital - Capital FM</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>RAYE - Where Is My Husband? (Live at Capital's Summertime Ball 2026)</v>
+        <v>Jason Derulo - Take You Dancing (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B4" t="str">
-        <v>16 hours ago</v>
+        <v>8h ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=Z_HR2ZYY1VA</v>
+        <v>https://www.youtube.com/watch?v=oLzj8E8fHRQ</v>
       </c>
       <c r="D4" t="str">
         <v>2026-06-08</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>16 hours ago</v>
+        <v>8h ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>RAYE - Where Is My Husband? (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Jason Derulo - Take You Dancing (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>RAYE - Escapism (Live at Capital's Summertime Ball 2026)</v>
+        <v>Sekou - Someone Like You (Adele Cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B5" t="str">
-        <v>16 hours ago</v>
+        <v>8h ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=ywplqaIeHeQ</v>
+        <v>https://www.youtube.com/watch?v=YIy2g4enMiY</v>
       </c>
       <c r="D5" t="str">
         <v>2026-06-08</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>16 hours ago</v>
+        <v>8h ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>RAYE - Escapism (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Sekou - Someone Like You (Adele Cover) (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Take That - Never Forget (Live at Capital's Summertime Ball 2026)</v>
+        <v>Sienna Spiro - He's Not My Baby, I'm His (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B6" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=9S61JkOZLe8</v>
+        <v>https://www.youtube.com/watch?v=NhuPT6MR2XU</v>
       </c>
       <c r="D6" t="str">
         <v>2026-06-08</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Take That - Never Forget (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Sienna Spiro - He's Not My Baby, I'm His (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Robyn - Dancing On My Own (Live at Capital's Summertime Ball 2026)</v>
+        <v>DEEP PURPLE - DIABLO (Official Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=_4SfgNPngbo</v>
+        <v>https://www.youtube.com/watch?v=Z4RpBEg5uis</v>
       </c>
       <c r="D7" t="str">
         <v>2026-06-08</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>Capital FM</v>
+        <v>earMUSIC and Deep Purple Official</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Robyn - Dancing On My Own (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>DEEP PURPLE - DIABLO (Official Video) - earMUSIC and Deep Purple Official</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Take That - Patience (Live at Capital's Summertime Ball 2026)</v>
+        <v>Reba McEntire - You Never Gave Up On Me</v>
       </c>
       <c r="B8" t="str">
-        <v>1 day ago</v>
+        <v>19h ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=_I9qIxmrDuI</v>
+        <v>https://www.youtube.com/watch?v=AUCRUStLmJM</v>
       </c>
       <c r="D8" t="str">
         <v>2026-06-08</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>1 day ago</v>
+        <v>19h ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>Capital FM</v>
+        <v>Reba McEntire</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Take That - Patience (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Reba McEntire - You Never Gave Up On Me - Reba McEntire</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Mis-Teeq - Full Set (Live at Capital's Summertime Ball 2026)</v>
+        <v>elijah woods - Wonder (Official Lyric Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>1 day ago</v>
+        <v>22h ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=5AyQM_coDb8</v>
+        <v>https://www.youtube.com/watch?v=sDDbD4R-xD4</v>
       </c>
       <c r="D9" t="str">
         <v>2026-06-08</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>1 day ago</v>
+        <v>22h ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>Capital FM</v>
+        <v>elijah woods</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Mis-Teeq - Full Set (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>elijah woods - Wonder (Official Lyric Video) - elijah woods</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Myles Smith - Stay (Live at Capital's Summertime Ball 2026)</v>
+        <v>XG - Flowers (Sweet Female Attitude Cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B10" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=2ekY7Cb7CKs</v>
+        <v>https://www.youtube.com/watch?v=MxJQoyKh8TQ</v>
       </c>
       <c r="D10" t="str">
         <v>2026-06-08</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>Capital FM</v>
+        <v>Capital FM and XG</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Myles Smith - Stay (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>XG - Flowers (Sweet Female Attitude Cover) (Live at Capital's Summertime Ball 2026) - Capital FM and XG</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Take That - Rule The World (Live at Capital's Summertime Ball 2026)</v>
+        <v>Niall Horan - Nice To Meet Ya (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B11" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=0nc-qdhh6eU</v>
+        <v>https://www.youtube.com/watch?v=-UIkkGxMQG8</v>
       </c>
       <c r="D11" t="str">
         <v>2026-06-08</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Take That - Rule The World (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Niall Horan - Nice To Meet Ya (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Sienna Spiro - Material Lover (Live at Capital's Summertime Ball 2026)</v>
+        <v>Niall Horan - Steal My Girl (One Direction cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B12" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=dZjAtTc9DBQ</v>
+        <v>https://www.youtube.com/watch?v=b_uO5ROpk_0</v>
       </c>
       <c r="D12" t="str">
         <v>2026-06-08</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Sienna Spiro - Material Lover (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Niall Horan - Steal My Girl (One Direction cover) (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Take That - Shine (Live at Capital's Summertime Ball 2026)</v>
+        <v>Niall Horan - Dinner Party (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B13" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=T6TmxqOGIf0</v>
+        <v>https://www.youtube.com/watch?v=hSJfAFpdllk</v>
       </c>
       <c r="D13" t="str">
         <v>2026-06-08</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Take That - Shine (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Niall Horan - Dinner Party (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>MEEK - Dracula (Tame Impala Cover) (Live at Capital's Summertime Ball 2026)</v>
+        <v>Niall Horan - Slow Hands (Live at Capital's Summertime Ball 2026) | Capital</v>
       </c>
       <c r="B14" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=4jnM--XhsC0</v>
+        <v>https://www.youtube.com/watch?v=vdMK2DvnWJI</v>
       </c>
       <c r="D14" t="str">
         <v>2026-06-08</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>MEEK - Dracula (Tame Impala Cover) (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Niall Horan - Slow Hands (Live at Capital's Summertime Ball 2026) | Capital - Capital FM</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>MEEK - Fabulous (Live at Capital's Summertime Ball 2026)</v>
+        <v>RAYE - Joy (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B15" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=kKSlraqNMhI</v>
+        <v>https://www.youtube.com/watch?v=5gvhRAGaOUo</v>
       </c>
       <c r="D15" t="str">
         <v>2026-06-08</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>MEEK - Fabulous (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>RAYE - Joy (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Lola Young - Messy (Live at Capital's Summertime Ball 2026)</v>
+        <v>Myles Smith - Stargazing (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B16" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=cUvsaKkjHYQ</v>
+        <v>https://www.youtube.com/watch?v=2AIMnAPxqfw</v>
       </c>
       <c r="D16" t="str">
         <v>2026-06-08</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>Capital FM and Lola Young</v>
+        <v>Capital FM</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Lola Young - Messy (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
+        <v>Myles Smith - Stargazing (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Stephen Sanchez - Until I Found You (Live at Capital's Summertime Ball 2026)</v>
+        <v>Lola Young - From Down Here (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B17" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=oKKNK0OCpQk</v>
+        <v>https://www.youtube.com/watch?v=UD7HkkAbnVA</v>
       </c>
       <c r="D17" t="str">
         <v>2026-06-08</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>Capital FM</v>
+        <v>Capital FM and Lola Young</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Stephen Sanchez - Until I Found You (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Lola Young - From Down Here (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Lola Young - D£aler (Live at Capital's Summertime Ball 2026)</v>
+        <v>XG - Hypnotize (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B18" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=ymvr4RCN-WE</v>
+        <v>https://www.youtube.com/watch?v=c5u3ur4vLo0</v>
       </c>
       <c r="D18" t="str">
         <v>2026-06-08</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>Capital FM and Lola Young</v>
+        <v>Capital FM and XG</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Lola Young - D£aler (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
+        <v>XG - Hypnotize (Live at Capital's Summertime Ball 2026) - Capital FM and XG</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Lola Young - One Thing (Live at Capital's Summertime Ball 2026)</v>
+        <v>Sienna Spiro - The Visitor (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B19" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=nhL2l4HCiRg</v>
+        <v>https://www.youtube.com/watch?v=MibVDrnrQ10</v>
       </c>
       <c r="D19" t="str">
         <v>2026-06-08</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>Capital FM and Lola Young</v>
+        <v>Capital FM</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Lola Young - One Thing (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
+        <v>Sienna Spiro - The Visitor (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Bebe Rexha - Sad Girls (Live at Capital's Summertime Ball 2026)</v>
+        <v>Sienna Spiro - Die On This Hill (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B20" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=e0PkSQNMcGs</v>
+        <v>https://www.youtube.com/watch?v=UhWumamExiI</v>
       </c>
       <c r="D20" t="str">
         <v>2026-06-08</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Bebe Rexha - Sad Girls (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Sienna Spiro - Die On This Hill (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Robyn - Dopamine (Live at Capital's Summertime Ball 2026)</v>
+        <v>RAYE - Where Is My Husband? (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B21" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=-7mPIus0U5Y</v>
+        <v>https://www.youtube.com/watch?v=Z_HR2ZYY1VA</v>
       </c>
       <c r="D21" t="str">
         <v>2026-06-08</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Robyn - Dopamine (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>RAYE - Where Is My Husband? (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Jason Derulo - Ridin' Solo (Live at Capital's Summertime Ball 2026)</v>
+        <v>RAYE - Escapism (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B22" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=G6jhovaAz3U</v>
+        <v>https://www.youtube.com/watch?v=ywplqaIeHeQ</v>
       </c>
       <c r="D22" t="str">
         <v>2026-06-08</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Jason Derulo - Ridin' Solo (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>RAYE - Escapism (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Jason Derulo - Trumpets (Live at Capital's Summertime Ball 2026)</v>
+        <v>Take That - Never Forget (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B23" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=QkCKENp-4Rs</v>
+        <v>https://www.youtube.com/watch?v=9S61JkOZLe8</v>
       </c>
       <c r="D23" t="str">
         <v>2026-06-08</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Jason Derulo - Trumpets (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Take That - Never Forget (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Jason Derulo - Whatcha Say (Live at Capital's Summertime Ball 2026)</v>
+        <v>Robyn - Dancing On My Own (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B24" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=jsFekVlEaSA</v>
+        <v>https://www.youtube.com/watch?v=_4SfgNPngbo</v>
       </c>
       <c r="D24" t="str">
         <v>2026-06-08</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Jason Derulo - Whatcha Say (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Robyn - Dancing On My Own (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Bebe Rexha - New Religion (Live at Capital's Summertime Ball 2026)</v>
+        <v>Take That - Patience (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B25" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=nfDKQ09bY_w</v>
+        <v>https://www.youtube.com/watch?v=_I9qIxmrDuI</v>
       </c>
       <c r="D25" t="str">
         <v>2026-06-08</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Bebe Rexha - New Religion (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Take That - Patience (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Bebe Rexha - I'm Good (Live at Capital's Summertime Ball 2026)</v>
+        <v>Mis-Teeq - Full Set (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B26" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=eqceDkaK3PU</v>
+        <v>https://www.youtube.com/watch?v=5AyQM_coDb8</v>
       </c>
       <c r="D26" t="str">
         <v>2026-06-08</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Bebe Rexha - I'm Good (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Mis-Teeq - Full Set (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Bebe Rexha - In The Name Of Love (Live at Capital's Summertime Ball 2026)</v>
+        <v>Myles Smith - Stay (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B27" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=UlP9zTLUeLw</v>
+        <v>https://www.youtube.com/watch?v=2ekY7Cb7CKs</v>
       </c>
       <c r="D27" t="str">
         <v>2026-06-08</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Bebe Rexha - In The Name Of Love (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Myles Smith - Stay (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>The Cranberries - Scenes From 'Linger' (The Only Color Reel)</v>
+        <v>Take That - Rule The World (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B28" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=5-peG8H-lqE</v>
+        <v>https://www.youtube.com/watch?v=0nc-qdhh6eU</v>
       </c>
       <c r="D28" t="str">
         <v>2026-06-08</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>TheCranberriesTV</v>
+        <v>Capital FM</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>The Cranberries - Scenes From 'Linger' (The Only Color Reel) - TheCranberriesTV</v>
+        <v>Take That - Rule The World (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Jordana Bryant - Too Little Too Late (Official Lyric Video)</v>
+        <v>Sienna Spiro - Material Lover (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B29" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=P26-NjdBmbU</v>
+        <v>https://www.youtube.com/watch?v=dZjAtTc9DBQ</v>
       </c>
       <c r="D29" t="str">
         <v>2026-06-08</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>Jordana Bryant</v>
+        <v>Capital FM</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Jordana Bryant - Too Little Too Late (Official Lyric Video) - Jordana Bryant</v>
+        <v>Sienna Spiro - Material Lover (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Grace Enger - "Running Back To You" (Official Music Video)</v>
+        <v>Take That - Shine (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B30" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=BON1BSWLntE</v>
+        <v>https://www.youtube.com/watch?v=T6TmxqOGIf0</v>
       </c>
       <c r="D30" t="str">
         <v>2026-06-08</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>Grace Enger</v>
+        <v>Capital FM</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Grace Enger - "Running Back To You" (Official Music Video) - Grace Enger</v>
+        <v>Take That - Shine (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>The Offspring - Gone Away | Live at BeachLife Festival 2026</v>
+        <v>MEEK - Dracula (Tame Impala Cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B31" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=UTw106Ivz8o</v>
+        <v>https://www.youtube.com/watch?v=4jnM--XhsC0</v>
       </c>
       <c r="D31" t="str">
         <v>2026-06-08</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>The Offspring</v>
+        <v>Capital FM</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>The Offspring - Gone Away | Live at BeachLife Festival 2026 - The Offspring</v>
+        <v>MEEK - Dracula (Tame Impala Cover) (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Lola Young – From Down Here (From The Pool)</v>
+        <v>MEEK - Fabulous (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B32" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=YFhpMpONGUY</v>
+        <v>https://www.youtube.com/watch?v=kKSlraqNMhI</v>
       </c>
       <c r="D32" t="str">
         <v>2026-06-08</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>Lola Young</v>
+        <v>Capital FM</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Lola Young – From Down Here (From The Pool) - Lola Young</v>
+        <v>MEEK - Fabulous (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>CAIN - Living Water (Music Video)</v>
+        <v>Lola Young - Messy (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B33" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=WrsXAfnTAdA</v>
+        <v>https://www.youtube.com/watch?v=cUvsaKkjHYQ</v>
       </c>
       <c r="D33" t="str">
         <v>2026-06-08</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>CAIN</v>
+        <v>Capital FM and Lola Young</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>CAIN - Living Water (Music Video) - CAIN</v>
+        <v>Lola Young - Messy (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>B.B. King &amp; Eric Clapton - Riding With The King (Official Music Video)</v>
+        <v>Stephen Sanchez - Until I Found You (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B34" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=L7Ls8ceHxhc</v>
+        <v>https://www.youtube.com/watch?v=oKKNK0OCpQk</v>
       </c>
       <c r="D34" t="str">
         <v>2026-06-08</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Eric Clapton</v>
+        <v>Capital FM</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>B.B. King &amp; Eric Clapton - Riding With The King (Official Music Video) - Eric Clapton</v>
+        <v>Stephen Sanchez - Until I Found You (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Blu DeTiger - Whisper (Official Music Video)</v>
+        <v>Lola Young - D£aler (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B35" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=OfcBfPnskG4</v>
+        <v>https://www.youtube.com/watch?v=ymvr4RCN-WE</v>
       </c>
       <c r="D35" t="str">
         <v>2026-06-08</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>Blu DeTiger</v>
+        <v>Capital FM and Lola Young</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Blu DeTiger - Whisper (Official Music Video) - Blu DeTiger</v>
+        <v>Lola Young - D£aler (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Romeo Santos, Prince Royce - Ay! San Miguel (Official Video)</v>
+        <v>Lola Young - One Thing (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B36" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=-uvNvVtUidc</v>
+        <v>https://www.youtube.com/watch?v=nhL2l4HCiRg</v>
       </c>
       <c r="D36" t="str">
         <v>2026-06-08</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>Romeo Santos and Prince Royce</v>
+        <v>Capital FM and Lola Young</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Romeo Santos, Prince Royce - Ay! San Miguel (Official Video) - Romeo Santos and Prince Royce</v>
+        <v>Lola Young - One Thing (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Strange Surreal AI - In Here - Kelly Boesch | 4K</v>
+        <v>Bebe Rexha - Sad Girls (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B37" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=QCNwFDTkfYU</v>
+        <v>https://www.youtube.com/watch?v=e0PkSQNMcGs</v>
       </c>
       <c r="D37" t="str">
         <v>2026-06-08</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>Kelly Boesch AI Art</v>
+        <v>Capital FM</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Strange Surreal AI - In Here - Kelly Boesch | 4K - Kelly Boesch AI Art</v>
+        <v>Bebe Rexha - Sad Girls (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Pink Floyd - Pigs on the Wing (8-Track Version - Official Audio)</v>
+        <v>Robyn - Dopamine (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B38" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=WZUKJ90i6Tw</v>
+        <v>https://www.youtube.com/watch?v=-7mPIus0U5Y</v>
       </c>
       <c r="D38" t="str">
         <v>2026-06-08</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>Pink Floyd</v>
+        <v>Capital FM</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Pink Floyd - Pigs on the Wing (8-Track Version - Official Audio) - Pink Floyd</v>
+        <v>Robyn - Dopamine (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Holly Humberstone - it’s just White Noise</v>
+        <v>Jason Derulo - Ridin' Solo (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B39" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=KeRZtPUjl8g</v>
+        <v>https://www.youtube.com/watch?v=G6jhovaAz3U</v>
       </c>
       <c r="D39" t="str">
         <v>2026-06-08</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>Holly Humberstone</v>
+        <v>Capital FM</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Holly Humberstone - it’s just White Noise - Holly Humberstone</v>
+        <v>Jason Derulo - Ridin' Solo (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Freya Ridings - Mother Of Pearl (Official Video)</v>
+        <v>Jason Derulo - Trumpets (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B40" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=So5gx12fCsA</v>
+        <v>https://www.youtube.com/watch?v=QkCKENp-4Rs</v>
       </c>
       <c r="D40" t="str">
         <v>2026-06-08</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>Freya Ridings</v>
+        <v>Capital FM</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Freya Ridings - Mother Of Pearl (Official Video) - Freya Ridings</v>
+        <v>Jason Derulo - Trumpets (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>MUSE - Nightshift Superstar (Official Music Video)</v>
+        <v>Jason Derulo - Whatcha Say (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B41" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=p--xk9n1eIM</v>
+        <v>https://www.youtube.com/watch?v=jsFekVlEaSA</v>
       </c>
       <c r="D41" t="str">
         <v>2026-06-08</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>Muse</v>
+        <v>Capital FM</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>MUSE - Nightshift Superstar (Official Music Video) - Muse</v>
+        <v>Jason Derulo - Whatcha Say (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Ellie Goulding - Black Prada Dress (Visualiser)</v>
+        <v>Bebe Rexha - New Religion (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B42" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=zr9CYpgPueI</v>
+        <v>https://www.youtube.com/watch?v=nfDKQ09bY_w</v>
       </c>
       <c r="D42" t="str">
         <v>2026-06-08</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>Ellie Goulding</v>
+        <v>Capital FM</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Ellie Goulding - Black Prada Dress (Visualiser) - Ellie Goulding</v>
+        <v>Bebe Rexha - New Religion (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>DEEP PURPLE - DIABLO (Official Video)</v>
+        <v>Bebe Rexha - I'm Good (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B43" t="str">
-        <v>6 hours ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=Z4RpBEg5uis</v>
+        <v>https://www.youtube.com/watch?v=eqceDkaK3PU</v>
       </c>
       <c r="D43" t="str">
         <v>2026-06-08</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>6 hours ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>earMUSIC and Deep Purple Official</v>
+        <v>Capital FM</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>DEEP PURPLE - DIABLO (Official Video) - earMUSIC and Deep Purple Official</v>
+        <v>Bebe Rexha - I'm Good (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Evanescence - Sanctuary (Official Visualizer)</v>
+        <v>Bebe Rexha - In The Name Of Love (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B44" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=E64jOWeVfpg</v>
+        <v>https://www.youtube.com/watch?v=UlP9zTLUeLw</v>
       </c>
       <c r="D44" t="str">
         <v>2026-06-08</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>Evanescence</v>
+        <v>Capital FM</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Evanescence - Sanctuary (Official Visualizer) - Evanescence</v>
+        <v>Bebe Rexha - In The Name Of Love (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>The Beaches - Perfect 10 (Official Visualizer)</v>
+        <v>Strange Surreal AI - In Here - Kelly Boesch | 4K</v>
       </c>
       <c r="B45" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=N7TOR_l-CM8</v>
+        <v>https://www.youtube.com/watch?v=QCNwFDTkfYU</v>
       </c>
       <c r="D45" t="str">
         <v>2026-06-08</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>The Beaches</v>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>The Beaches - Perfect 10 (Official Visualizer) - The Beaches</v>
+        <v>Strange Surreal AI - In Here - Kelly Boesch | 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Bella White - Stuff (Official Music Video)</v>
+        <v>The Cranberries - Scenes From 'Linger' (The Only Color Reel)</v>
       </c>
       <c r="B46" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=7QZtxsGBTks</v>
+        <v>https://www.youtube.com/watch?v=5-peG8H-lqE</v>
       </c>
       <c r="D46" t="str">
         <v>2026-06-08</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>Bella White</v>
+        <v>TheCranberriesTV</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Bella White - Stuff (Official Music Video) - Bella White</v>
+        <v>The Cranberries - Scenes From 'Linger' (The Only Color Reel) - TheCranberriesTV</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Meduza, Rani - Silence (Official Visualizer)</v>
+        <v>Jordana Bryant - Too Little Too Late (Official Lyric Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=cIdqz-WMod4</v>
+        <v>https://www.youtube.com/watch?v=P26-NjdBmbU</v>
       </c>
       <c r="D47" t="str">
         <v>2026-06-08</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>Meduza and 2 more</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Meduza, Rani - Silence (Official Visualizer) - Meduza and 2 more</v>
+        <v>Jordana Bryant - Too Little Too Late (Official Lyric Video) - Jordana Bryant</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>CAIN - Living Water (Lyric Video)</v>
+        <v>Grace Enger - "Running Back To You" (Official Music Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=Hv-8CM5NIPM</v>
+        <v>https://www.youtube.com/watch?v=BON1BSWLntE</v>
       </c>
       <c r="D48" t="str">
         <v>2026-06-08</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>CAIN</v>
+        <v>Grace Enger</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>CAIN - Living Water (Lyric Video) - CAIN</v>
+        <v>Grace Enger - "Running Back To You" (Official Music Video) - Grace Enger</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Fitz and the Tantrums - Greenlight (Official Visualizer)</v>
+        <v>The Offspring - Gone Away | Live at BeachLife Festival 2026</v>
       </c>
       <c r="B49" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=Zx-ZPBbcA58</v>
+        <v>https://www.youtube.com/watch?v=UTw106Ivz8o</v>
       </c>
       <c r="D49" t="str">
         <v>2026-06-08</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>Fitz and the Tantrums</v>
+        <v>The Offspring</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Fitz and the Tantrums - Greenlight (Official Visualizer) - Fitz and the Tantrums</v>
+        <v>The Offspring - Gone Away | Live at BeachLife Festival 2026 - The Offspring</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Jeremy Camp - Reflector (Official Music Video)</v>
+        <v>Lola Young – From Down Here (From The Pool)</v>
       </c>
       <c r="B50" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=SR-4q1yiYNA</v>
+        <v>https://www.youtube.com/watch?v=YFhpMpONGUY</v>
       </c>
       <c r="D50" t="str">
         <v>2026-06-08</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>Jeremy Camp</v>
+        <v>Lola Young</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Jeremy Camp - Reflector (Official Music Video) - Jeremy Camp</v>
+        <v>Lola Young – From Down Here (From The Pool) - Lola Young</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Alesso, OneRepublic - In Your Eyes (Visualizer)</v>
+        <v>CAIN - Living Water (Music Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=bS9C1ipyMy8</v>
+        <v>https://www.youtube.com/watch?v=WrsXAfnTAdA</v>
       </c>
       <c r="D51" t="str">
         <v>2026-06-08</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>Alesso</v>
+        <v>CAIN</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Alesso, OneRepublic - In Your Eyes (Visualizer) - Alesso</v>
+        <v>CAIN - Living Water (Music Video) - CAIN</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Malcolm Todd - Free.99 (Official Visualizer)</v>
+        <v>B.B. King &amp; Eric Clapton - Riding With The King (Official Music Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=wBBQptUsOhw</v>
+        <v>https://www.youtube.com/watch?v=L7Ls8ceHxhc</v>
       </c>
       <c r="D52" t="str">
         <v>2026-06-08</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>Malcolm Todd</v>
+        <v>Eric Clapton</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Malcolm Todd - Free.99 (Official Visualizer) - Malcolm Todd</v>
+        <v>B.B. King &amp; Eric Clapton - Riding With The King (Official Music Video) - Eric Clapton</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Isabel LaRosa - Every Life (Visualizer)</v>
+        <v>Blu DeTiger - Whisper (Official Music Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=tIQDAtwNAY4</v>
+        <v>https://www.youtube.com/watch?v=OfcBfPnskG4</v>
       </c>
       <c r="D53" t="str">
         <v>2026-06-08</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>Isabel LaRosa</v>
+        <v>Blu DeTiger</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Isabel LaRosa - Every Life (Visualizer) - Isabel LaRosa</v>
+        <v>Blu DeTiger - Whisper (Official Music Video) - Blu DeTiger</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Wyatt Flores - Half The Man (Official Music Video)</v>
+        <v>Romeo Santos, Prince Royce - Ay! San Miguel (Official Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=2ChzcWHryFM</v>
+        <v>https://www.youtube.com/watch?v=-uvNvVtUidc</v>
       </c>
       <c r="D54" t="str">
         <v>2026-06-08</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>Wyatt Flores</v>
+        <v>Romeo Santos and Prince Royce</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Wyatt Flores - Half The Man (Official Music Video) - Wyatt Flores</v>
+        <v>Romeo Santos, Prince Royce - Ay! San Miguel (Official Video) - Romeo Santos and Prince Royce</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Mckenna Grace - Ugly and Rotten (Official Music Video)</v>
+        <v>Pink Floyd - Pigs on the Wing (8-Track Version - Official Audio)</v>
       </c>
       <c r="B55" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=4yXFVgy7laM</v>
+        <v>https://www.youtube.com/watch?v=WZUKJ90i6Tw</v>
       </c>
       <c r="D55" t="str">
         <v>2026-06-08</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>Mckenna Grace</v>
+        <v>Pink Floyd</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Mckenna Grace - Ugly and Rotten (Official Music Video) - Mckenna Grace</v>
+        <v>Pink Floyd - Pigs on the Wing (8-Track Version - Official Audio) - Pink Floyd</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Robert Grace - If You Were Gone ft. Bob Grace (OFFICIAL LYRIC VIDEO)</v>
+        <v>Holly Humberstone - it’s just White Noise</v>
       </c>
       <c r="B56" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=fbpQjMi3Hco</v>
+        <v>https://www.youtube.com/watch?v=KeRZtPUjl8g</v>
       </c>
       <c r="D56" t="str">
         <v>2026-06-08</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>Robert Grace</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Robert Grace - If You Were Gone ft. Bob Grace (OFFICIAL LYRIC VIDEO) - Robert Grace</v>
+        <v>Holly Humberstone - it’s just White Noise - Holly Humberstone</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Boyzone - No Matter What (Live)</v>
+        <v>Freya Ridings - Mother Of Pearl (Official Video)</v>
       </c>
       <c r="B57" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=CEy96_jHw-Q</v>
+        <v>https://www.youtube.com/watch?v=So5gx12fCsA</v>
       </c>
       <c r="D57" t="str">
         <v>2026-06-08</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>Boyzone</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Boyzone - No Matter What (Live) - Boyzone</v>
+        <v>Freya Ridings - Mother Of Pearl (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Florrie - The Times (Official Video)</v>
+        <v>MUSE - Nightshift Superstar (Official Music Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=6yBlNUaW7r4</v>
+        <v>https://www.youtube.com/watch?v=p--xk9n1eIM</v>
       </c>
       <c r="D58" t="str">
         <v>2026-06-08</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>florriemusic</v>
+        <v>Muse</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Florrie - The Times (Official Video) - florriemusic</v>
+        <v>MUSE - Nightshift Superstar (Official Music Video) - Muse</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Madonna - Love Sensation (Official Visualizer)</v>
+        <v>Ellie Goulding - Black Prada Dress (Visualiser)</v>
       </c>
       <c r="B59" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=88fD-UtG_yo</v>
+        <v>https://www.youtube.com/watch?v=zr9CYpgPueI</v>
       </c>
       <c r="D59" t="str">
         <v>2026-06-08</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>Madonna</v>
+        <v>Ellie Goulding</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Madonna - Love Sensation (Official Visualizer) - Madonna</v>
+        <v>Ellie Goulding - Black Prada Dress (Visualiser) - Ellie Goulding</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>DMA'S - Hurracane (Official Video)</v>
+        <v>Evanescence - Sanctuary (Official Visualizer)</v>
       </c>
       <c r="B60" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=-zTB57LiXPk</v>
+        <v>https://www.youtube.com/watch?v=E64jOWeVfpg</v>
       </c>
       <c r="D60" t="str">
         <v>2026-06-08</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>DMA'S</v>
+        <v>Evanescence</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>DMA'S - Hurracane (Official Video) - DMA'S</v>
+        <v>Evanescence - Sanctuary (Official Visualizer) - Evanescence</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Lainey Wilson and John Mayer - Phone, Keys, Wallet (Official Audio)</v>
+        <v>The Beaches - Perfect 10 (Official Visualizer)</v>
       </c>
       <c r="B61" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=JzW6RnzeF9A</v>
+        <v>https://www.youtube.com/watch?v=N7TOR_l-CM8</v>
       </c>
       <c r="D61" t="str">
         <v>2026-06-08</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>Lainey Wilson and John Mayer</v>
+        <v>The Beaches</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Lainey Wilson and John Mayer - Phone, Keys, Wallet (Official Audio) - Lainey Wilson and John Mayer</v>
+        <v>The Beaches - Perfect 10 (Official Visualizer) - The Beaches</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>ROLE MODEL - High Hopes 3000 (Official Music Video)</v>
+        <v>Bella White - Stuff (Official Music Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>4 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=D_KTG0BzRiI</v>
+        <v>https://www.youtube.com/watch?v=7QZtxsGBTks</v>
       </c>
       <c r="D62" t="str">
         <v>2026-06-08</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>4 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>ROLE MODEL</v>
+        <v>Bella White</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>ROLE MODEL - High Hopes 3000 (Official Music Video) - ROLE MODEL</v>
+        <v>Bella White - Stuff (Official Music Video) - Bella White</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Shawn Mendes - Treat You Better (Live from New York)</v>
+        <v>Meduza, Rani - Silence (Official Visualizer)</v>
       </c>
       <c r="B63" t="str">
-        <v>4 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=29bfaHc1XiY</v>
+        <v>https://www.youtube.com/watch?v=cIdqz-WMod4</v>
       </c>
       <c r="D63" t="str">
         <v>2026-06-08</v>
@@ -2769,13 +2769,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>4 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>Shawn Mendes</v>
+        <v>Meduza and 2 more</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Shawn Mendes - Treat You Better (Live from New York) - Shawn Mendes</v>
+        <v>Meduza, Rani - Silence (Official Visualizer) - Meduza and 2 more</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>SIENNA SPIRO - The Visitor (Official Music Video)</v>
+        <v>CAIN - Living Water (Lyric Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>4 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=LiYb4WGbp5Y</v>
+        <v>https://www.youtube.com/watch?v=Hv-8CM5NIPM</v>
       </c>
       <c r="D64" t="str">
         <v>2026-06-08</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>4 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>CAIN</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>SIENNA SPIRO - The Visitor (Official Music Video) - SIENNA SPIRO</v>
+        <v>CAIN - Living Water (Lyric Video) - CAIN</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Just Slide Official Music Video | Kelly Boesch | 4K</v>
+        <v>Fitz and the Tantrums - Greenlight (Official Visualizer)</v>
       </c>
       <c r="B65" t="str">
-        <v>4 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=lC14fuU8aPc</v>
+        <v>https://www.youtube.com/watch?v=Zx-ZPBbcA58</v>
       </c>
       <c r="D65" t="str">
         <v>2026-06-08</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>4 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>Kelly Boesch AI Art</v>
+        <v>Fitz and the Tantrums</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Just Slide Official Music Video | Kelly Boesch | 4K - Kelly Boesch AI Art</v>
+        <v>Fitz and the Tantrums - Greenlight (Official Visualizer) - Fitz and the Tantrums</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Europe - The Cult of Ignorance (Official Video)</v>
+        <v>Jeremy Camp - Reflector (Official Music Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>4 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=p-IOsjOJpnA</v>
+        <v>https://www.youtube.com/watch?v=SR-4q1yiYNA</v>
       </c>
       <c r="D66" t="str">
         <v>2026-06-08</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>4 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>Europe</v>
+        <v>Jeremy Camp</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Europe - The Cult of Ignorance (Official Video) - Europe</v>
+        <v>Jeremy Camp - Reflector (Official Music Video) - Jeremy Camp</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Air Supply - Sweet Dreams (Official Lyric Video)</v>
+        <v>Alesso, OneRepublic - In Your Eyes (Visualizer)</v>
       </c>
       <c r="B67" t="str">
-        <v>4 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=axiK2vYjXio</v>
+        <v>https://www.youtube.com/watch?v=bS9C1ipyMy8</v>
       </c>
       <c r="D67" t="str">
         <v>2026-06-08</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>4 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>Air Supply</v>
+        <v>Alesso</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Air Supply - Sweet Dreams (Official Lyric Video) - Air Supply</v>
+        <v>Alesso, OneRepublic - In Your Eyes (Visualizer) - Alesso</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Julia Cole - Treat Me Like Dirt (Official Lyric Video)</v>
+        <v>Malcolm Todd - Free.99 (Official Visualizer)</v>
       </c>
       <c r="B68" t="str">
-        <v>5 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=TS2Mgp5F0cs</v>
+        <v>https://www.youtube.com/watch?v=wBBQptUsOhw</v>
       </c>
       <c r="D68" t="str">
         <v>2026-06-08</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>5 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>Julia Cole Music</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Julia Cole - Treat Me Like Dirt (Official Lyric Video) - Julia Cole Music</v>
+        <v>Malcolm Todd - Free.99 (Official Visualizer) - Malcolm Todd</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Allen Stone - A Fathers Song - Placeholder Sessions</v>
+        <v>Isabel LaRosa - Every Life (Visualizer)</v>
       </c>
       <c r="B69" t="str">
-        <v>5 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=JPetpt4QMPE</v>
+        <v>https://www.youtube.com/watch?v=tIQDAtwNAY4</v>
       </c>
       <c r="D69" t="str">
         <v>2026-06-08</v>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>5 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>Allen Stone and Placeholder Sessions</v>
+        <v>Isabel LaRosa</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Allen Stone - A Fathers Song - Placeholder Sessions - Allen Stone and Placeholder Sessions</v>
+        <v>Isabel LaRosa - Every Life (Visualizer) - Isabel LaRosa</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Morgan Wallen - Don't We (Live From Tuscaloosa)</v>
+        <v>Wyatt Flores - Half The Man (Official Music Video)</v>
       </c>
       <c r="B70" t="str">
-        <v>5 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=qhmWM3uXPAU</v>
+        <v>https://www.youtube.com/watch?v=2ChzcWHryFM</v>
       </c>
       <c r="D70" t="str">
         <v>2026-06-08</v>
@@ -3035,13 +3035,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>5 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>Morgan Wallen</v>
+        <v>Wyatt Flores</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Morgan Wallen - Don't We (Live From Tuscaloosa) - Morgan Wallen</v>
+        <v>Wyatt Flores - Half The Man (Official Music Video) - Wyatt Flores</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Billy Idol - John Wayne feat. Alison Mosshart (Official Music Video)</v>
+        <v>Mckenna Grace - Ugly and Rotten (Official Music Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>5 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=47LNk7oiTVI</v>
+        <v>https://www.youtube.com/watch?v=4yXFVgy7laM</v>
       </c>
       <c r="D71" t="str">
         <v>2026-06-08</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>5 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>Billy Idol</v>
+        <v>Mckenna Grace</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Billy Idol - John Wayne feat. Alison Mosshart (Official Music Video) - Billy Idol</v>
+        <v>Mckenna Grace - Ugly and Rotten (Official Music Video) - Mckenna Grace</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>'It's Unusual' Official Music Video - Kelly Boesch | 4K</v>
+        <v>Robert Grace - If You Were Gone ft. Bob Grace (OFFICIAL LYRIC VIDEO)</v>
       </c>
       <c r="B72" t="str">
-        <v>9 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=Ru3fB2l1RSo</v>
+        <v>https://www.youtube.com/watch?v=fbpQjMi3Hco</v>
       </c>
       <c r="D72" t="str">
         <v>2026-06-08</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>9 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>Kelly Boesch AI Art</v>
+        <v>Robert Grace</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>'It's Unusual' Official Music Video - Kelly Boesch | 4K - Kelly Boesch AI Art</v>
+        <v>Robert Grace - If You Were Gone ft. Bob Grace (OFFICIAL LYRIC VIDEO) - Robert Grace</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Icona Pop - Butterfly Feelings (Official Video)</v>
+        <v>Boyzone - No Matter What (Live)</v>
       </c>
       <c r="B73" t="str">
-        <v>5 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=AMW1Zq9RbIU</v>
+        <v>https://www.youtube.com/watch?v=CEy96_jHw-Q</v>
       </c>
       <c r="D73" t="str">
         <v>2026-06-08</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>5 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>Icona Pop</v>
+        <v>Boyzone</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Icona Pop - Butterfly Feelings (Official Video) - Icona Pop</v>
+        <v>Boyzone - No Matter What (Live) - Boyzone</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Hippo Campus - South</v>
+        <v>Florrie - The Times (Official Video)</v>
       </c>
       <c r="B74" t="str">
-        <v>6 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=FYOmFfV7Ojo</v>
+        <v>https://www.youtube.com/watch?v=6yBlNUaW7r4</v>
       </c>
       <c r="D74" t="str">
         <v>2026-06-08</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>6 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>Hippo Campus</v>
+        <v>florriemusic</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Hippo Campus - South - Hippo Campus</v>
+        <v>Florrie - The Times (Official Video) - florriemusic</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>elijah woods - Old (Treehouse Sessions)</v>
+        <v>Madonna - Love Sensation (Official Visualizer)</v>
       </c>
       <c r="B75" t="str">
-        <v>6 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=yDlkPdR_6zM</v>
+        <v>https://www.youtube.com/watch?v=88fD-UtG_yo</v>
       </c>
       <c r="D75" t="str">
         <v>2026-06-08</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>6 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>elijah woods</v>
+        <v>Madonna</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>elijah woods - Old (Treehouse Sessions) - elijah woods</v>
+        <v>Madonna - Love Sensation (Official Visualizer) - Madonna</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Nothing But Thieves - Evolution (Official Video)</v>
+        <v>DMA'S - Hurracane (Official Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>6 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=hmjfuuuRRYU</v>
+        <v>https://www.youtube.com/watch?v=-zTB57LiXPk</v>
       </c>
       <c r="D76" t="str">
         <v>2026-06-08</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>6 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>Nothing But Thieves</v>
+        <v>DMA'S</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Nothing But Thieves - Evolution (Official Video) - Nothing But Thieves</v>
+        <v>DMA'S - Hurracane (Official Video) - DMA'S</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Ariana Grande - hate that i made you love me (official music video)</v>
+        <v>Lainey Wilson and John Mayer - Phone, Keys, Wallet (Official Audio)</v>
       </c>
       <c r="B77" t="str">
-        <v>6 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=82-jTNka3uc</v>
+        <v>https://www.youtube.com/watch?v=JzW6RnzeF9A</v>
       </c>
       <c r="D77" t="str">
         <v>2026-06-08</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>6 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>Ariana Grande</v>
+        <v>Lainey Wilson and John Mayer</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Ariana Grande - hate that i made you love me (official music video) - Ariana Grande</v>
+        <v>Lainey Wilson and John Mayer - Phone, Keys, Wallet (Official Audio) - Lainey Wilson and John Mayer</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>LAUREL - Fire Breather</v>
+        <v>ROLE MODEL - High Hopes 3000 (Official Music Video)</v>
       </c>
       <c r="B78" t="str">
-        <v>6 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=rtyavLIJjy0</v>
+        <v>https://www.youtube.com/watch?v=D_KTG0BzRiI</v>
       </c>
       <c r="D78" t="str">
         <v>2026-06-08</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>6 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>LAUREL</v>
+        <v>ROLE MODEL</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>LAUREL - Fire Breather - LAUREL</v>
+        <v>ROLE MODEL - High Hopes 3000 (Official Music Video) - ROLE MODEL</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>The Warning - Ego (Performance Video)</v>
+        <v>Shawn Mendes - Treat You Better (Live from New York)</v>
       </c>
       <c r="B79" t="str">
-        <v>8 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=7PApWObImjo</v>
+        <v>https://www.youtube.com/watch?v=29bfaHc1XiY</v>
       </c>
       <c r="D79" t="str">
         <v>2026-06-08</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>8 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>The Warning</v>
+        <v>Shawn Mendes</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>The Warning - Ego (Performance Video) - The Warning</v>
+        <v>Shawn Mendes - Treat You Better (Live from New York) - Shawn Mendes</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (feat. Gabito Ballesteros) [Official Lyric Video]</v>
+        <v>SIENNA SPIRO - The Visitor (Official Music Video)</v>
       </c>
       <c r="B80" t="str">
-        <v>8 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=vruZSAYJBe4</v>
+        <v>https://www.youtube.com/watch?v=LiYb4WGbp5Y</v>
       </c>
       <c r="D80" t="str">
         <v>2026-06-08</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>8 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (feat. Gabito Ballesteros) [Official Lyric Video] - David Guetta and Jennifer Lopez</v>
+        <v>SIENNA SPIRO - The Visitor (Official Music Video) - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Armin van Buuren - Equanimity (from 'Piano' album) [Official Video]</v>
+        <v>Just Slide Official Music Video | Kelly Boesch | 4K</v>
       </c>
       <c r="B81" t="str">
-        <v>8 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=k93t10R-Qrg</v>
+        <v>https://www.youtube.com/watch?v=lC14fuU8aPc</v>
       </c>
       <c r="D81" t="str">
         <v>2026-06-08</v>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>8 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>Armin van Buuren</v>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Armin van Buuren - Equanimity (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Just Slide Official Music Video | Kelly Boesch | 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>“I Didn’t Know What Time It Was” - Andrew Bird Jazz Trio (Live from The Green Mill)</v>
+        <v>Europe - The Cult of Ignorance (Official Video)</v>
       </c>
       <c r="B82" t="str">
-        <v>9 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=XyRgdfXo2nI</v>
+        <v>https://www.youtube.com/watch?v=p-IOsjOJpnA</v>
       </c>
       <c r="D82" t="str">
         <v>2026-06-08</v>
@@ -3491,13 +3491,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>9 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>Andrew Bird</v>
+        <v>Europe</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>“I Didn’t Know What Time It Was” - Andrew Bird Jazz Trio (Live from The Green Mill) - Andrew Bird</v>
+        <v>Europe - The Cult of Ignorance (Official Video) - Europe</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Danny Gokey - God's Not (Official Music Video)</v>
+        <v>Air Supply - Sweet Dreams (Official Lyric Video)</v>
       </c>
       <c r="B83" t="str">
-        <v>9 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=oGpKqX6ftcU</v>
+        <v>https://www.youtube.com/watch?v=axiK2vYjXio</v>
       </c>
       <c r="D83" t="str">
         <v>2026-06-08</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>9 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>Danny Gokey</v>
+        <v>Air Supply</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Danny Gokey - God's Not (Official Music Video) - Danny Gokey</v>
+        <v>Air Supply - Sweet Dreams (Official Lyric Video) - Air Supply</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Armik - Brisas (2026 Remaster/Remix) (Exciting Rumba Flamenco, Spanish Guitar)</v>
+        <v>Julia Cole - Treat Me Like Dirt (Official Lyric Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>9 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=51Zu2iU2z2Q</v>
+        <v>https://www.youtube.com/watch?v=TS2Mgp5F0cs</v>
       </c>
       <c r="D84" t="str">
         <v>2026-06-08</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>9 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>Armik</v>
+        <v>Julia Cole Music</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Armik - Brisas (2026 Remaster/Remix) (Exciting Rumba Flamenco, Spanish Guitar) - Armik</v>
+        <v>Julia Cole - Treat Me Like Dirt (Official Lyric Video) - Julia Cole Music</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Holly Humberstone - Lucy (Free People Sessions)</v>
+        <v>Allen Stone - A Fathers Song - Placeholder Sessions</v>
       </c>
       <c r="B85" t="str">
-        <v>9 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=c1GR2TTs9W8</v>
+        <v>https://www.youtube.com/watch?v=JPetpt4QMPE</v>
       </c>
       <c r="D85" t="str">
         <v>2026-06-08</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>9 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>Holly Humberstone and Free People</v>
+        <v>Allen Stone and Placeholder Sessions</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Holly Humberstone - Lucy (Free People Sessions) - Holly Humberstone and Free People</v>
+        <v>Allen Stone - A Fathers Song - Placeholder Sessions - Allen Stone and Placeholder Sessions</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>The Offspring - Why Don’t You Get a Job? | Live at BeachLife Festival 2026</v>
+        <v>Morgan Wallen - Don't We (Live From Tuscaloosa)</v>
       </c>
       <c r="B86" t="str">
-        <v>9 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=zRJ2etb_rpI</v>
+        <v>https://www.youtube.com/watch?v=qhmWM3uXPAU</v>
       </c>
       <c r="D86" t="str">
         <v>2026-06-08</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>9 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>The Offspring</v>
+        <v>Morgan Wallen</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>The Offspring - Why Don’t You Get a Job? | Live at BeachLife Festival 2026 - The Offspring</v>
+        <v>Morgan Wallen - Don't We (Live From Tuscaloosa) - Morgan Wallen</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Jagwar Twin, sir lucius - bad feeling (oompa loompa) (Visualizer)</v>
+        <v>Billy Idol - John Wayne feat. Alison Mosshart (Official Music Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>9 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=XGgI5HvR-gg</v>
+        <v>https://www.youtube.com/watch?v=47LNk7oiTVI</v>
       </c>
       <c r="D87" t="str">
         <v>2026-06-08</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>9 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>Jagwar Twin</v>
+        <v>Billy Idol</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Jagwar Twin, sir lucius - bad feeling (oompa loompa) (Visualizer) - Jagwar Twin</v>
+        <v>Billy Idol - John Wayne feat. Alison Mosshart (Official Music Video) - Billy Idol</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Nathan Evans x SAINT PHNX - Home (World Cup 2026) (Official Music Video)</v>
+        <v>'It's Unusual' Official Music Video - Kelly Boesch | 4K</v>
       </c>
       <c r="B88" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=lRBNYETENNg</v>
+        <v>https://www.youtube.com/watch?v=Ru3fB2l1RSo</v>
       </c>
       <c r="D88" t="str">
         <v>2026-06-08</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>NathanEvanss</v>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Nathan Evans x SAINT PHNX - Home (World Cup 2026) (Official Music Video) - NathanEvanss</v>
+        <v>'It's Unusual' Official Music Video - Kelly Boesch | 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Greta Van Fleet - Play Your Games (Official Video)</v>
+        <v>Icona Pop - Butterfly Feelings (Official Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>9 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=CJsfI1QVBEM</v>
+        <v>https://www.youtube.com/watch?v=AMW1Zq9RbIU</v>
       </c>
       <c r="D89" t="str">
         <v>2026-06-08</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>9 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>Greta Van Fleet</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Greta Van Fleet - Play Your Games (Official Video) - Greta Van Fleet</v>
+        <v>Icona Pop - Butterfly Feelings (Official Video) - Icona Pop</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Lola Young – From Down Here (From a Living Room)</v>
+        <v>Hippo Campus - South</v>
       </c>
       <c r="B90" t="str">
-        <v>9 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=uF5HUfho2NU</v>
+        <v>https://www.youtube.com/watch?v=FYOmFfV7Ojo</v>
       </c>
       <c r="D90" t="str">
         <v>2026-06-08</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>9 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>Lola Young</v>
+        <v>Hippo Campus</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Lola Young – From Down Here (From a Living Room) - Lola Young</v>
+        <v>Hippo Campus - South - Hippo Campus</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Lawrence - Rain Check ft. Quinn XCII (Lyric Video)</v>
+        <v>elijah woods - Old (Treehouse Sessions)</v>
       </c>
       <c r="B91" t="str">
-        <v>9 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=xXeyznlIrFY</v>
+        <v>https://www.youtube.com/watch?v=yDlkPdR_6zM</v>
       </c>
       <c r="D91" t="str">
         <v>2026-06-08</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>9 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>Lawrence and Quinn XCII</v>
+        <v>elijah woods</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Lawrence - Rain Check ft. Quinn XCII (Lyric Video) - Lawrence and Quinn XCII</v>
+        <v>elijah woods - Old (Treehouse Sessions) - elijah woods</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>ANTONIA - NO HATE | Official Music Video</v>
+        <v>Nothing But Thieves - Evolution (Official Video)</v>
       </c>
       <c r="B92" t="str">
-        <v>9 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=rhlONr1DTj0</v>
+        <v>https://www.youtube.com/watch?v=hmjfuuuRRYU</v>
       </c>
       <c r="D92" t="str">
         <v>2026-06-08</v>
@@ -3871,13 +3871,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>9 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>ANTONIA</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>ANTONIA - NO HATE | Official Music Video - ANTONIA</v>
+        <v>Nothing But Thieves - Evolution (Official Video) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>R3HAB - "Lost in translation..." (Official Lyric Video)</v>
+        <v>Ariana Grande - hate that i made you love me (official music video)</v>
       </c>
       <c r="B93" t="str">
-        <v>9 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=TbJtz0oy2cI</v>
+        <v>https://www.youtube.com/watch?v=82-jTNka3uc</v>
       </c>
       <c r="D93" t="str">
         <v>2026-06-08</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>9 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>R3HAB</v>
+        <v>Ariana Grande</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>R3HAB - "Lost in translation..." (Official Lyric Video) - R3HAB</v>
+        <v>Ariana Grande - hate that i made you love me (official music video) - Ariana Grande</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Pink Floyd - Shine On You Crazy Diamond (Parts 1-5) - Live in Venice (Official Video)</v>
+        <v>LAUREL - Fire Breather</v>
       </c>
       <c r="B94" t="str">
-        <v>9 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=kwiawhDk2TM</v>
+        <v>https://www.youtube.com/watch?v=rtyavLIJjy0</v>
       </c>
       <c r="D94" t="str">
         <v>2026-06-08</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>9 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>Pink Floyd</v>
+        <v>LAUREL</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Pink Floyd - Shine On You Crazy Diamond (Parts 1-5) - Live in Venice (Official Video) - Pink Floyd</v>
+        <v>LAUREL - Fire Breather - LAUREL</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>SHADE - TOXIC</v>
+        <v>The Warning - Ego (Performance Video)</v>
       </c>
       <c r="B95" t="str">
-        <v>9 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=A3km0zrBKSg</v>
+        <v>https://www.youtube.com/watch?v=7PApWObImjo</v>
       </c>
       <c r="D95" t="str">
         <v>2026-06-08</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>9 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>Shade Official Channel</v>
+        <v>The Warning</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>SHADE - TOXIC - Shade Official Channel</v>
+        <v>The Warning - Ego (Performance Video) - The Warning</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Dua Lipa - Physical (Live From Mexico)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (feat. Gabito Ballesteros) [Official Lyric Video]</v>
       </c>
       <c r="B96" t="str">
-        <v>10 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=xZAe-d3bXTs</v>
+        <v>https://www.youtube.com/watch?v=vruZSAYJBe4</v>
       </c>
       <c r="D96" t="str">
         <v>2026-06-08</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>10 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>Dua Lipa</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Dua Lipa - Physical (Live From Mexico) - Dua Lipa</v>
+        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (feat. Gabito Ballesteros) [Official Lyric Video] - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Dagny - Rain (Lyric Video)</v>
+        <v>Armin van Buuren - Equanimity (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B97" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=j3ZJwczZoUQ</v>
+        <v>https://www.youtube.com/watch?v=k93t10R-Qrg</v>
       </c>
       <c r="D97" t="str">
         <v>2026-06-08</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>Dagny</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Dagny - Rain (Lyric Video) - Dagny</v>
+        <v>Armin van Buuren - Equanimity (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Modern Talking - Cheri Cheri Lady (Auf los geht's los, 14.09.1985)</v>
+        <v>“I Didn’t Know What Time It Was” - Andrew Bird Jazz Trio (Live from The Green Mill)</v>
       </c>
       <c r="B98" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=c0LtTVKNwNA</v>
+        <v>https://www.youtube.com/watch?v=XyRgdfXo2nI</v>
       </c>
       <c r="D98" t="str">
         <v>2026-06-08</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>Modern Talking Offiziell</v>
+        <v>Andrew Bird</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Modern Talking - Cheri Cheri Lady (Auf los geht's los, 14.09.1985) - Modern Talking Offiziell</v>
+        <v>“I Didn’t Know What Time It Was” - Andrew Bird Jazz Trio (Live from The Green Mill) - Andrew Bird</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>The Chemical Brothers - Go (Live Show Visual)</v>
+        <v>Danny Gokey - God's Not (Official Music Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=fHCIchBq8CM</v>
+        <v>https://www.youtube.com/watch?v=oGpKqX6ftcU</v>
       </c>
       <c r="D99" t="str">
         <v>2026-06-08</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>The Chemical Brothers</v>
+        <v>Danny Gokey</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>The Chemical Brothers - Go (Live Show Visual) - The Chemical Brothers</v>
+        <v>Danny Gokey - God's Not (Official Music Video) - Danny Gokey</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Jonas Blue - Girl (Official Lyric Video)</v>
+        <v>Armik - Brisas (2026 Remaster/Remix) (Exciting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B100" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=FTUe3jzUqXU</v>
+        <v>https://www.youtube.com/watch?v=51Zu2iU2z2Q</v>
       </c>
       <c r="D100" t="str">
         <v>2026-06-08</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>Defected Records and Jonas Blue</v>
+        <v>Armik</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Jonas Blue - Girl (Official Lyric Video) - Defected Records and Jonas Blue</v>
+        <v>Armik - Brisas (2026 Remaster/Remix) (Exciting Rumba Flamenco, Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Dogpark - Don't Lie (Visualizer)</v>
+        <v>Holly Humberstone - Lucy (Free People Sessions)</v>
       </c>
       <c r="B101" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=is7qKBRycJI</v>
+        <v>https://www.youtube.com/watch?v=c1GR2TTs9W8</v>
       </c>
       <c r="D101" t="str">
         <v>2026-06-08</v>
@@ -4213,13 +4213,13 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G101" t="str">
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Dogpark</v>
+        <v>Holly Humberstone and Free People</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,7 +4231,7 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Dogpark - Don't Lie (Visualizer) - Dogpark</v>
+        <v>Holly Humberstone - Lucy (Free People Sessions) - Holly Humberstone and Free People</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-06-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-06-week02/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Jason Derulo - The Other Side (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B2" t="str">
-        <v>8h ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=ym-h0EIlL3A</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>8h ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,7 +477,7 @@
         <v>Stephen Sanchez - Be More (Live at Capital's Summertime Ball 2026) | Capital</v>
       </c>
       <c r="B3" t="str">
-        <v>8h ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=bIwcNmu-rAg</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>8h ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,7 +515,7 @@
         <v>Jason Derulo - Take You Dancing (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B4" t="str">
-        <v>8h ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=oLzj8E8fHRQ</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>8h ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>Sekou - Someone Like You (Adele Cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B5" t="str">
-        <v>8h ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=YIy2g4enMiY</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>8h ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,7 +591,7 @@
         <v>Sienna Spiro - He's Not My Baby, I'm His (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B6" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=NhuPT6MR2XU</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,7 +629,7 @@
         <v>DEEP PURPLE - DIABLO (Official Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=Z4RpBEg5uis</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>Reba McEntire - You Never Gave Up On Me</v>
       </c>
       <c r="B8" t="str">
-        <v>19h ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=AUCRUStLmJM</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>19h ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,7 +705,7 @@
         <v>elijah woods - Wonder (Official Lyric Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>22h ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=sDDbD4R-xD4</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>22h ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -743,7 +743,7 @@
         <v>XG - Flowers (Sweet Female Attitude Cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B10" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=MxJQoyKh8TQ</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -781,7 +781,7 @@
         <v>Niall Horan - Nice To Meet Ya (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B11" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=-UIkkGxMQG8</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -819,7 +819,7 @@
         <v>Niall Horan - Steal My Girl (One Direction cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B12" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=b_uO5ROpk_0</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -857,7 +857,7 @@
         <v>Niall Horan - Dinner Party (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B13" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=hSJfAFpdllk</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -895,7 +895,7 @@
         <v>Niall Horan - Slow Hands (Live at Capital's Summertime Ball 2026) | Capital</v>
       </c>
       <c r="B14" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=vdMK2DvnWJI</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -933,7 +933,7 @@
         <v>RAYE - Joy (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B15" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=5gvhRAGaOUo</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,7 +971,7 @@
         <v>Myles Smith - Stargazing (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B16" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=2AIMnAPxqfw</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1009,7 +1009,7 @@
         <v>Lola Young - From Down Here (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B17" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=UD7HkkAbnVA</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1047,7 +1047,7 @@
         <v>XG - Hypnotize (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B18" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=c5u3ur4vLo0</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1085,7 +1085,7 @@
         <v>Sienna Spiro - The Visitor (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B19" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=MibVDrnrQ10</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,7 +1123,7 @@
         <v>Sienna Spiro - Die On This Hill (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B20" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=UhWumamExiI</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1161,7 +1161,7 @@
         <v>RAYE - Where Is My Husband? (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B21" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=Z_HR2ZYY1VA</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1199,7 +1199,7 @@
         <v>RAYE - Escapism (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B22" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=ywplqaIeHeQ</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1237,7 +1237,7 @@
         <v>Take That - Never Forget (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B23" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=9S61JkOZLe8</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1275,7 +1275,7 @@
         <v>Robyn - Dancing On My Own (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B24" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=_4SfgNPngbo</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1313,7 +1313,7 @@
         <v>Take That - Patience (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B25" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=_I9qIxmrDuI</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1351,7 +1351,7 @@
         <v>Mis-Teeq - Full Set (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B26" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=5AyQM_coDb8</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1389,7 +1389,7 @@
         <v>Myles Smith - Stay (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B27" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=2ekY7Cb7CKs</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1427,7 +1427,7 @@
         <v>Take That - Rule The World (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B28" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=0nc-qdhh6eU</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1465,7 +1465,7 @@
         <v>Sienna Spiro - Material Lover (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B29" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=dZjAtTc9DBQ</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1503,7 +1503,7 @@
         <v>Take That - Shine (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B30" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=T6TmxqOGIf0</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1541,7 +1541,7 @@
         <v>MEEK - Dracula (Tame Impala Cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B31" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=4jnM--XhsC0</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1579,7 +1579,7 @@
         <v>MEEK - Fabulous (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B32" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=kKSlraqNMhI</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1617,7 +1617,7 @@
         <v>Lola Young - Messy (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B33" t="str">
-        <v>1d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=cUvsaKkjHYQ</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>1d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1655,7 +1655,7 @@
         <v>Stephen Sanchez - Until I Found You (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B34" t="str">
-        <v>1d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=oKKNK0OCpQk</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>1d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1693,7 +1693,7 @@
         <v>Lola Young - D£aler (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B35" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=ymvr4RCN-WE</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1731,7 +1731,7 @@
         <v>Lola Young - One Thing (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B36" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=nhL2l4HCiRg</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1769,7 +1769,7 @@
         <v>Bebe Rexha - Sad Girls (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B37" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=e0PkSQNMcGs</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1807,7 +1807,7 @@
         <v>Robyn - Dopamine (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B38" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=-7mPIus0U5Y</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1845,7 +1845,7 @@
         <v>Jason Derulo - Ridin' Solo (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B39" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=G6jhovaAz3U</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1883,7 +1883,7 @@
         <v>Jason Derulo - Trumpets (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B40" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=QkCKENp-4Rs</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1921,7 +1921,7 @@
         <v>Jason Derulo - Whatcha Say (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B41" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=jsFekVlEaSA</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1959,7 +1959,7 @@
         <v>Bebe Rexha - New Religion (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B42" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=nfDKQ09bY_w</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -1997,7 +1997,7 @@
         <v>Bebe Rexha - I'm Good (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B43" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=eqceDkaK3PU</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2035,7 +2035,7 @@
         <v>Bebe Rexha - In The Name Of Love (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B44" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=UlP9zTLUeLw</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2073,7 +2073,7 @@
         <v>Strange Surreal AI - In Here - Kelly Boesch | 4K</v>
       </c>
       <c r="B45" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=QCNwFDTkfYU</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2111,7 +2111,7 @@
         <v>The Cranberries - Scenes From 'Linger' (The Only Color Reel)</v>
       </c>
       <c r="B46" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=5-peG8H-lqE</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2149,7 +2149,7 @@
         <v>Jordana Bryant - Too Little Too Late (Official Lyric Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=P26-NjdBmbU</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2187,7 +2187,7 @@
         <v>Grace Enger - "Running Back To You" (Official Music Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=BON1BSWLntE</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2225,7 +2225,7 @@
         <v>The Offspring - Gone Away | Live at BeachLife Festival 2026</v>
       </c>
       <c r="B49" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=UTw106Ivz8o</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2263,7 +2263,7 @@
         <v>Lola Young – From Down Here (From The Pool)</v>
       </c>
       <c r="B50" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=YFhpMpONGUY</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2301,7 +2301,7 @@
         <v>CAIN - Living Water (Music Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=WrsXAfnTAdA</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2339,7 +2339,7 @@
         <v>B.B. King &amp; Eric Clapton - Riding With The King (Official Music Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=L7Ls8ceHxhc</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2377,7 +2377,7 @@
         <v>Blu DeTiger - Whisper (Official Music Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=OfcBfPnskG4</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2415,7 +2415,7 @@
         <v>Romeo Santos, Prince Royce - Ay! San Miguel (Official Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=-uvNvVtUidc</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2453,7 +2453,7 @@
         <v>Pink Floyd - Pigs on the Wing (8-Track Version - Official Audio)</v>
       </c>
       <c r="B55" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=WZUKJ90i6Tw</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2491,7 +2491,7 @@
         <v>Holly Humberstone - it’s just White Noise</v>
       </c>
       <c r="B56" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=KeRZtPUjl8g</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2529,7 +2529,7 @@
         <v>Freya Ridings - Mother Of Pearl (Official Video)</v>
       </c>
       <c r="B57" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=So5gx12fCsA</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2567,7 +2567,7 @@
         <v>MUSE - Nightshift Superstar (Official Music Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=p--xk9n1eIM</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2605,7 +2605,7 @@
         <v>Ellie Goulding - Black Prada Dress (Visualiser)</v>
       </c>
       <c r="B59" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=zr9CYpgPueI</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2643,7 +2643,7 @@
         <v>Evanescence - Sanctuary (Official Visualizer)</v>
       </c>
       <c r="B60" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=E64jOWeVfpg</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2681,7 +2681,7 @@
         <v>The Beaches - Perfect 10 (Official Visualizer)</v>
       </c>
       <c r="B61" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=N7TOR_l-CM8</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2719,7 +2719,7 @@
         <v>Bella White - Stuff (Official Music Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=7QZtxsGBTks</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2757,7 +2757,7 @@
         <v>Meduza, Rani - Silence (Official Visualizer)</v>
       </c>
       <c r="B63" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=cIdqz-WMod4</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2795,7 +2795,7 @@
         <v>CAIN - Living Water (Lyric Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=Hv-8CM5NIPM</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2833,7 +2833,7 @@
         <v>Fitz and the Tantrums - Greenlight (Official Visualizer)</v>
       </c>
       <c r="B65" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=Zx-ZPBbcA58</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2871,7 +2871,7 @@
         <v>Jeremy Camp - Reflector (Official Music Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=SR-4q1yiYNA</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2909,7 +2909,7 @@
         <v>Alesso, OneRepublic - In Your Eyes (Visualizer)</v>
       </c>
       <c r="B67" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=bS9C1ipyMy8</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2947,7 +2947,7 @@
         <v>Malcolm Todd - Free.99 (Official Visualizer)</v>
       </c>
       <c r="B68" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=wBBQptUsOhw</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -2985,7 +2985,7 @@
         <v>Isabel LaRosa - Every Life (Visualizer)</v>
       </c>
       <c r="B69" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=tIQDAtwNAY4</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3023,7 +3023,7 @@
         <v>Wyatt Flores - Half The Man (Official Music Video)</v>
       </c>
       <c r="B70" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=2ChzcWHryFM</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3061,7 +3061,7 @@
         <v>Mckenna Grace - Ugly and Rotten (Official Music Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=4yXFVgy7laM</v>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3099,7 +3099,7 @@
         <v>Robert Grace - If You Were Gone ft. Bob Grace (OFFICIAL LYRIC VIDEO)</v>
       </c>
       <c r="B72" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=fbpQjMi3Hco</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3137,7 +3137,7 @@
         <v>Boyzone - No Matter What (Live)</v>
       </c>
       <c r="B73" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=CEy96_jHw-Q</v>
@@ -3149,7 +3149,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3175,7 +3175,7 @@
         <v>Florrie - The Times (Official Video)</v>
       </c>
       <c r="B74" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=6yBlNUaW7r4</v>
@@ -3187,7 +3187,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3213,7 +3213,7 @@
         <v>Madonna - Love Sensation (Official Visualizer)</v>
       </c>
       <c r="B75" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=88fD-UtG_yo</v>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3251,7 +3251,7 @@
         <v>DMA'S - Hurracane (Official Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=-zTB57LiXPk</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3289,7 +3289,7 @@
         <v>Lainey Wilson and John Mayer - Phone, Keys, Wallet (Official Audio)</v>
       </c>
       <c r="B77" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=JzW6RnzeF9A</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -3327,7 +3327,7 @@
         <v>ROLE MODEL - High Hopes 3000 (Official Music Video)</v>
       </c>
       <c r="B78" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=D_KTG0BzRiI</v>
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -3365,7 +3365,7 @@
         <v>Shawn Mendes - Treat You Better (Live from New York)</v>
       </c>
       <c r="B79" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=29bfaHc1XiY</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -3403,7 +3403,7 @@
         <v>SIENNA SPIRO - The Visitor (Official Music Video)</v>
       </c>
       <c r="B80" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=LiYb4WGbp5Y</v>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -3441,7 +3441,7 @@
         <v>Just Slide Official Music Video | Kelly Boesch | 4K</v>
       </c>
       <c r="B81" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=lC14fuU8aPc</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -3479,7 +3479,7 @@
         <v>Europe - The Cult of Ignorance (Official Video)</v>
       </c>
       <c r="B82" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=p-IOsjOJpnA</v>
@@ -3491,7 +3491,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -3517,7 +3517,7 @@
         <v>Air Supply - Sweet Dreams (Official Lyric Video)</v>
       </c>
       <c r="B83" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=axiK2vYjXio</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -3555,7 +3555,7 @@
         <v>Julia Cole - Treat Me Like Dirt (Official Lyric Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=TS2Mgp5F0cs</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -3593,7 +3593,7 @@
         <v>Allen Stone - A Fathers Song - Placeholder Sessions</v>
       </c>
       <c r="B85" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=JPetpt4QMPE</v>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -3631,7 +3631,7 @@
         <v>Morgan Wallen - Don't We (Live From Tuscaloosa)</v>
       </c>
       <c r="B86" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=qhmWM3uXPAU</v>
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -3669,7 +3669,7 @@
         <v>Billy Idol - John Wayne feat. Alison Mosshart (Official Music Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=47LNk7oiTVI</v>
@@ -3681,7 +3681,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -3707,7 +3707,7 @@
         <v>'It's Unusual' Official Music Video - Kelly Boesch | 4K</v>
       </c>
       <c r="B88" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=Ru3fB2l1RSo</v>
@@ -3719,7 +3719,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -3745,7 +3745,7 @@
         <v>Icona Pop - Butterfly Feelings (Official Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=AMW1Zq9RbIU</v>
@@ -3757,7 +3757,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -3783,7 +3783,7 @@
         <v>Hippo Campus - South</v>
       </c>
       <c r="B90" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=FYOmFfV7Ojo</v>
@@ -3795,7 +3795,7 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -3821,7 +3821,7 @@
         <v>elijah woods - Old (Treehouse Sessions)</v>
       </c>
       <c r="B91" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=yDlkPdR_6zM</v>
@@ -3833,7 +3833,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -3859,7 +3859,7 @@
         <v>Nothing But Thieves - Evolution (Official Video)</v>
       </c>
       <c r="B92" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=hmjfuuuRRYU</v>
@@ -3871,7 +3871,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -3897,7 +3897,7 @@
         <v>Ariana Grande - hate that i made you love me (official music video)</v>
       </c>
       <c r="B93" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=82-jTNka3uc</v>
@@ -3909,7 +3909,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -3935,7 +3935,7 @@
         <v>LAUREL - Fire Breather</v>
       </c>
       <c r="B94" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=rtyavLIJjy0</v>
@@ -3947,7 +3947,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -3973,7 +3973,7 @@
         <v>The Warning - Ego (Performance Video)</v>
       </c>
       <c r="B95" t="str">
-        <v>8d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C95" t="str">
         <v>https://www.youtube.com/watch?v=7PApWObImjo</v>
@@ -3985,7 +3985,7 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>8d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -4011,7 +4011,7 @@
         <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (feat. Gabito Ballesteros) [Official Lyric Video]</v>
       </c>
       <c r="B96" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C96" t="str">
         <v>https://www.youtube.com/watch?v=vruZSAYJBe4</v>
@@ -4023,7 +4023,7 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -4049,7 +4049,7 @@
         <v>Armin van Buuren - Equanimity (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B97" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=k93t10R-Qrg</v>
@@ -4061,7 +4061,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -4087,7 +4087,7 @@
         <v>“I Didn’t Know What Time It Was” - Andrew Bird Jazz Trio (Live from The Green Mill)</v>
       </c>
       <c r="B98" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=XyRgdfXo2nI</v>
@@ -4099,7 +4099,7 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -4125,7 +4125,7 @@
         <v>Danny Gokey - God's Not (Official Music Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C99" t="str">
         <v>https://www.youtube.com/watch?v=oGpKqX6ftcU</v>
@@ -4137,7 +4137,7 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
@@ -4163,7 +4163,7 @@
         <v>Armik - Brisas (2026 Remaster/Remix) (Exciting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B100" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=51Zu2iU2z2Q</v>
@@ -4175,7 +4175,7 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -4201,7 +4201,7 @@
         <v>Holly Humberstone - Lucy (Free People Sessions)</v>
       </c>
       <c r="B101" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=c1GR2TTs9W8</v>
@@ -4213,7 +4213,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G101" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-06-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-06-week02/titles.xlsx
@@ -439,19 +439,19 @@
         <v>Jason Derulo - The Other Side (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B2" t="str">
-        <v>10 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=ym-h0EIlL3A</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>10 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,19 +477,19 @@
         <v>Stephen Sanchez - Be More (Live at Capital's Summertime Ball 2026) | Capital</v>
       </c>
       <c r="B3" t="str">
-        <v>10 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=bIwcNmu-rAg</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>10 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,19 +515,19 @@
         <v>Jason Derulo - Take You Dancing (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B4" t="str">
-        <v>11 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=oLzj8E8fHRQ</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>11 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,19 +553,19 @@
         <v>Sekou - Someone Like You (Adele Cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B5" t="str">
-        <v>11 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=YIy2g4enMiY</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>11 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://www.youtube.com/watch?v=NhuPT6MR2XU</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://www.youtube.com/watch?v=Z4RpBEg5uis</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -667,19 +667,19 @@
         <v>Reba McEntire - You Never Gave Up On Me</v>
       </c>
       <c r="B8" t="str">
-        <v>21 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=AUCRUStLmJM</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E8" t="str">
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>21 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://www.youtube.com/watch?v=sDDbD4R-xD4</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://www.youtube.com/watch?v=MxJQoyKh8TQ</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://www.youtube.com/watch?v=-UIkkGxMQG8</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://www.youtube.com/watch?v=b_uO5ROpk_0</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://www.youtube.com/watch?v=hSJfAFpdllk</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://www.youtube.com/watch?v=vdMK2DvnWJI</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://www.youtube.com/watch?v=5gvhRAGaOUo</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://www.youtube.com/watch?v=2AIMnAPxqfw</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://www.youtube.com/watch?v=UD7HkkAbnVA</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://www.youtube.com/watch?v=c5u3ur4vLo0</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://www.youtube.com/watch?v=MibVDrnrQ10</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://www.youtube.com/watch?v=UhWumamExiI</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://www.youtube.com/watch?v=Z_HR2ZYY1VA</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://www.youtube.com/watch?v=ywplqaIeHeQ</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1237,19 +1237,19 @@
         <v>Take That - Never Forget (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B23" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=9S61JkOZLe8</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E23" t="str">
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1275,19 +1275,19 @@
         <v>Robyn - Dancing On My Own (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B24" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=_4SfgNPngbo</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E24" t="str">
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1313,19 +1313,19 @@
         <v>Take That - Patience (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B25" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=_I9qIxmrDuI</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E25" t="str">
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1351,19 +1351,19 @@
         <v>Mis-Teeq - Full Set (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B26" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=5AyQM_coDb8</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E26" t="str">
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1389,19 +1389,19 @@
         <v>Myles Smith - Stay (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B27" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=2ekY7Cb7CKs</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E27" t="str">
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1427,19 +1427,19 @@
         <v>Take That - Rule The World (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B28" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=0nc-qdhh6eU</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E28" t="str">
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1465,19 +1465,19 @@
         <v>Sienna Spiro - Material Lover (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B29" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=dZjAtTc9DBQ</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E29" t="str">
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1503,19 +1503,19 @@
         <v>Take That - Shine (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B30" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=T6TmxqOGIf0</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E30" t="str">
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1541,19 +1541,19 @@
         <v>MEEK - Dracula (Tame Impala Cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B31" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=4jnM--XhsC0</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E31" t="str">
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1579,19 +1579,19 @@
         <v>MEEK - Fabulous (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B32" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=kKSlraqNMhI</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E32" t="str">
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://www.youtube.com/watch?v=cUvsaKkjHYQ</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://www.youtube.com/watch?v=oKKNK0OCpQk</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://www.youtube.com/watch?v=ymvr4RCN-WE</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://www.youtube.com/watch?v=nhL2l4HCiRg</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://www.youtube.com/watch?v=e0PkSQNMcGs</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://www.youtube.com/watch?v=-7mPIus0U5Y</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://www.youtube.com/watch?v=G6jhovaAz3U</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://www.youtube.com/watch?v=QkCKENp-4Rs</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://www.youtube.com/watch?v=jsFekVlEaSA</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://www.youtube.com/watch?v=nfDKQ09bY_w</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://www.youtube.com/watch?v=eqceDkaK3PU</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://www.youtube.com/watch?v=UlP9zTLUeLw</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://www.youtube.com/watch?v=QCNwFDTkfYU</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2111,19 +2111,19 @@
         <v>The Cranberries - Scenes From 'Linger' (The Only Color Reel)</v>
       </c>
       <c r="B46" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=5-peG8H-lqE</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E46" t="str">
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://www.youtube.com/watch?v=P26-NjdBmbU</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://www.youtube.com/watch?v=BON1BSWLntE</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://www.youtube.com/watch?v=UTw106Ivz8o</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://www.youtube.com/watch?v=YFhpMpONGUY</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://www.youtube.com/watch?v=WrsXAfnTAdA</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://www.youtube.com/watch?v=L7Ls8ceHxhc</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://www.youtube.com/watch?v=OfcBfPnskG4</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://www.youtube.com/watch?v=-uvNvVtUidc</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://www.youtube.com/watch?v=WZUKJ90i6Tw</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://www.youtube.com/watch?v=KeRZtPUjl8g</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://www.youtube.com/watch?v=So5gx12fCsA</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://www.youtube.com/watch?v=p--xk9n1eIM</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://www.youtube.com/watch?v=zr9CYpgPueI</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://www.youtube.com/watch?v=E64jOWeVfpg</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://www.youtube.com/watch?v=N7TOR_l-CM8</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://www.youtube.com/watch?v=7QZtxsGBTks</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://www.youtube.com/watch?v=cIdqz-WMod4</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://www.youtube.com/watch?v=Hv-8CM5NIPM</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://www.youtube.com/watch?v=Zx-ZPBbcA58</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://www.youtube.com/watch?v=SR-4q1yiYNA</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://www.youtube.com/watch?v=bS9C1ipyMy8</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://www.youtube.com/watch?v=wBBQptUsOhw</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://www.youtube.com/watch?v=tIQDAtwNAY4</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://www.youtube.com/watch?v=2ChzcWHryFM</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://www.youtube.com/watch?v=4yXFVgy7laM</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3099,19 +3099,19 @@
         <v>Robert Grace - If You Were Gone ft. Bob Grace (OFFICIAL LYRIC VIDEO)</v>
       </c>
       <c r="B72" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=fbpQjMi3Hco</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E72" t="str">
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3137,19 +3137,19 @@
         <v>Boyzone - No Matter What (Live)</v>
       </c>
       <c r="B73" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=CEy96_jHw-Q</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E73" t="str">
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3175,19 +3175,19 @@
         <v>Florrie - The Times (Official Video)</v>
       </c>
       <c r="B74" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=6yBlNUaW7r4</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E74" t="str">
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3213,19 +3213,19 @@
         <v>Madonna - Love Sensation (Official Visualizer)</v>
       </c>
       <c r="B75" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=88fD-UtG_yo</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E75" t="str">
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://www.youtube.com/watch?v=-zTB57LiXPk</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://www.youtube.com/watch?v=JzW6RnzeF9A</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://www.youtube.com/watch?v=D_KTG0BzRiI</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://www.youtube.com/watch?v=29bfaHc1XiY</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://www.youtube.com/watch?v=LiYb4WGbp5Y</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://www.youtube.com/watch?v=lC14fuU8aPc</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://www.youtube.com/watch?v=p-IOsjOJpnA</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://www.youtube.com/watch?v=axiK2vYjXio</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3555,19 +3555,19 @@
         <v>Julia Cole - Treat Me Like Dirt (Official Lyric Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=TS2Mgp5F0cs</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E84" t="str">
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -3593,19 +3593,19 @@
         <v>Allen Stone - A Fathers Song - Placeholder Sessions</v>
       </c>
       <c r="B85" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=JPetpt4QMPE</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E85" t="str">
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://www.youtube.com/watch?v=qhmWM3uXPAU</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://www.youtube.com/watch?v=47LNk7oiTVI</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://www.youtube.com/watch?v=Ru3fB2l1RSo</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://www.youtube.com/watch?v=AMW1Zq9RbIU</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://www.youtube.com/watch?v=FYOmFfV7Ojo</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://www.youtube.com/watch?v=yDlkPdR_6zM</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://www.youtube.com/watch?v=hmjfuuuRRYU</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://www.youtube.com/watch?v=82-jTNka3uc</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://www.youtube.com/watch?v=rtyavLIJjy0</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://www.youtube.com/watch?v=7PApWObImjo</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://www.youtube.com/watch?v=vruZSAYJBe4</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://www.youtube.com/watch?v=k93t10R-Qrg</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://www.youtube.com/watch?v=XyRgdfXo2nI</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://www.youtube.com/watch?v=oGpKqX6ftcU</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://www.youtube.com/watch?v=51Zu2iU2z2Q</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>https://www.youtube.com/watch?v=c1GR2TTs9W8</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E101" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-06-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-06-week02/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Jason Derulo - The Other Side (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B2" t="str">
-        <v>15 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=ym-h0EIlL3A</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>15 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,7 +477,7 @@
         <v>Stephen Sanchez - Be More (Live at Capital's Summertime Ball 2026) | Capital</v>
       </c>
       <c r="B3" t="str">
-        <v>15 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=bIwcNmu-rAg</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>15 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,7 +515,7 @@
         <v>Jason Derulo - Take You Dancing (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B4" t="str">
-        <v>15 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=oLzj8E8fHRQ</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>15 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>Sekou - Someone Like You (Adele Cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B5" t="str">
-        <v>15 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=YIy2g4enMiY</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>15 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -2643,7 +2643,7 @@
         <v>Evanescence - Sanctuary (Official Visualizer)</v>
       </c>
       <c r="B60" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=E64jOWeVfpg</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2681,7 +2681,7 @@
         <v>The Beaches - Perfect 10 (Official Visualizer)</v>
       </c>
       <c r="B61" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=N7TOR_l-CM8</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2719,7 +2719,7 @@
         <v>Bella White - Stuff (Official Music Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=7QZtxsGBTks</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2757,7 +2757,7 @@
         <v>Meduza, Rani - Silence (Official Visualizer)</v>
       </c>
       <c r="B63" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=cIdqz-WMod4</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2795,7 +2795,7 @@
         <v>CAIN - Living Water (Lyric Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=Hv-8CM5NIPM</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2833,7 +2833,7 @@
         <v>Fitz and the Tantrums - Greenlight (Official Visualizer)</v>
       </c>
       <c r="B65" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=Zx-ZPBbcA58</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2871,7 +2871,7 @@
         <v>Jeremy Camp - Reflector (Official Music Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=SR-4q1yiYNA</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2909,7 +2909,7 @@
         <v>Alesso, OneRepublic - In Your Eyes (Visualizer)</v>
       </c>
       <c r="B67" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=bS9C1ipyMy8</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2947,7 +2947,7 @@
         <v>Malcolm Todd - Free.99 (Official Visualizer)</v>
       </c>
       <c r="B68" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=wBBQptUsOhw</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -2985,7 +2985,7 @@
         <v>Isabel LaRosa - Every Life (Visualizer)</v>
       </c>
       <c r="B69" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=tIQDAtwNAY4</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3023,7 +3023,7 @@
         <v>Wyatt Flores - Half The Man (Official Music Video)</v>
       </c>
       <c r="B70" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=2ChzcWHryFM</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3061,7 +3061,7 @@
         <v>Mckenna Grace - Ugly and Rotten (Official Music Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=4yXFVgy7laM</v>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3289,7 +3289,7 @@
         <v>Lainey Wilson and John Mayer - Phone, Keys, Wallet (Official Audio)</v>
       </c>
       <c r="B77" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=JzW6RnzeF9A</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G77" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-06-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-06-week02/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Jason Derulo - The Other Side (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B2" t="str">
-        <v>19 hours ago</v>
+        <v>23h ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=ym-h0EIlL3A</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>19 hours ago</v>
+        <v>23h ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,7 +477,7 @@
         <v>Stephen Sanchez - Be More (Live at Capital's Summertime Ball 2026) | Capital</v>
       </c>
       <c r="B3" t="str">
-        <v>19 hours ago</v>
+        <v>23h ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=bIwcNmu-rAg</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>19 hours ago</v>
+        <v>23h ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,7 +515,7 @@
         <v>Jason Derulo - Take You Dancing (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B4" t="str">
-        <v>19 hours ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=oLzj8E8fHRQ</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>19 hours ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>Sekou - Someone Like You (Adele Cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B5" t="str">
-        <v>19 hours ago</v>
+        <v>23h ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=YIy2g4enMiY</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>19 hours ago</v>
+        <v>23h ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,7 +591,7 @@
         <v>Sienna Spiro - He's Not My Baby, I'm His (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B6" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=NhuPT6MR2XU</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,7 +629,7 @@
         <v>DEEP PURPLE - DIABLO (Official Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=Z4RpBEg5uis</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>Reba McEntire - You Never Gave Up On Me</v>
       </c>
       <c r="B8" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=AUCRUStLmJM</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,7 +705,7 @@
         <v>elijah woods - Wonder (Official Lyric Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=sDDbD4R-xD4</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -743,7 +743,7 @@
         <v>XG - Flowers (Sweet Female Attitude Cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B10" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=MxJQoyKh8TQ</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -781,7 +781,7 @@
         <v>Niall Horan - Nice To Meet Ya (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B11" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=-UIkkGxMQG8</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -819,7 +819,7 @@
         <v>Niall Horan - Steal My Girl (One Direction cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B12" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=b_uO5ROpk_0</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -857,7 +857,7 @@
         <v>Niall Horan - Dinner Party (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B13" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=hSJfAFpdllk</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -895,7 +895,7 @@
         <v>Niall Horan - Slow Hands (Live at Capital's Summertime Ball 2026) | Capital</v>
       </c>
       <c r="B14" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=vdMK2DvnWJI</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -933,7 +933,7 @@
         <v>RAYE - Joy (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B15" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=5gvhRAGaOUo</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,7 +971,7 @@
         <v>Myles Smith - Stargazing (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B16" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=2AIMnAPxqfw</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1009,7 +1009,7 @@
         <v>Lola Young - From Down Here (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B17" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=UD7HkkAbnVA</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1047,7 +1047,7 @@
         <v>XG - Hypnotize (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B18" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=c5u3ur4vLo0</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1085,7 +1085,7 @@
         <v>Sienna Spiro - The Visitor (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B19" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=MibVDrnrQ10</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,7 +1123,7 @@
         <v>Sienna Spiro - Die On This Hill (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B20" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=UhWumamExiI</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1161,7 +1161,7 @@
         <v>RAYE - Where Is My Husband? (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B21" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=Z_HR2ZYY1VA</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1199,7 +1199,7 @@
         <v>RAYE - Escapism (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B22" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=ywplqaIeHeQ</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1237,7 +1237,7 @@
         <v>Take That - Never Forget (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B23" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=9S61JkOZLe8</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>Capital FM</v>
+        <v>Capital FM and Take That</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,7 +1267,7 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Take That - Never Forget (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Take That - Never Forget (Live at Capital's Summertime Ball 2026) - Capital FM and Take That</v>
       </c>
     </row>
     <row r="24">
@@ -1275,7 +1275,7 @@
         <v>Robyn - Dancing On My Own (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B24" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=_4SfgNPngbo</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1313,7 +1313,7 @@
         <v>Take That - Patience (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B25" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=_I9qIxmrDuI</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>Capital FM</v>
+        <v>Capital FM and Take That</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,7 +1343,7 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Take That - Patience (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Take That - Patience (Live at Capital's Summertime Ball 2026) - Capital FM and Take That</v>
       </c>
     </row>
     <row r="26">
@@ -1351,7 +1351,7 @@
         <v>Mis-Teeq - Full Set (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B26" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=5AyQM_coDb8</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1389,7 +1389,7 @@
         <v>Myles Smith - Stay (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B27" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=2ekY7Cb7CKs</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1427,7 +1427,7 @@
         <v>Take That - Rule The World (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B28" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=0nc-qdhh6eU</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>Capital FM</v>
+        <v>Capital FM and Take That</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,7 +1457,7 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Take That - Rule The World (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Take That - Rule The World (Live at Capital's Summertime Ball 2026) - Capital FM and Take That</v>
       </c>
     </row>
     <row r="29">
@@ -1465,7 +1465,7 @@
         <v>Sienna Spiro - Material Lover (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B29" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=dZjAtTc9DBQ</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1503,7 +1503,7 @@
         <v>Take That - Shine (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B30" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=T6TmxqOGIf0</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1541,7 +1541,7 @@
         <v>MEEK - Dracula (Tame Impala Cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B31" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=4jnM--XhsC0</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1579,7 +1579,7 @@
         <v>MEEK - Fabulous (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B32" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=kKSlraqNMhI</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1617,7 +1617,7 @@
         <v>Lola Young - Messy (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B33" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=cUvsaKkjHYQ</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1655,7 +1655,7 @@
         <v>Stephen Sanchez - Until I Found You (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B34" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=oKKNK0OCpQk</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1693,7 +1693,7 @@
         <v>Lola Young - D£aler (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B35" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=ymvr4RCN-WE</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1731,7 +1731,7 @@
         <v>Lola Young - One Thing (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B36" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=nhL2l4HCiRg</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1769,7 +1769,7 @@
         <v>Bebe Rexha - Sad Girls (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B37" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=e0PkSQNMcGs</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1807,7 +1807,7 @@
         <v>Robyn - Dopamine (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B38" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=-7mPIus0U5Y</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1845,7 +1845,7 @@
         <v>Jason Derulo - Ridin' Solo (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B39" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=G6jhovaAz3U</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1883,7 +1883,7 @@
         <v>Jason Derulo - Trumpets (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B40" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=QkCKENp-4Rs</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1921,7 +1921,7 @@
         <v>Jason Derulo - Whatcha Say (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B41" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=jsFekVlEaSA</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1959,7 +1959,7 @@
         <v>Bebe Rexha - New Religion (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B42" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=nfDKQ09bY_w</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -1997,7 +1997,7 @@
         <v>Bebe Rexha - I'm Good (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B43" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=eqceDkaK3PU</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2035,7 +2035,7 @@
         <v>Bebe Rexha - In The Name Of Love (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B44" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=UlP9zTLUeLw</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2073,7 +2073,7 @@
         <v>Strange Surreal AI - In Here - Kelly Boesch | 4K</v>
       </c>
       <c r="B45" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=QCNwFDTkfYU</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2111,7 +2111,7 @@
         <v>The Cranberries - Scenes From 'Linger' (The Only Color Reel)</v>
       </c>
       <c r="B46" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=5-peG8H-lqE</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2149,7 +2149,7 @@
         <v>Jordana Bryant - Too Little Too Late (Official Lyric Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=P26-NjdBmbU</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2187,7 +2187,7 @@
         <v>Grace Enger - "Running Back To You" (Official Music Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=BON1BSWLntE</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2225,7 +2225,7 @@
         <v>The Offspring - Gone Away | Live at BeachLife Festival 2026</v>
       </c>
       <c r="B49" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=UTw106Ivz8o</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2263,7 +2263,7 @@
         <v>Lola Young – From Down Here (From The Pool)</v>
       </c>
       <c r="B50" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=YFhpMpONGUY</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2301,7 +2301,7 @@
         <v>CAIN - Living Water (Music Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=WrsXAfnTAdA</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2339,7 +2339,7 @@
         <v>B.B. King &amp; Eric Clapton - Riding With The King (Official Music Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=L7Ls8ceHxhc</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2377,7 +2377,7 @@
         <v>Blu DeTiger - Whisper (Official Music Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=OfcBfPnskG4</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2415,7 +2415,7 @@
         <v>Romeo Santos, Prince Royce - Ay! San Miguel (Official Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=-uvNvVtUidc</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2453,7 +2453,7 @@
         <v>Pink Floyd - Pigs on the Wing (8-Track Version - Official Audio)</v>
       </c>
       <c r="B55" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=WZUKJ90i6Tw</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2491,7 +2491,7 @@
         <v>Holly Humberstone - it’s just White Noise</v>
       </c>
       <c r="B56" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=KeRZtPUjl8g</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2529,7 +2529,7 @@
         <v>Freya Ridings - Mother Of Pearl (Official Video)</v>
       </c>
       <c r="B57" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=So5gx12fCsA</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2567,7 +2567,7 @@
         <v>MUSE - Nightshift Superstar (Official Music Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=p--xk9n1eIM</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2605,7 +2605,7 @@
         <v>Ellie Goulding - Black Prada Dress (Visualiser)</v>
       </c>
       <c r="B59" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=zr9CYpgPueI</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2643,7 +2643,7 @@
         <v>Evanescence - Sanctuary (Official Visualizer)</v>
       </c>
       <c r="B60" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=E64jOWeVfpg</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2681,7 +2681,7 @@
         <v>The Beaches - Perfect 10 (Official Visualizer)</v>
       </c>
       <c r="B61" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=N7TOR_l-CM8</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2719,7 +2719,7 @@
         <v>Bella White - Stuff (Official Music Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=7QZtxsGBTks</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2757,7 +2757,7 @@
         <v>Meduza, Rani - Silence (Official Visualizer)</v>
       </c>
       <c r="B63" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=cIdqz-WMod4</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2795,7 +2795,7 @@
         <v>CAIN - Living Water (Lyric Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=Hv-8CM5NIPM</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2833,7 +2833,7 @@
         <v>Fitz and the Tantrums - Greenlight (Official Visualizer)</v>
       </c>
       <c r="B65" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=Zx-ZPBbcA58</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2871,7 +2871,7 @@
         <v>Jeremy Camp - Reflector (Official Music Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=SR-4q1yiYNA</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2909,7 +2909,7 @@
         <v>Alesso, OneRepublic - In Your Eyes (Visualizer)</v>
       </c>
       <c r="B67" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=bS9C1ipyMy8</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2947,7 +2947,7 @@
         <v>Malcolm Todd - Free.99 (Official Visualizer)</v>
       </c>
       <c r="B68" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=wBBQptUsOhw</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -2985,7 +2985,7 @@
         <v>Isabel LaRosa - Every Life (Visualizer)</v>
       </c>
       <c r="B69" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=tIQDAtwNAY4</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3023,7 +3023,7 @@
         <v>Wyatt Flores - Half The Man (Official Music Video)</v>
       </c>
       <c r="B70" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=2ChzcWHryFM</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3061,7 +3061,7 @@
         <v>Mckenna Grace - Ugly and Rotten (Official Music Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=4yXFVgy7laM</v>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3099,7 +3099,7 @@
         <v>Robert Grace - If You Were Gone ft. Bob Grace (OFFICIAL LYRIC VIDEO)</v>
       </c>
       <c r="B72" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=fbpQjMi3Hco</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3137,7 +3137,7 @@
         <v>Boyzone - No Matter What (Live)</v>
       </c>
       <c r="B73" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=CEy96_jHw-Q</v>
@@ -3149,7 +3149,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3175,7 +3175,7 @@
         <v>Florrie - The Times (Official Video)</v>
       </c>
       <c r="B74" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=6yBlNUaW7r4</v>
@@ -3187,7 +3187,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3213,7 +3213,7 @@
         <v>Madonna - Love Sensation (Official Visualizer)</v>
       </c>
       <c r="B75" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=88fD-UtG_yo</v>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3251,7 +3251,7 @@
         <v>DMA'S - Hurracane (Official Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=-zTB57LiXPk</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3289,7 +3289,7 @@
         <v>Lainey Wilson and John Mayer - Phone, Keys, Wallet (Official Audio)</v>
       </c>
       <c r="B77" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=JzW6RnzeF9A</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -3327,7 +3327,7 @@
         <v>ROLE MODEL - High Hopes 3000 (Official Music Video)</v>
       </c>
       <c r="B78" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=D_KTG0BzRiI</v>
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -3365,7 +3365,7 @@
         <v>Shawn Mendes - Treat You Better (Live from New York)</v>
       </c>
       <c r="B79" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=29bfaHc1XiY</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -3403,7 +3403,7 @@
         <v>SIENNA SPIRO - The Visitor (Official Music Video)</v>
       </c>
       <c r="B80" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=LiYb4WGbp5Y</v>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -3441,7 +3441,7 @@
         <v>Just Slide Official Music Video | Kelly Boesch | 4K</v>
       </c>
       <c r="B81" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=lC14fuU8aPc</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -3479,7 +3479,7 @@
         <v>Europe - The Cult of Ignorance (Official Video)</v>
       </c>
       <c r="B82" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=p-IOsjOJpnA</v>
@@ -3491,7 +3491,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -3517,7 +3517,7 @@
         <v>Air Supply - Sweet Dreams (Official Lyric Video)</v>
       </c>
       <c r="B83" t="str">
-        <v>5 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=axiK2vYjXio</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>5 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -3555,7 +3555,7 @@
         <v>Julia Cole - Treat Me Like Dirt (Official Lyric Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=TS2Mgp5F0cs</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -3593,7 +3593,7 @@
         <v>Allen Stone - A Fathers Song - Placeholder Sessions</v>
       </c>
       <c r="B85" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=JPetpt4QMPE</v>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -3631,7 +3631,7 @@
         <v>Morgan Wallen - Don't We (Live From Tuscaloosa)</v>
       </c>
       <c r="B86" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=qhmWM3uXPAU</v>
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -3669,7 +3669,7 @@
         <v>Billy Idol - John Wayne feat. Alison Mosshart (Official Music Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=47LNk7oiTVI</v>
@@ -3681,7 +3681,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -3707,7 +3707,7 @@
         <v>'It's Unusual' Official Music Video - Kelly Boesch | 4K</v>
       </c>
       <c r="B88" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=Ru3fB2l1RSo</v>
@@ -3719,7 +3719,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -3745,7 +3745,7 @@
         <v>Icona Pop - Butterfly Feelings (Official Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=AMW1Zq9RbIU</v>
@@ -3757,7 +3757,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -3783,7 +3783,7 @@
         <v>Hippo Campus - South</v>
       </c>
       <c r="B90" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=FYOmFfV7Ojo</v>
@@ -3795,7 +3795,7 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -3821,7 +3821,7 @@
         <v>elijah woods - Old (Treehouse Sessions)</v>
       </c>
       <c r="B91" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=yDlkPdR_6zM</v>
@@ -3833,7 +3833,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -3859,7 +3859,7 @@
         <v>Nothing But Thieves - Evolution (Official Video)</v>
       </c>
       <c r="B92" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=hmjfuuuRRYU</v>
@@ -3871,7 +3871,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -3897,7 +3897,7 @@
         <v>Ariana Grande - hate that i made you love me (official music video)</v>
       </c>
       <c r="B93" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=82-jTNka3uc</v>
@@ -3909,7 +3909,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -3935,7 +3935,7 @@
         <v>LAUREL - Fire Breather</v>
       </c>
       <c r="B94" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=rtyavLIJjy0</v>
@@ -3947,7 +3947,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -3973,7 +3973,7 @@
         <v>The Warning - Ego (Performance Video)</v>
       </c>
       <c r="B95" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C95" t="str">
         <v>https://www.youtube.com/watch?v=7PApWObImjo</v>
@@ -3985,7 +3985,7 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -4011,7 +4011,7 @@
         <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (feat. Gabito Ballesteros) [Official Lyric Video]</v>
       </c>
       <c r="B96" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C96" t="str">
         <v>https://www.youtube.com/watch?v=vruZSAYJBe4</v>
@@ -4023,7 +4023,7 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -4049,7 +4049,7 @@
         <v>Armin van Buuren - Equanimity (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B97" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=k93t10R-Qrg</v>
@@ -4061,7 +4061,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -4087,7 +4087,7 @@
         <v>“I Didn’t Know What Time It Was” - Andrew Bird Jazz Trio (Live from The Green Mill)</v>
       </c>
       <c r="B98" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=XyRgdfXo2nI</v>
@@ -4099,7 +4099,7 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -4125,7 +4125,7 @@
         <v>Danny Gokey - God's Not (Official Music Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C99" t="str">
         <v>https://www.youtube.com/watch?v=oGpKqX6ftcU</v>
@@ -4137,7 +4137,7 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
@@ -4163,7 +4163,7 @@
         <v>Armik - Brisas (2026 Remaster/Remix) (Exciting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B100" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=51Zu2iU2z2Q</v>
@@ -4175,7 +4175,7 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -4201,7 +4201,7 @@
         <v>Holly Humberstone - Lucy (Free People Sessions)</v>
       </c>
       <c r="B101" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=c1GR2TTs9W8</v>
@@ -4213,7 +4213,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G101" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-06-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-06-week02/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Jason Derulo - The Other Side (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B2" t="str">
-        <v>23h ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=ym-h0EIlL3A</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>23h ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,7 +477,7 @@
         <v>Stephen Sanchez - Be More (Live at Capital's Summertime Ball 2026) | Capital</v>
       </c>
       <c r="B3" t="str">
-        <v>23h ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=bIwcNmu-rAg</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>23h ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,7 +515,7 @@
         <v>Jason Derulo - Take You Dancing (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B4" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=oLzj8E8fHRQ</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>Sekou - Someone Like You (Adele Cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B5" t="str">
-        <v>23h ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=YIy2g4enMiY</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>23h ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,7 +591,7 @@
         <v>Sienna Spiro - He's Not My Baby, I'm His (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B6" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=NhuPT6MR2XU</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,7 +629,7 @@
         <v>DEEP PURPLE - DIABLO (Official Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=Z4RpBEg5uis</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>Reba McEntire - You Never Gave Up On Me</v>
       </c>
       <c r="B8" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=AUCRUStLmJM</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,7 +705,7 @@
         <v>elijah woods - Wonder (Official Lyric Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=sDDbD4R-xD4</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -743,7 +743,7 @@
         <v>XG - Flowers (Sweet Female Attitude Cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B10" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=MxJQoyKh8TQ</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -781,7 +781,7 @@
         <v>Niall Horan - Nice To Meet Ya (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B11" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=-UIkkGxMQG8</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -819,7 +819,7 @@
         <v>Niall Horan - Steal My Girl (One Direction cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B12" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=b_uO5ROpk_0</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -857,7 +857,7 @@
         <v>Niall Horan - Dinner Party (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B13" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=hSJfAFpdllk</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -895,7 +895,7 @@
         <v>Niall Horan - Slow Hands (Live at Capital's Summertime Ball 2026) | Capital</v>
       </c>
       <c r="B14" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=vdMK2DvnWJI</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -933,7 +933,7 @@
         <v>RAYE - Joy (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B15" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=5gvhRAGaOUo</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,7 +971,7 @@
         <v>Myles Smith - Stargazing (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B16" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=2AIMnAPxqfw</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1009,7 +1009,7 @@
         <v>Lola Young - From Down Here (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B17" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=UD7HkkAbnVA</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1047,7 +1047,7 @@
         <v>XG - Hypnotize (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B18" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=c5u3ur4vLo0</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1085,7 +1085,7 @@
         <v>Sienna Spiro - The Visitor (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B19" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=MibVDrnrQ10</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,7 +1123,7 @@
         <v>Sienna Spiro - Die On This Hill (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B20" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=UhWumamExiI</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1161,7 +1161,7 @@
         <v>RAYE - Where Is My Husband? (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B21" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=Z_HR2ZYY1VA</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1199,7 +1199,7 @@
         <v>RAYE - Escapism (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B22" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=ywplqaIeHeQ</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1237,7 +1237,7 @@
         <v>Take That - Never Forget (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B23" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=9S61JkOZLe8</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1275,7 +1275,7 @@
         <v>Robyn - Dancing On My Own (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B24" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=_4SfgNPngbo</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1313,7 +1313,7 @@
         <v>Take That - Patience (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B25" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=_I9qIxmrDuI</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1351,7 +1351,7 @@
         <v>Mis-Teeq - Full Set (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B26" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=5AyQM_coDb8</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1389,7 +1389,7 @@
         <v>Myles Smith - Stay (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B27" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=2ekY7Cb7CKs</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1427,7 +1427,7 @@
         <v>Take That - Rule The World (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B28" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=0nc-qdhh6eU</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1465,7 +1465,7 @@
         <v>Sienna Spiro - Material Lover (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B29" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=dZjAtTc9DBQ</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1503,7 +1503,7 @@
         <v>Take That - Shine (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B30" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=T6TmxqOGIf0</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1541,7 +1541,7 @@
         <v>MEEK - Dracula (Tame Impala Cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B31" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=4jnM--XhsC0</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1579,7 +1579,7 @@
         <v>MEEK - Fabulous (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B32" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=kKSlraqNMhI</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1617,7 +1617,7 @@
         <v>Lola Young - Messy (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B33" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=cUvsaKkjHYQ</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1655,7 +1655,7 @@
         <v>Stephen Sanchez - Until I Found You (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B34" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=oKKNK0OCpQk</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1693,7 +1693,7 @@
         <v>Lola Young - D£aler (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B35" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=ymvr4RCN-WE</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1731,7 +1731,7 @@
         <v>Lola Young - One Thing (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B36" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=nhL2l4HCiRg</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1769,7 +1769,7 @@
         <v>Bebe Rexha - Sad Girls (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B37" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=e0PkSQNMcGs</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1807,7 +1807,7 @@
         <v>Robyn - Dopamine (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B38" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=-7mPIus0U5Y</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1845,7 +1845,7 @@
         <v>Jason Derulo - Ridin' Solo (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B39" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=G6jhovaAz3U</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1883,7 +1883,7 @@
         <v>Jason Derulo - Trumpets (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B40" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=QkCKENp-4Rs</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1921,7 +1921,7 @@
         <v>Jason Derulo - Whatcha Say (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B41" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=jsFekVlEaSA</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1959,7 +1959,7 @@
         <v>Bebe Rexha - New Religion (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B42" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=nfDKQ09bY_w</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -1997,7 +1997,7 @@
         <v>Bebe Rexha - I'm Good (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B43" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=eqceDkaK3PU</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2035,7 +2035,7 @@
         <v>Bebe Rexha - In The Name Of Love (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B44" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=UlP9zTLUeLw</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2073,7 +2073,7 @@
         <v>Strange Surreal AI - In Here - Kelly Boesch | 4K</v>
       </c>
       <c r="B45" t="str">
-        <v>3d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=QCNwFDTkfYU</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>3d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2111,7 +2111,7 @@
         <v>The Cranberries - Scenes From 'Linger' (The Only Color Reel)</v>
       </c>
       <c r="B46" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=5-peG8H-lqE</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2149,7 +2149,7 @@
         <v>Jordana Bryant - Too Little Too Late (Official Lyric Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=P26-NjdBmbU</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2187,7 +2187,7 @@
         <v>Grace Enger - "Running Back To You" (Official Music Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=BON1BSWLntE</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2225,7 +2225,7 @@
         <v>The Offspring - Gone Away | Live at BeachLife Festival 2026</v>
       </c>
       <c r="B49" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=UTw106Ivz8o</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2263,7 +2263,7 @@
         <v>Lola Young – From Down Here (From The Pool)</v>
       </c>
       <c r="B50" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=YFhpMpONGUY</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2301,7 +2301,7 @@
         <v>CAIN - Living Water (Music Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=WrsXAfnTAdA</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2339,7 +2339,7 @@
         <v>B.B. King &amp; Eric Clapton - Riding With The King (Official Music Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=L7Ls8ceHxhc</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2377,7 +2377,7 @@
         <v>Blu DeTiger - Whisper (Official Music Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=OfcBfPnskG4</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2415,7 +2415,7 @@
         <v>Romeo Santos, Prince Royce - Ay! San Miguel (Official Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=-uvNvVtUidc</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2453,7 +2453,7 @@
         <v>Pink Floyd - Pigs on the Wing (8-Track Version - Official Audio)</v>
       </c>
       <c r="B55" t="str">
-        <v>3d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=WZUKJ90i6Tw</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>3d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2491,7 +2491,7 @@
         <v>Holly Humberstone - it’s just White Noise</v>
       </c>
       <c r="B56" t="str">
-        <v>3d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=KeRZtPUjl8g</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>3d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2529,7 +2529,7 @@
         <v>Freya Ridings - Mother Of Pearl (Official Video)</v>
       </c>
       <c r="B57" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=So5gx12fCsA</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2567,7 +2567,7 @@
         <v>MUSE - Nightshift Superstar (Official Music Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=p--xk9n1eIM</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2605,7 +2605,7 @@
         <v>Ellie Goulding - Black Prada Dress (Visualiser)</v>
       </c>
       <c r="B59" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=zr9CYpgPueI</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2643,7 +2643,7 @@
         <v>Evanescence - Sanctuary (Official Visualizer)</v>
       </c>
       <c r="B60" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=E64jOWeVfpg</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2681,7 +2681,7 @@
         <v>The Beaches - Perfect 10 (Official Visualizer)</v>
       </c>
       <c r="B61" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=N7TOR_l-CM8</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2719,7 +2719,7 @@
         <v>Bella White - Stuff (Official Music Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=7QZtxsGBTks</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2757,7 +2757,7 @@
         <v>Meduza, Rani - Silence (Official Visualizer)</v>
       </c>
       <c r="B63" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=cIdqz-WMod4</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2795,7 +2795,7 @@
         <v>CAIN - Living Water (Lyric Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=Hv-8CM5NIPM</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2833,7 +2833,7 @@
         <v>Fitz and the Tantrums - Greenlight (Official Visualizer)</v>
       </c>
       <c r="B65" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=Zx-ZPBbcA58</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2871,7 +2871,7 @@
         <v>Jeremy Camp - Reflector (Official Music Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=SR-4q1yiYNA</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2909,7 +2909,7 @@
         <v>Alesso, OneRepublic - In Your Eyes (Visualizer)</v>
       </c>
       <c r="B67" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=bS9C1ipyMy8</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2947,7 +2947,7 @@
         <v>Malcolm Todd - Free.99 (Official Visualizer)</v>
       </c>
       <c r="B68" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=wBBQptUsOhw</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -2985,7 +2985,7 @@
         <v>Isabel LaRosa - Every Life (Visualizer)</v>
       </c>
       <c r="B69" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=tIQDAtwNAY4</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3023,7 +3023,7 @@
         <v>Wyatt Flores - Half The Man (Official Music Video)</v>
       </c>
       <c r="B70" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=2ChzcWHryFM</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3061,7 +3061,7 @@
         <v>Mckenna Grace - Ugly and Rotten (Official Music Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=4yXFVgy7laM</v>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3099,7 +3099,7 @@
         <v>Robert Grace - If You Were Gone ft. Bob Grace (OFFICIAL LYRIC VIDEO)</v>
       </c>
       <c r="B72" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=fbpQjMi3Hco</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3137,7 +3137,7 @@
         <v>Boyzone - No Matter What (Live)</v>
       </c>
       <c r="B73" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=CEy96_jHw-Q</v>
@@ -3149,7 +3149,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3175,7 +3175,7 @@
         <v>Florrie - The Times (Official Video)</v>
       </c>
       <c r="B74" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=6yBlNUaW7r4</v>
@@ -3187,7 +3187,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3213,7 +3213,7 @@
         <v>Madonna - Love Sensation (Official Visualizer)</v>
       </c>
       <c r="B75" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=88fD-UtG_yo</v>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3251,7 +3251,7 @@
         <v>DMA'S - Hurracane (Official Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=-zTB57LiXPk</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3289,7 +3289,7 @@
         <v>Lainey Wilson and John Mayer - Phone, Keys, Wallet (Official Audio)</v>
       </c>
       <c r="B77" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=JzW6RnzeF9A</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -3327,7 +3327,7 @@
         <v>ROLE MODEL - High Hopes 3000 (Official Music Video)</v>
       </c>
       <c r="B78" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=D_KTG0BzRiI</v>
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -3365,7 +3365,7 @@
         <v>Shawn Mendes - Treat You Better (Live from New York)</v>
       </c>
       <c r="B79" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=29bfaHc1XiY</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -3403,7 +3403,7 @@
         <v>SIENNA SPIRO - The Visitor (Official Music Video)</v>
       </c>
       <c r="B80" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=LiYb4WGbp5Y</v>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -3441,7 +3441,7 @@
         <v>Just Slide Official Music Video | Kelly Boesch | 4K</v>
       </c>
       <c r="B81" t="str">
-        <v>5d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=lC14fuU8aPc</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>5d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -3479,7 +3479,7 @@
         <v>Europe - The Cult of Ignorance (Official Video)</v>
       </c>
       <c r="B82" t="str">
-        <v>5d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=p-IOsjOJpnA</v>
@@ -3491,7 +3491,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>5d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -3517,7 +3517,7 @@
         <v>Air Supply - Sweet Dreams (Official Lyric Video)</v>
       </c>
       <c r="B83" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=axiK2vYjXio</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -3555,7 +3555,7 @@
         <v>Julia Cole - Treat Me Like Dirt (Official Lyric Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=TS2Mgp5F0cs</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -3593,7 +3593,7 @@
         <v>Allen Stone - A Fathers Song - Placeholder Sessions</v>
       </c>
       <c r="B85" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=JPetpt4QMPE</v>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -3631,7 +3631,7 @@
         <v>Morgan Wallen - Don't We (Live From Tuscaloosa)</v>
       </c>
       <c r="B86" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=qhmWM3uXPAU</v>
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -3669,7 +3669,7 @@
         <v>Billy Idol - John Wayne feat. Alison Mosshart (Official Music Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=47LNk7oiTVI</v>
@@ -3681,7 +3681,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -3707,7 +3707,7 @@
         <v>'It's Unusual' Official Music Video - Kelly Boesch | 4K</v>
       </c>
       <c r="B88" t="str">
-        <v>10d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=Ru3fB2l1RSo</v>
@@ -3719,7 +3719,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>10d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -3745,7 +3745,7 @@
         <v>Icona Pop - Butterfly Feelings (Official Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=AMW1Zq9RbIU</v>
@@ -3757,7 +3757,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -3783,7 +3783,7 @@
         <v>Hippo Campus - South</v>
       </c>
       <c r="B90" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=FYOmFfV7Ojo</v>
@@ -3795,7 +3795,7 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -3821,7 +3821,7 @@
         <v>elijah woods - Old (Treehouse Sessions)</v>
       </c>
       <c r="B91" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=yDlkPdR_6zM</v>
@@ -3833,7 +3833,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -3859,7 +3859,7 @@
         <v>Nothing But Thieves - Evolution (Official Video)</v>
       </c>
       <c r="B92" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=hmjfuuuRRYU</v>
@@ -3871,7 +3871,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -3897,7 +3897,7 @@
         <v>Ariana Grande - hate that i made you love me (official music video)</v>
       </c>
       <c r="B93" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=82-jTNka3uc</v>
@@ -3909,7 +3909,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -3935,7 +3935,7 @@
         <v>LAUREL - Fire Breather</v>
       </c>
       <c r="B94" t="str">
-        <v>7d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=rtyavLIJjy0</v>
@@ -3947,7 +3947,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>7d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -3973,7 +3973,7 @@
         <v>The Warning - Ego (Performance Video)</v>
       </c>
       <c r="B95" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C95" t="str">
         <v>https://www.youtube.com/watch?v=7PApWObImjo</v>
@@ -3985,7 +3985,7 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -4011,7 +4011,7 @@
         <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (feat. Gabito Ballesteros) [Official Lyric Video]</v>
       </c>
       <c r="B96" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C96" t="str">
         <v>https://www.youtube.com/watch?v=vruZSAYJBe4</v>
@@ -4023,7 +4023,7 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -4049,7 +4049,7 @@
         <v>Armin van Buuren - Equanimity (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B97" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=k93t10R-Qrg</v>
@@ -4061,7 +4061,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -4087,7 +4087,7 @@
         <v>“I Didn’t Know What Time It Was” - Andrew Bird Jazz Trio (Live from The Green Mill)</v>
       </c>
       <c r="B98" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=XyRgdfXo2nI</v>
@@ -4099,7 +4099,7 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -4125,7 +4125,7 @@
         <v>Danny Gokey - God's Not (Official Music Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C99" t="str">
         <v>https://www.youtube.com/watch?v=oGpKqX6ftcU</v>
@@ -4137,7 +4137,7 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
@@ -4163,7 +4163,7 @@
         <v>Armik - Brisas (2026 Remaster/Remix) (Exciting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B100" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=51Zu2iU2z2Q</v>
@@ -4175,7 +4175,7 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -4201,7 +4201,7 @@
         <v>Holly Humberstone - Lucy (Free People Sessions)</v>
       </c>
       <c r="B101" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=c1GR2TTs9W8</v>
@@ -4213,7 +4213,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G101" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-06-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-06-week02/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Jason Derulo - The Other Side (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B2" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=ym-h0EIlL3A</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,7 +477,7 @@
         <v>Stephen Sanchez - Be More (Live at Capital's Summertime Ball 2026) | Capital</v>
       </c>
       <c r="B3" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=bIwcNmu-rAg</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,7 +515,7 @@
         <v>Jason Derulo - Take You Dancing (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B4" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=oLzj8E8fHRQ</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>Sekou - Someone Like You (Adele Cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B5" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=YIy2g4enMiY</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,7 +591,7 @@
         <v>Sienna Spiro - He's Not My Baby, I'm His (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B6" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=NhuPT6MR2XU</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,7 +629,7 @@
         <v>DEEP PURPLE - DIABLO (Official Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=Z4RpBEg5uis</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>Reba McEntire - You Never Gave Up On Me</v>
       </c>
       <c r="B8" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=AUCRUStLmJM</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,7 +705,7 @@
         <v>elijah woods - Wonder (Official Lyric Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=sDDbD4R-xD4</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -743,7 +743,7 @@
         <v>XG - Flowers (Sweet Female Attitude Cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B10" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=MxJQoyKh8TQ</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -781,7 +781,7 @@
         <v>Niall Horan - Nice To Meet Ya (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B11" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=-UIkkGxMQG8</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -819,7 +819,7 @@
         <v>Niall Horan - Steal My Girl (One Direction cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B12" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=b_uO5ROpk_0</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -857,7 +857,7 @@
         <v>Niall Horan - Dinner Party (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B13" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=hSJfAFpdllk</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -895,7 +895,7 @@
         <v>Niall Horan - Slow Hands (Live at Capital's Summertime Ball 2026) | Capital</v>
       </c>
       <c r="B14" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=vdMK2DvnWJI</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -933,7 +933,7 @@
         <v>RAYE - Joy (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B15" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=5gvhRAGaOUo</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,7 +971,7 @@
         <v>Myles Smith - Stargazing (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B16" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=2AIMnAPxqfw</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1009,7 +1009,7 @@
         <v>Lola Young - From Down Here (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B17" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=UD7HkkAbnVA</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1047,7 +1047,7 @@
         <v>XG - Hypnotize (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B18" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=c5u3ur4vLo0</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1085,7 +1085,7 @@
         <v>Sienna Spiro - The Visitor (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B19" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=MibVDrnrQ10</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,7 +1123,7 @@
         <v>Sienna Spiro - Die On This Hill (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B20" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=UhWumamExiI</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1161,7 +1161,7 @@
         <v>RAYE - Where Is My Husband? (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B21" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=Z_HR2ZYY1VA</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1199,7 +1199,7 @@
         <v>RAYE - Escapism (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B22" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=ywplqaIeHeQ</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1237,7 +1237,7 @@
         <v>Take That - Never Forget (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B23" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=9S61JkOZLe8</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1275,7 +1275,7 @@
         <v>Robyn - Dancing On My Own (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B24" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=_4SfgNPngbo</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1313,7 +1313,7 @@
         <v>Take That - Patience (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B25" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=_I9qIxmrDuI</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1351,7 +1351,7 @@
         <v>Mis-Teeq - Full Set (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B26" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=5AyQM_coDb8</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1389,7 +1389,7 @@
         <v>Myles Smith - Stay (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B27" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=2ekY7Cb7CKs</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1427,7 +1427,7 @@
         <v>Take That - Rule The World (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B28" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=0nc-qdhh6eU</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1465,7 +1465,7 @@
         <v>Sienna Spiro - Material Lover (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B29" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=dZjAtTc9DBQ</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1503,7 +1503,7 @@
         <v>Take That - Shine (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B30" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=T6TmxqOGIf0</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1541,7 +1541,7 @@
         <v>MEEK - Dracula (Tame Impala Cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B31" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=4jnM--XhsC0</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1579,7 +1579,7 @@
         <v>MEEK - Fabulous (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B32" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=kKSlraqNMhI</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1617,7 +1617,7 @@
         <v>Lola Young - Messy (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B33" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=cUvsaKkjHYQ</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1655,7 +1655,7 @@
         <v>Stephen Sanchez - Until I Found You (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B34" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=oKKNK0OCpQk</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1693,7 +1693,7 @@
         <v>Lola Young - D£aler (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B35" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=ymvr4RCN-WE</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1731,7 +1731,7 @@
         <v>Lola Young - One Thing (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B36" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=nhL2l4HCiRg</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1769,7 +1769,7 @@
         <v>Bebe Rexha - Sad Girls (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B37" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=e0PkSQNMcGs</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1807,7 +1807,7 @@
         <v>Robyn - Dopamine (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B38" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=-7mPIus0U5Y</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1845,7 +1845,7 @@
         <v>Jason Derulo - Ridin' Solo (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B39" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=G6jhovaAz3U</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1883,7 +1883,7 @@
         <v>Jason Derulo - Trumpets (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B40" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=QkCKENp-4Rs</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1921,7 +1921,7 @@
         <v>Jason Derulo - Whatcha Say (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B41" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=jsFekVlEaSA</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1959,7 +1959,7 @@
         <v>Bebe Rexha - New Religion (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B42" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=nfDKQ09bY_w</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -1997,7 +1997,7 @@
         <v>Bebe Rexha - I'm Good (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B43" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=eqceDkaK3PU</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2035,7 +2035,7 @@
         <v>Bebe Rexha - In The Name Of Love (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B44" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=UlP9zTLUeLw</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2073,7 +2073,7 @@
         <v>Strange Surreal AI - In Here - Kelly Boesch | 4K</v>
       </c>
       <c r="B45" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=QCNwFDTkfYU</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2111,7 +2111,7 @@
         <v>The Cranberries - Scenes From 'Linger' (The Only Color Reel)</v>
       </c>
       <c r="B46" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=5-peG8H-lqE</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2149,7 +2149,7 @@
         <v>Jordana Bryant - Too Little Too Late (Official Lyric Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=P26-NjdBmbU</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2187,7 +2187,7 @@
         <v>Grace Enger - "Running Back To You" (Official Music Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=BON1BSWLntE</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2225,7 +2225,7 @@
         <v>The Offspring - Gone Away | Live at BeachLife Festival 2026</v>
       </c>
       <c r="B49" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=UTw106Ivz8o</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2263,7 +2263,7 @@
         <v>Lola Young – From Down Here (From The Pool)</v>
       </c>
       <c r="B50" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=YFhpMpONGUY</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2301,7 +2301,7 @@
         <v>CAIN - Living Water (Music Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=WrsXAfnTAdA</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2339,7 +2339,7 @@
         <v>B.B. King &amp; Eric Clapton - Riding With The King (Official Music Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=L7Ls8ceHxhc</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2377,7 +2377,7 @@
         <v>Blu DeTiger - Whisper (Official Music Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=OfcBfPnskG4</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2415,7 +2415,7 @@
         <v>Romeo Santos, Prince Royce - Ay! San Miguel (Official Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=-uvNvVtUidc</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2453,7 +2453,7 @@
         <v>Pink Floyd - Pigs on the Wing (8-Track Version - Official Audio)</v>
       </c>
       <c r="B55" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=WZUKJ90i6Tw</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2491,7 +2491,7 @@
         <v>Holly Humberstone - it’s just White Noise</v>
       </c>
       <c r="B56" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=KeRZtPUjl8g</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2529,7 +2529,7 @@
         <v>Freya Ridings - Mother Of Pearl (Official Video)</v>
       </c>
       <c r="B57" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=So5gx12fCsA</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2567,7 +2567,7 @@
         <v>MUSE - Nightshift Superstar (Official Music Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=p--xk9n1eIM</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2605,7 +2605,7 @@
         <v>Ellie Goulding - Black Prada Dress (Visualiser)</v>
       </c>
       <c r="B59" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=zr9CYpgPueI</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2643,7 +2643,7 @@
         <v>Evanescence - Sanctuary (Official Visualizer)</v>
       </c>
       <c r="B60" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=E64jOWeVfpg</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2681,7 +2681,7 @@
         <v>The Beaches - Perfect 10 (Official Visualizer)</v>
       </c>
       <c r="B61" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=N7TOR_l-CM8</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2719,7 +2719,7 @@
         <v>Bella White - Stuff (Official Music Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=7QZtxsGBTks</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2757,7 +2757,7 @@
         <v>Meduza, Rani - Silence (Official Visualizer)</v>
       </c>
       <c r="B63" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=cIdqz-WMod4</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2795,7 +2795,7 @@
         <v>CAIN - Living Water (Lyric Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=Hv-8CM5NIPM</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2833,7 +2833,7 @@
         <v>Fitz and the Tantrums - Greenlight (Official Visualizer)</v>
       </c>
       <c r="B65" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=Zx-ZPBbcA58</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2871,7 +2871,7 @@
         <v>Jeremy Camp - Reflector (Official Music Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=SR-4q1yiYNA</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2909,7 +2909,7 @@
         <v>Alesso, OneRepublic - In Your Eyes (Visualizer)</v>
       </c>
       <c r="B67" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=bS9C1ipyMy8</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2947,7 +2947,7 @@
         <v>Malcolm Todd - Free.99 (Official Visualizer)</v>
       </c>
       <c r="B68" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=wBBQptUsOhw</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -2985,7 +2985,7 @@
         <v>Isabel LaRosa - Every Life (Visualizer)</v>
       </c>
       <c r="B69" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=tIQDAtwNAY4</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3023,7 +3023,7 @@
         <v>Wyatt Flores - Half The Man (Official Music Video)</v>
       </c>
       <c r="B70" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=2ChzcWHryFM</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3061,7 +3061,7 @@
         <v>Mckenna Grace - Ugly and Rotten (Official Music Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=4yXFVgy7laM</v>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3099,7 +3099,7 @@
         <v>Robert Grace - If You Were Gone ft. Bob Grace (OFFICIAL LYRIC VIDEO)</v>
       </c>
       <c r="B72" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=fbpQjMi3Hco</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3137,7 +3137,7 @@
         <v>Boyzone - No Matter What (Live)</v>
       </c>
       <c r="B73" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=CEy96_jHw-Q</v>
@@ -3149,7 +3149,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3175,7 +3175,7 @@
         <v>Florrie - The Times (Official Video)</v>
       </c>
       <c r="B74" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=6yBlNUaW7r4</v>
@@ -3187,7 +3187,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3213,7 +3213,7 @@
         <v>Madonna - Love Sensation (Official Visualizer)</v>
       </c>
       <c r="B75" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=88fD-UtG_yo</v>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3251,7 +3251,7 @@
         <v>DMA'S - Hurracane (Official Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=-zTB57LiXPk</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3289,7 +3289,7 @@
         <v>Lainey Wilson and John Mayer - Phone, Keys, Wallet (Official Audio)</v>
       </c>
       <c r="B77" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=JzW6RnzeF9A</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -3327,7 +3327,7 @@
         <v>ROLE MODEL - High Hopes 3000 (Official Music Video)</v>
       </c>
       <c r="B78" t="str">
-        <v>5 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=D_KTG0BzRiI</v>
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>5 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -3365,7 +3365,7 @@
         <v>Shawn Mendes - Treat You Better (Live from New York)</v>
       </c>
       <c r="B79" t="str">
-        <v>5 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=29bfaHc1XiY</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>5 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -3403,7 +3403,7 @@
         <v>SIENNA SPIRO - The Visitor (Official Music Video)</v>
       </c>
       <c r="B80" t="str">
-        <v>5 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=LiYb4WGbp5Y</v>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>5 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -3441,7 +3441,7 @@
         <v>Just Slide Official Music Video | Kelly Boesch | 4K</v>
       </c>
       <c r="B81" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=lC14fuU8aPc</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -3479,7 +3479,7 @@
         <v>Europe - The Cult of Ignorance (Official Video)</v>
       </c>
       <c r="B82" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=p-IOsjOJpnA</v>
@@ -3491,7 +3491,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -3517,7 +3517,7 @@
         <v>Air Supply - Sweet Dreams (Official Lyric Video)</v>
       </c>
       <c r="B83" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=axiK2vYjXio</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -3555,7 +3555,7 @@
         <v>Julia Cole - Treat Me Like Dirt (Official Lyric Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=TS2Mgp5F0cs</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -3593,7 +3593,7 @@
         <v>Allen Stone - A Fathers Song - Placeholder Sessions</v>
       </c>
       <c r="B85" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=JPetpt4QMPE</v>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -3631,7 +3631,7 @@
         <v>Morgan Wallen - Don't We (Live From Tuscaloosa)</v>
       </c>
       <c r="B86" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=qhmWM3uXPAU</v>
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -3669,7 +3669,7 @@
         <v>Billy Idol - John Wayne feat. Alison Mosshart (Official Music Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=47LNk7oiTVI</v>
@@ -3681,7 +3681,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -3707,7 +3707,7 @@
         <v>'It's Unusual' Official Music Video - Kelly Boesch | 4K</v>
       </c>
       <c r="B88" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=Ru3fB2l1RSo</v>
@@ -3719,7 +3719,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -3745,7 +3745,7 @@
         <v>Icona Pop - Butterfly Feelings (Official Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=AMW1Zq9RbIU</v>
@@ -3757,7 +3757,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -3783,7 +3783,7 @@
         <v>Hippo Campus - South</v>
       </c>
       <c r="B90" t="str">
-        <v>7 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=FYOmFfV7Ojo</v>
@@ -3795,7 +3795,7 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>7 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -3821,7 +3821,7 @@
         <v>elijah woods - Old (Treehouse Sessions)</v>
       </c>
       <c r="B91" t="str">
-        <v>7 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=yDlkPdR_6zM</v>
@@ -3833,7 +3833,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>7 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -3859,7 +3859,7 @@
         <v>Nothing But Thieves - Evolution (Official Video)</v>
       </c>
       <c r="B92" t="str">
-        <v>7 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=hmjfuuuRRYU</v>
@@ -3871,7 +3871,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>7 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -3897,7 +3897,7 @@
         <v>Ariana Grande - hate that i made you love me (official music video)</v>
       </c>
       <c r="B93" t="str">
-        <v>7 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=82-jTNka3uc</v>
@@ -3909,7 +3909,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>7 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -3935,7 +3935,7 @@
         <v>LAUREL - Fire Breather</v>
       </c>
       <c r="B94" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=rtyavLIJjy0</v>
@@ -3947,7 +3947,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -3973,7 +3973,7 @@
         <v>The Warning - Ego (Performance Video)</v>
       </c>
       <c r="B95" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C95" t="str">
         <v>https://www.youtube.com/watch?v=7PApWObImjo</v>
@@ -3985,7 +3985,7 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -4011,7 +4011,7 @@
         <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (feat. Gabito Ballesteros) [Official Lyric Video]</v>
       </c>
       <c r="B96" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C96" t="str">
         <v>https://www.youtube.com/watch?v=vruZSAYJBe4</v>
@@ -4023,7 +4023,7 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -4049,7 +4049,7 @@
         <v>Armin van Buuren - Equanimity (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B97" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=k93t10R-Qrg</v>
@@ -4061,7 +4061,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -4087,7 +4087,7 @@
         <v>“I Didn’t Know What Time It Was” - Andrew Bird Jazz Trio (Live from The Green Mill)</v>
       </c>
       <c r="B98" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=XyRgdfXo2nI</v>
@@ -4099,7 +4099,7 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -4125,7 +4125,7 @@
         <v>Danny Gokey - God's Not (Official Music Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C99" t="str">
         <v>https://www.youtube.com/watch?v=oGpKqX6ftcU</v>
@@ -4137,7 +4137,7 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
@@ -4163,7 +4163,7 @@
         <v>Armik - Brisas (2026 Remaster/Remix) (Exciting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B100" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=51Zu2iU2z2Q</v>
@@ -4175,7 +4175,7 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -4201,7 +4201,7 @@
         <v>Holly Humberstone - Lucy (Free People Sessions)</v>
       </c>
       <c r="B101" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=c1GR2TTs9W8</v>
@@ -4213,7 +4213,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G101" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-06-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-06-week02/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Jason Derulo - The Other Side (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B2" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=ym-h0EIlL3A</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,7 +477,7 @@
         <v>Stephen Sanchez - Be More (Live at Capital's Summertime Ball 2026) | Capital</v>
       </c>
       <c r="B3" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=bIwcNmu-rAg</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,7 +515,7 @@
         <v>Jason Derulo - Take You Dancing (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B4" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=oLzj8E8fHRQ</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>Sekou - Someone Like You (Adele Cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B5" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=YIy2g4enMiY</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,7 +591,7 @@
         <v>Sienna Spiro - He's Not My Baby, I'm His (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B6" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=NhuPT6MR2XU</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,7 +629,7 @@
         <v>DEEP PURPLE - DIABLO (Official Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=Z4RpBEg5uis</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>Reba McEntire - You Never Gave Up On Me</v>
       </c>
       <c r="B8" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=AUCRUStLmJM</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,7 +705,7 @@
         <v>elijah woods - Wonder (Official Lyric Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>1d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=sDDbD4R-xD4</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>1d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -743,7 +743,7 @@
         <v>XG - Flowers (Sweet Female Attitude Cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B10" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=MxJQoyKh8TQ</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -781,7 +781,7 @@
         <v>Niall Horan - Nice To Meet Ya (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B11" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=-UIkkGxMQG8</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -819,7 +819,7 @@
         <v>Niall Horan - Steal My Girl (One Direction cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B12" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=b_uO5ROpk_0</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -857,7 +857,7 @@
         <v>Niall Horan - Dinner Party (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B13" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=hSJfAFpdllk</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -895,7 +895,7 @@
         <v>Niall Horan - Slow Hands (Live at Capital's Summertime Ball 2026) | Capital</v>
       </c>
       <c r="B14" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=vdMK2DvnWJI</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -933,7 +933,7 @@
         <v>RAYE - Joy (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B15" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=5gvhRAGaOUo</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,7 +971,7 @@
         <v>Myles Smith - Stargazing (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B16" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=2AIMnAPxqfw</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1009,7 +1009,7 @@
         <v>Lola Young - From Down Here (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B17" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=UD7HkkAbnVA</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1047,7 +1047,7 @@
         <v>XG - Hypnotize (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B18" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=c5u3ur4vLo0</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1085,7 +1085,7 @@
         <v>Sienna Spiro - The Visitor (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B19" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=MibVDrnrQ10</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,7 +1123,7 @@
         <v>Sienna Spiro - Die On This Hill (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B20" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=UhWumamExiI</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1161,7 +1161,7 @@
         <v>RAYE - Where Is My Husband? (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B21" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=Z_HR2ZYY1VA</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1199,7 +1199,7 @@
         <v>RAYE - Escapism (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B22" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=ywplqaIeHeQ</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1237,7 +1237,7 @@
         <v>Take That - Never Forget (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B23" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=9S61JkOZLe8</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1275,7 +1275,7 @@
         <v>Robyn - Dancing On My Own (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B24" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=_4SfgNPngbo</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1313,7 +1313,7 @@
         <v>Take That - Patience (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B25" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=_I9qIxmrDuI</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1351,7 +1351,7 @@
         <v>Mis-Teeq - Full Set (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B26" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=5AyQM_coDb8</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1389,7 +1389,7 @@
         <v>Myles Smith - Stay (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B27" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=2ekY7Cb7CKs</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1427,7 +1427,7 @@
         <v>Take That - Rule The World (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B28" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=0nc-qdhh6eU</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1465,7 +1465,7 @@
         <v>Sienna Spiro - Material Lover (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B29" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=dZjAtTc9DBQ</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1503,7 +1503,7 @@
         <v>Take That - Shine (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B30" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=T6TmxqOGIf0</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1541,7 +1541,7 @@
         <v>MEEK - Dracula (Tame Impala Cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B31" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=4jnM--XhsC0</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1579,7 +1579,7 @@
         <v>MEEK - Fabulous (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B32" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=kKSlraqNMhI</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1617,7 +1617,7 @@
         <v>Lola Young - Messy (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B33" t="str">
-        <v>2d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=cUvsaKkjHYQ</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>2d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1655,7 +1655,7 @@
         <v>Stephen Sanchez - Until I Found You (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B34" t="str">
-        <v>2d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=oKKNK0OCpQk</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>2d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1693,7 +1693,7 @@
         <v>Lola Young - D£aler (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B35" t="str">
-        <v>2d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=ymvr4RCN-WE</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>2d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1731,7 +1731,7 @@
         <v>Lola Young - One Thing (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B36" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=nhL2l4HCiRg</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1769,7 +1769,7 @@
         <v>Bebe Rexha - Sad Girls (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B37" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=e0PkSQNMcGs</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1807,7 +1807,7 @@
         <v>Robyn - Dopamine (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B38" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=-7mPIus0U5Y</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1845,7 +1845,7 @@
         <v>Jason Derulo - Ridin' Solo (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B39" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=G6jhovaAz3U</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1883,7 +1883,7 @@
         <v>Jason Derulo - Trumpets (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B40" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=QkCKENp-4Rs</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1921,7 +1921,7 @@
         <v>Jason Derulo - Whatcha Say (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B41" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=jsFekVlEaSA</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1959,7 +1959,7 @@
         <v>Bebe Rexha - New Religion (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B42" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=nfDKQ09bY_w</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -1997,7 +1997,7 @@
         <v>Bebe Rexha - I'm Good (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B43" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=eqceDkaK3PU</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2035,7 +2035,7 @@
         <v>Bebe Rexha - In The Name Of Love (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B44" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=UlP9zTLUeLw</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2073,7 +2073,7 @@
         <v>Strange Surreal AI - In Here - Kelly Boesch | 4K</v>
       </c>
       <c r="B45" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=QCNwFDTkfYU</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2111,7 +2111,7 @@
         <v>The Cranberries - Scenes From 'Linger' (The Only Color Reel)</v>
       </c>
       <c r="B46" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=5-peG8H-lqE</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2149,7 +2149,7 @@
         <v>Jordana Bryant - Too Little Too Late (Official Lyric Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=P26-NjdBmbU</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2187,7 +2187,7 @@
         <v>Grace Enger - "Running Back To You" (Official Music Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=BON1BSWLntE</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2225,7 +2225,7 @@
         <v>The Offspring - Gone Away | Live at BeachLife Festival 2026</v>
       </c>
       <c r="B49" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=UTw106Ivz8o</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2263,7 +2263,7 @@
         <v>Lola Young – From Down Here (From The Pool)</v>
       </c>
       <c r="B50" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=YFhpMpONGUY</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2301,7 +2301,7 @@
         <v>CAIN - Living Water (Music Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=WrsXAfnTAdA</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2339,7 +2339,7 @@
         <v>B.B. King &amp; Eric Clapton - Riding With The King (Official Music Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=L7Ls8ceHxhc</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2377,7 +2377,7 @@
         <v>Blu DeTiger - Whisper (Official Music Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=OfcBfPnskG4</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2415,7 +2415,7 @@
         <v>Romeo Santos, Prince Royce - Ay! San Miguel (Official Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=-uvNvVtUidc</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2453,7 +2453,7 @@
         <v>Pink Floyd - Pigs on the Wing (8-Track Version - Official Audio)</v>
       </c>
       <c r="B55" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=WZUKJ90i6Tw</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2491,7 +2491,7 @@
         <v>Holly Humberstone - it’s just White Noise</v>
       </c>
       <c r="B56" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=KeRZtPUjl8g</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2529,7 +2529,7 @@
         <v>Freya Ridings - Mother Of Pearl (Official Video)</v>
       </c>
       <c r="B57" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=So5gx12fCsA</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2567,7 +2567,7 @@
         <v>MUSE - Nightshift Superstar (Official Music Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=p--xk9n1eIM</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2605,7 +2605,7 @@
         <v>Ellie Goulding - Black Prada Dress (Visualiser)</v>
       </c>
       <c r="B59" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=zr9CYpgPueI</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2643,7 +2643,7 @@
         <v>Evanescence - Sanctuary (Official Visualizer)</v>
       </c>
       <c r="B60" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=E64jOWeVfpg</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2681,7 +2681,7 @@
         <v>The Beaches - Perfect 10 (Official Visualizer)</v>
       </c>
       <c r="B61" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=N7TOR_l-CM8</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2719,7 +2719,7 @@
         <v>Bella White - Stuff (Official Music Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=7QZtxsGBTks</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2757,7 +2757,7 @@
         <v>Meduza, Rani - Silence (Official Visualizer)</v>
       </c>
       <c r="B63" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=cIdqz-WMod4</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2795,7 +2795,7 @@
         <v>CAIN - Living Water (Lyric Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=Hv-8CM5NIPM</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2833,7 +2833,7 @@
         <v>Fitz and the Tantrums - Greenlight (Official Visualizer)</v>
       </c>
       <c r="B65" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=Zx-ZPBbcA58</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2871,7 +2871,7 @@
         <v>Jeremy Camp - Reflector (Official Music Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=SR-4q1yiYNA</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2909,7 +2909,7 @@
         <v>Alesso, OneRepublic - In Your Eyes (Visualizer)</v>
       </c>
       <c r="B67" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=bS9C1ipyMy8</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2947,7 +2947,7 @@
         <v>Malcolm Todd - Free.99 (Official Visualizer)</v>
       </c>
       <c r="B68" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=wBBQptUsOhw</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -2985,7 +2985,7 @@
         <v>Isabel LaRosa - Every Life (Visualizer)</v>
       </c>
       <c r="B69" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=tIQDAtwNAY4</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3023,7 +3023,7 @@
         <v>Wyatt Flores - Half The Man (Official Music Video)</v>
       </c>
       <c r="B70" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=2ChzcWHryFM</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3061,7 +3061,7 @@
         <v>Mckenna Grace - Ugly and Rotten (Official Music Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=4yXFVgy7laM</v>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3099,7 +3099,7 @@
         <v>Robert Grace - If You Were Gone ft. Bob Grace (OFFICIAL LYRIC VIDEO)</v>
       </c>
       <c r="B72" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=fbpQjMi3Hco</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3137,7 +3137,7 @@
         <v>Boyzone - No Matter What (Live)</v>
       </c>
       <c r="B73" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=CEy96_jHw-Q</v>
@@ -3149,7 +3149,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3175,7 +3175,7 @@
         <v>Florrie - The Times (Official Video)</v>
       </c>
       <c r="B74" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=6yBlNUaW7r4</v>
@@ -3187,7 +3187,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3213,7 +3213,7 @@
         <v>Madonna - Love Sensation (Official Visualizer)</v>
       </c>
       <c r="B75" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=88fD-UtG_yo</v>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3251,7 +3251,7 @@
         <v>DMA'S - Hurracane (Official Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=-zTB57LiXPk</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3289,7 +3289,7 @@
         <v>Lainey Wilson and John Mayer - Phone, Keys, Wallet (Official Audio)</v>
       </c>
       <c r="B77" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=JzW6RnzeF9A</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -3327,7 +3327,7 @@
         <v>ROLE MODEL - High Hopes 3000 (Official Music Video)</v>
       </c>
       <c r="B78" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=D_KTG0BzRiI</v>
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -3365,7 +3365,7 @@
         <v>Shawn Mendes - Treat You Better (Live from New York)</v>
       </c>
       <c r="B79" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=29bfaHc1XiY</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -3403,7 +3403,7 @@
         <v>SIENNA SPIRO - The Visitor (Official Music Video)</v>
       </c>
       <c r="B80" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=LiYb4WGbp5Y</v>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -3441,7 +3441,7 @@
         <v>Just Slide Official Music Video | Kelly Boesch | 4K</v>
       </c>
       <c r="B81" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=lC14fuU8aPc</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -3479,7 +3479,7 @@
         <v>Europe - The Cult of Ignorance (Official Video)</v>
       </c>
       <c r="B82" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=p-IOsjOJpnA</v>
@@ -3491,7 +3491,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -3517,7 +3517,7 @@
         <v>Air Supply - Sweet Dreams (Official Lyric Video)</v>
       </c>
       <c r="B83" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=axiK2vYjXio</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -3555,7 +3555,7 @@
         <v>Julia Cole - Treat Me Like Dirt (Official Lyric Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=TS2Mgp5F0cs</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -3593,7 +3593,7 @@
         <v>Allen Stone - A Fathers Song - Placeholder Sessions</v>
       </c>
       <c r="B85" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=JPetpt4QMPE</v>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -3631,7 +3631,7 @@
         <v>Morgan Wallen - Don't We (Live From Tuscaloosa)</v>
       </c>
       <c r="B86" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=qhmWM3uXPAU</v>
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -3669,7 +3669,7 @@
         <v>Billy Idol - John Wayne feat. Alison Mosshart (Official Music Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=47LNk7oiTVI</v>
@@ -3681,7 +3681,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -3707,7 +3707,7 @@
         <v>'It's Unusual' Official Music Video - Kelly Boesch | 4K</v>
       </c>
       <c r="B88" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=Ru3fB2l1RSo</v>
@@ -3719,7 +3719,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -3745,7 +3745,7 @@
         <v>Icona Pop - Butterfly Feelings (Official Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=AMW1Zq9RbIU</v>
@@ -3757,7 +3757,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -3783,7 +3783,7 @@
         <v>Hippo Campus - South</v>
       </c>
       <c r="B90" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=FYOmFfV7Ojo</v>
@@ -3795,7 +3795,7 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -3821,7 +3821,7 @@
         <v>elijah woods - Old (Treehouse Sessions)</v>
       </c>
       <c r="B91" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=yDlkPdR_6zM</v>
@@ -3833,7 +3833,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -3859,7 +3859,7 @@
         <v>Nothing But Thieves - Evolution (Official Video)</v>
       </c>
       <c r="B92" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=hmjfuuuRRYU</v>
@@ -3871,7 +3871,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -3897,7 +3897,7 @@
         <v>Ariana Grande - hate that i made you love me (official music video)</v>
       </c>
       <c r="B93" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=82-jTNka3uc</v>
@@ -3909,7 +3909,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -3935,7 +3935,7 @@
         <v>LAUREL - Fire Breather</v>
       </c>
       <c r="B94" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=rtyavLIJjy0</v>
@@ -3947,7 +3947,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -3973,7 +3973,7 @@
         <v>The Warning - Ego (Performance Video)</v>
       </c>
       <c r="B95" t="str">
-        <v>9d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C95" t="str">
         <v>https://www.youtube.com/watch?v=7PApWObImjo</v>
@@ -3985,7 +3985,7 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>9d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -4011,7 +4011,7 @@
         <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (feat. Gabito Ballesteros) [Official Lyric Video]</v>
       </c>
       <c r="B96" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C96" t="str">
         <v>https://www.youtube.com/watch?v=vruZSAYJBe4</v>
@@ -4023,7 +4023,7 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -4049,7 +4049,7 @@
         <v>Armin van Buuren - Equanimity (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B97" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=k93t10R-Qrg</v>
@@ -4061,7 +4061,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -4087,7 +4087,7 @@
         <v>“I Didn’t Know What Time It Was” - Andrew Bird Jazz Trio (Live from The Green Mill)</v>
       </c>
       <c r="B98" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=XyRgdfXo2nI</v>
@@ -4099,7 +4099,7 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -4125,7 +4125,7 @@
         <v>Danny Gokey - God's Not (Official Music Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C99" t="str">
         <v>https://www.youtube.com/watch?v=oGpKqX6ftcU</v>
@@ -4137,7 +4137,7 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
@@ -4163,7 +4163,7 @@
         <v>Armik - Brisas (2026 Remaster/Remix) (Exciting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B100" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=51Zu2iU2z2Q</v>
@@ -4175,7 +4175,7 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -4201,7 +4201,7 @@
         <v>Holly Humberstone - Lucy (Free People Sessions)</v>
       </c>
       <c r="B101" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=c1GR2TTs9W8</v>
@@ -4213,7 +4213,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G101" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-06-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-06-week02/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://www.youtube.com/watch?v=ym-h0EIlL3A</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://www.youtube.com/watch?v=bIwcNmu-rAg</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -515,19 +515,19 @@
         <v>Jason Derulo - Take You Dancing (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B4" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=oLzj8E8fHRQ</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,19 +553,19 @@
         <v>Sekou - Someone Like You (Adele Cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B5" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=YIy2g4enMiY</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://www.youtube.com/watch?v=NhuPT6MR2XU</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://www.youtube.com/watch?v=Z4RpBEg5uis</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -667,19 +667,19 @@
         <v>Reba McEntire - You Never Gave Up On Me</v>
       </c>
       <c r="B8" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=AUCRUStLmJM</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E8" t="str">
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://www.youtube.com/watch?v=sDDbD4R-xD4</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://www.youtube.com/watch?v=MxJQoyKh8TQ</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://www.youtube.com/watch?v=-UIkkGxMQG8</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://www.youtube.com/watch?v=b_uO5ROpk_0</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://www.youtube.com/watch?v=hSJfAFpdllk</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://www.youtube.com/watch?v=vdMK2DvnWJI</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://www.youtube.com/watch?v=5gvhRAGaOUo</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://www.youtube.com/watch?v=2AIMnAPxqfw</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://www.youtube.com/watch?v=UD7HkkAbnVA</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://www.youtube.com/watch?v=c5u3ur4vLo0</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1085,19 +1085,19 @@
         <v>Sienna Spiro - The Visitor (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B19" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=MibVDrnrQ10</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E19" t="str">
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,19 +1123,19 @@
         <v>Sienna Spiro - Die On This Hill (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B20" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=UhWumamExiI</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E20" t="str">
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1161,19 +1161,19 @@
         <v>RAYE - Where Is My Husband? (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B21" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=Z_HR2ZYY1VA</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E21" t="str">
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1199,19 +1199,19 @@
         <v>RAYE - Escapism (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B22" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=ywplqaIeHeQ</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E22" t="str">
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1237,19 +1237,19 @@
         <v>Take That - Never Forget (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B23" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=9S61JkOZLe8</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E23" t="str">
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1275,19 +1275,19 @@
         <v>Robyn - Dancing On My Own (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B24" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=_4SfgNPngbo</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E24" t="str">
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1313,19 +1313,19 @@
         <v>Take That - Patience (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B25" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=_I9qIxmrDuI</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E25" t="str">
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1351,19 +1351,19 @@
         <v>Mis-Teeq - Full Set (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B26" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=5AyQM_coDb8</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E26" t="str">
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1389,19 +1389,19 @@
         <v>Myles Smith - Stay (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B27" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=2ekY7Cb7CKs</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E27" t="str">
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1427,19 +1427,19 @@
         <v>Take That - Rule The World (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B28" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=0nc-qdhh6eU</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E28" t="str">
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1465,19 +1465,19 @@
         <v>Sienna Spiro - Material Lover (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B29" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=dZjAtTc9DBQ</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E29" t="str">
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1503,19 +1503,19 @@
         <v>Take That - Shine (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B30" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=T6TmxqOGIf0</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E30" t="str">
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1541,19 +1541,19 @@
         <v>MEEK - Dracula (Tame Impala Cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B31" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=4jnM--XhsC0</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E31" t="str">
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1579,19 +1579,19 @@
         <v>MEEK - Fabulous (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B32" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=kKSlraqNMhI</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E32" t="str">
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://www.youtube.com/watch?v=cUvsaKkjHYQ</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://www.youtube.com/watch?v=oKKNK0OCpQk</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://www.youtube.com/watch?v=ymvr4RCN-WE</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://www.youtube.com/watch?v=nhL2l4HCiRg</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://www.youtube.com/watch?v=e0PkSQNMcGs</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://www.youtube.com/watch?v=-7mPIus0U5Y</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://www.youtube.com/watch?v=G6jhovaAz3U</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://www.youtube.com/watch?v=QkCKENp-4Rs</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://www.youtube.com/watch?v=jsFekVlEaSA</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://www.youtube.com/watch?v=nfDKQ09bY_w</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://www.youtube.com/watch?v=eqceDkaK3PU</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://www.youtube.com/watch?v=UlP9zTLUeLw</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://www.youtube.com/watch?v=QCNwFDTkfYU</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2111,19 +2111,19 @@
         <v>The Cranberries - Scenes From 'Linger' (The Only Color Reel)</v>
       </c>
       <c r="B46" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=5-peG8H-lqE</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E46" t="str">
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://www.youtube.com/watch?v=P26-NjdBmbU</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://www.youtube.com/watch?v=BON1BSWLntE</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://www.youtube.com/watch?v=UTw106Ivz8o</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://www.youtube.com/watch?v=YFhpMpONGUY</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://www.youtube.com/watch?v=WrsXAfnTAdA</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://www.youtube.com/watch?v=L7Ls8ceHxhc</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://www.youtube.com/watch?v=OfcBfPnskG4</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://www.youtube.com/watch?v=-uvNvVtUidc</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://www.youtube.com/watch?v=WZUKJ90i6Tw</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://www.youtube.com/watch?v=KeRZtPUjl8g</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2529,19 +2529,19 @@
         <v>Freya Ridings - Mother Of Pearl (Official Video)</v>
       </c>
       <c r="B57" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=So5gx12fCsA</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E57" t="str">
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2567,19 +2567,19 @@
         <v>MUSE - Nightshift Superstar (Official Music Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=p--xk9n1eIM</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E58" t="str">
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2605,19 +2605,19 @@
         <v>Ellie Goulding - Black Prada Dress (Visualiser)</v>
       </c>
       <c r="B59" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=zr9CYpgPueI</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E59" t="str">
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2643,19 +2643,19 @@
         <v>Evanescence - Sanctuary (Official Visualizer)</v>
       </c>
       <c r="B60" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=E64jOWeVfpg</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E60" t="str">
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2681,19 +2681,19 @@
         <v>The Beaches - Perfect 10 (Official Visualizer)</v>
       </c>
       <c r="B61" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=N7TOR_l-CM8</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E61" t="str">
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2719,19 +2719,19 @@
         <v>Bella White - Stuff (Official Music Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=7QZtxsGBTks</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E62" t="str">
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2757,19 +2757,19 @@
         <v>Meduza, Rani - Silence (Official Visualizer)</v>
       </c>
       <c r="B63" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=cIdqz-WMod4</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E63" t="str">
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2795,19 +2795,19 @@
         <v>CAIN - Living Water (Lyric Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=Hv-8CM5NIPM</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E64" t="str">
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2833,19 +2833,19 @@
         <v>Fitz and the Tantrums - Greenlight (Official Visualizer)</v>
       </c>
       <c r="B65" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=Zx-ZPBbcA58</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E65" t="str">
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2871,19 +2871,19 @@
         <v>Jeremy Camp - Reflector (Official Music Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=SR-4q1yiYNA</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E66" t="str">
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2909,19 +2909,19 @@
         <v>Alesso, OneRepublic - In Your Eyes (Visualizer)</v>
       </c>
       <c r="B67" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=bS9C1ipyMy8</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E67" t="str">
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2947,19 +2947,19 @@
         <v>Malcolm Todd - Free.99 (Official Visualizer)</v>
       </c>
       <c r="B68" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=wBBQptUsOhw</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E68" t="str">
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -2985,19 +2985,19 @@
         <v>Isabel LaRosa - Every Life (Visualizer)</v>
       </c>
       <c r="B69" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=tIQDAtwNAY4</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E69" t="str">
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3023,19 +3023,19 @@
         <v>Wyatt Flores - Half The Man (Official Music Video)</v>
       </c>
       <c r="B70" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=2ChzcWHryFM</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E70" t="str">
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3061,19 +3061,19 @@
         <v>Mckenna Grace - Ugly and Rotten (Official Music Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=4yXFVgy7laM</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E71" t="str">
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3099,19 +3099,19 @@
         <v>Robert Grace - If You Were Gone ft. Bob Grace (OFFICIAL LYRIC VIDEO)</v>
       </c>
       <c r="B72" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=fbpQjMi3Hco</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E72" t="str">
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3137,19 +3137,19 @@
         <v>Boyzone - No Matter What (Live)</v>
       </c>
       <c r="B73" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=CEy96_jHw-Q</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E73" t="str">
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3175,19 +3175,19 @@
         <v>Florrie - The Times (Official Video)</v>
       </c>
       <c r="B74" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=6yBlNUaW7r4</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E74" t="str">
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3213,19 +3213,19 @@
         <v>Madonna - Love Sensation (Official Visualizer)</v>
       </c>
       <c r="B75" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=88fD-UtG_yo</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E75" t="str">
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3251,19 +3251,19 @@
         <v>DMA'S - Hurracane (Official Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=-zTB57LiXPk</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E76" t="str">
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3289,19 +3289,19 @@
         <v>Lainey Wilson and John Mayer - Phone, Keys, Wallet (Official Audio)</v>
       </c>
       <c r="B77" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=JzW6RnzeF9A</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E77" t="str">
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://www.youtube.com/watch?v=D_KTG0BzRiI</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://www.youtube.com/watch?v=29bfaHc1XiY</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://www.youtube.com/watch?v=LiYb4WGbp5Y</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://www.youtube.com/watch?v=lC14fuU8aPc</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3479,19 +3479,19 @@
         <v>Europe - The Cult of Ignorance (Official Video)</v>
       </c>
       <c r="B82" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=p-IOsjOJpnA</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E82" t="str">
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -3517,19 +3517,19 @@
         <v>Air Supply - Sweet Dreams (Official Lyric Video)</v>
       </c>
       <c r="B83" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=axiK2vYjXio</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E83" t="str">
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -3555,19 +3555,19 @@
         <v>Julia Cole - Treat Me Like Dirt (Official Lyric Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=TS2Mgp5F0cs</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E84" t="str">
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -3593,19 +3593,19 @@
         <v>Allen Stone - A Fathers Song - Placeholder Sessions</v>
       </c>
       <c r="B85" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=JPetpt4QMPE</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E85" t="str">
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://www.youtube.com/watch?v=qhmWM3uXPAU</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://www.youtube.com/watch?v=47LNk7oiTVI</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://www.youtube.com/watch?v=Ru3fB2l1RSo</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://www.youtube.com/watch?v=AMW1Zq9RbIU</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://www.youtube.com/watch?v=FYOmFfV7Ojo</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://www.youtube.com/watch?v=yDlkPdR_6zM</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://www.youtube.com/watch?v=hmjfuuuRRYU</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://www.youtube.com/watch?v=82-jTNka3uc</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://www.youtube.com/watch?v=rtyavLIJjy0</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://www.youtube.com/watch?v=7PApWObImjo</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://www.youtube.com/watch?v=vruZSAYJBe4</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://www.youtube.com/watch?v=k93t10R-Qrg</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://www.youtube.com/watch?v=XyRgdfXo2nI</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://www.youtube.com/watch?v=oGpKqX6ftcU</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://www.youtube.com/watch?v=51Zu2iU2z2Q</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>https://www.youtube.com/watch?v=c1GR2TTs9W8</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E101" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-06-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-06-week02/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Jason Derulo - The Other Side (Live at Capital's Summertime Ball 2026)</v>
+        <v>Niall Horan feat. Myles Smith - Drive Safe (Live at Capital's Summertime Ball 2026) | Capital</v>
       </c>
       <c r="B2" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=ym-h0EIlL3A</v>
+        <v>https://www.youtube.com/watch?v=mmu5Vh4hMu0</v>
       </c>
       <c r="D2" t="str">
         <v>2026-06-10</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Jason Derulo - The Other Side (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Niall Horan feat. Myles Smith - Drive Safe (Live at Capital's Summertime Ball 2026) | Capital - Capital FM</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Stephen Sanchez - Be More (Live at Capital's Summertime Ball 2026) | Capital</v>
+        <v>Gia Ford - At Least For Now</v>
       </c>
       <c r="B3" t="str">
-        <v>1 day ago</v>
+        <v>14h ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=bIwcNmu-rAg</v>
+        <v>https://www.youtube.com/watch?v=u2U0gUeCE5M</v>
       </c>
       <c r="D3" t="str">
         <v>2026-06-10</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>1 day ago</v>
+        <v>14h ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>Capital FM</v>
+        <v>Gia Ford</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Stephen Sanchez - Be More (Live at Capital's Summertime Ball 2026) | Capital - Capital FM</v>
+        <v>Gia Ford - At Least For Now - Gia Ford</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Jason Derulo - Take You Dancing (Live at Capital's Summertime Ball 2026)</v>
+        <v>Emilia Tarrant - The Three Words / Better Together (Live at Bread &amp; Butter Lounge)</v>
       </c>
       <c r="B4" t="str">
-        <v>2 days ago</v>
+        <v>18h ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=oLzj8E8fHRQ</v>
+        <v>https://www.youtube.com/watch?v=pE5wZRhY0P0</v>
       </c>
       <c r="D4" t="str">
         <v>2026-06-10</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>2 days ago</v>
+        <v>18h ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>Capital FM</v>
+        <v>Emilia Tarrant</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Jason Derulo - Take You Dancing (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Emilia Tarrant - The Three Words / Better Together (Live at Bread &amp; Butter Lounge) - Emilia Tarrant</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Sekou - Someone Like You (Adele Cover) (Live at Capital's Summertime Ball 2026)</v>
+        <v>Rodrigo y Gabriela - Monster (Official Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>2 days ago</v>
+        <v>18h ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=YIy2g4enMiY</v>
+        <v>https://www.youtube.com/watch?v=Wolzo63vons</v>
       </c>
       <c r="D5" t="str">
         <v>2026-06-10</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>2 days ago</v>
+        <v>18h ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>Capital FM</v>
+        <v>Rodrigo y Gabriela</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Sekou - Someone Like You (Adele Cover) (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Rodrigo y Gabriela - Monster (Official Video) - Rodrigo y Gabriela</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Sienna Spiro - He's Not My Baby, I'm His (Live at Capital's Summertime Ball 2026)</v>
+        <v>Max McNown - Done For (Performance Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>2 days ago</v>
+        <v>18h ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=NhuPT6MR2XU</v>
+        <v>https://www.youtube.com/watch?v=L1SxYiMiZEM</v>
       </c>
       <c r="D6" t="str">
         <v>2026-06-10</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>2 days ago</v>
+        <v>18h ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>Capital FM</v>
+        <v>Max McNown</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Sienna Spiro - He's Not My Baby, I'm His (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Max McNown - Done For (Performance Video) - Max McNown</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>DEEP PURPLE - DIABLO (Official Video)</v>
+        <v>Julia Cole - Big Picture (Official Lyric Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>2 days ago</v>
+        <v>23h ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=Z4RpBEg5uis</v>
+        <v>https://www.youtube.com/watch?v=M7LF0hhoPoc</v>
       </c>
       <c r="D7" t="str">
         <v>2026-06-10</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>2 days ago</v>
+        <v>23h ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>earMUSIC and Deep Purple Official</v>
+        <v>Julia Cole Music</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>DEEP PURPLE - DIABLO (Official Video) - earMUSIC and Deep Purple Official</v>
+        <v>Julia Cole - Big Picture (Official Lyric Video) - Julia Cole Music</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Reba McEntire - You Never Gave Up On Me</v>
+        <v>Joalin - On A Day Like This</v>
       </c>
       <c r="B8" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=AUCRUStLmJM</v>
+        <v>https://www.youtube.com/watch?v=VWLPWi9edlQ</v>
       </c>
       <c r="D8" t="str">
         <v>2026-06-10</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>Reba McEntire</v>
+        <v>Joalin</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Reba McEntire - You Never Gave Up On Me - Reba McEntire</v>
+        <v>Joalin - On A Day Like This - Joalin</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>elijah woods - Wonder (Official Lyric Video)</v>
+        <v>RAYE - Click Clack Symphony (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B9" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=sDDbD4R-xD4</v>
+        <v>https://www.youtube.com/watch?v=_TUh78OrzSM</v>
       </c>
       <c r="D9" t="str">
         <v>2026-06-10</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>elijah woods</v>
+        <v>Capital FM</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>elijah woods - Wonder (Official Lyric Video) - elijah woods</v>
+        <v>RAYE - Click Clack Symphony (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>XG - Flowers (Sweet Female Attitude Cover) (Live at Capital's Summertime Ball 2026)</v>
+        <v>Vera Blue - Rituals (Official Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=MxJQoyKh8TQ</v>
+        <v>https://www.youtube.com/watch?v=zJ2HNWcNauU</v>
       </c>
       <c r="D10" t="str">
         <v>2026-06-10</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>Capital FM and XG</v>
+        <v>Vera Blue</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>XG - Flowers (Sweet Female Attitude Cover) (Live at Capital's Summertime Ball 2026) - Capital FM and XG</v>
+        <v>Vera Blue - Rituals (Official Video) - Vera Blue</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Niall Horan - Nice To Meet Ya (Live at Capital's Summertime Ball 2026)</v>
+        <v>Wishy - Lovesick (Official Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=-UIkkGxMQG8</v>
+        <v>https://www.youtube.com/watch?v=q_WXgLn8sVw</v>
       </c>
       <c r="D11" t="str">
         <v>2026-06-10</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>Capital FM</v>
+        <v>Wishy</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Niall Horan - Nice To Meet Ya (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Wishy - Lovesick (Official Video) - Wishy</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Niall Horan - Steal My Girl (One Direction cover) (Live at Capital's Summertime Ball 2026)</v>
+        <v>Jason Derulo - In My Head (Live at Capital's Summertime Ball 2026) | Capital</v>
       </c>
       <c r="B12" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=b_uO5ROpk_0</v>
+        <v>https://www.youtube.com/watch?v=LudSER6wECQ</v>
       </c>
       <c r="D12" t="str">
         <v>2026-06-10</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Niall Horan - Steal My Girl (One Direction cover) (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Jason Derulo - In My Head (Live at Capital's Summertime Ball 2026) | Capital - Capital FM</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Niall Horan - Dinner Party (Live at Capital's Summertime Ball 2026)</v>
+        <v>RAYE - Beware.. The South London Lover Boy. (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B13" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=hSJfAFpdllk</v>
+        <v>https://www.youtube.com/watch?v=TxlMo7pbCOs</v>
       </c>
       <c r="D13" t="str">
         <v>2026-06-10</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Niall Horan - Dinner Party (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>RAYE - Beware.. The South London Lover Boy. (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Niall Horan - Slow Hands (Live at Capital's Summertime Ball 2026) | Capital</v>
+        <v>Niall Horan - This Town (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B14" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=vdMK2DvnWJI</v>
+        <v>https://www.youtube.com/watch?v=6TO_ITkIgBI</v>
       </c>
       <c r="D14" t="str">
         <v>2026-06-10</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Niall Horan - Slow Hands (Live at Capital's Summertime Ball 2026) | Capital - Capital FM</v>
+        <v>Niall Horan - This Town (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>RAYE - Joy (Live at Capital's Summertime Ball 2026)</v>
+        <v>Soft Cell - Danceteria (Official Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=5gvhRAGaOUo</v>
+        <v>https://www.youtube.com/watch?v=P4kE8CNvoOw</v>
       </c>
       <c r="D15" t="str">
         <v>2026-06-10</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>Capital FM</v>
+        <v>Soft Cell</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>RAYE - Joy (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Soft Cell - Danceteria (Official Video) - Soft Cell</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Myles Smith - Stargazing (Live at Capital's Summertime Ball 2026)</v>
+        <v>Take That - Greatest Day (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B16" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=2AIMnAPxqfw</v>
+        <v>https://www.youtube.com/watch?v=3dwS84ONnZ0</v>
       </c>
       <c r="D16" t="str">
         <v>2026-06-10</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Myles Smith - Stargazing (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Take That - Greatest Day (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Lola Young - From Down Here (Live at Capital's Summertime Ball 2026)</v>
+        <v>Take That - You're A Superstar (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B17" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=UD7HkkAbnVA</v>
+        <v>https://www.youtube.com/watch?v=g_KsWUl-nxw</v>
       </c>
       <c r="D17" t="str">
         <v>2026-06-10</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>Capital FM and Lola Young</v>
+        <v>Capital FM</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Lola Young - From Down Here (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
+        <v>Take That - You're A Superstar (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>XG - Hypnotize (Live at Capital's Summertime Ball 2026)</v>
+        <v>Jessie J - CALIFORNIA (Official Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=c5u3ur4vLo0</v>
+        <v>https://www.youtube.com/watch?v=tN1mV6mCJ3k</v>
       </c>
       <c r="D18" t="str">
         <v>2026-06-10</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>Capital FM and XG</v>
+        <v>Jessie J</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>XG - Hypnotize (Live at Capital's Summertime Ball 2026) - Capital FM and XG</v>
+        <v>Jessie J - CALIFORNIA (Official Video) - Jessie J</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Sienna Spiro - The Visitor (Live at Capital's Summertime Ball 2026)</v>
+        <v>Olivia Rodrigo - the cure (performance video)</v>
       </c>
       <c r="B19" t="str">
-        <v>3 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=MibVDrnrQ10</v>
+        <v>https://www.youtube.com/watch?v=OA2YUsJyQI0</v>
       </c>
       <c r="D19" t="str">
         <v>2026-06-10</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>3 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>Capital FM</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Sienna Spiro - The Visitor (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Olivia Rodrigo - the cure (performance video) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Sienna Spiro - Die On This Hill (Live at Capital's Summertime Ball 2026)</v>
+        <v>XG - Something Ain’t Right (Live at Capital's Summertime Ball 2026) | Capital</v>
       </c>
       <c r="B20" t="str">
-        <v>3 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=UhWumamExiI</v>
+        <v>https://www.youtube.com/watch?v=BWASDZZtO6w</v>
       </c>
       <c r="D20" t="str">
         <v>2026-06-10</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>3 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>Capital FM</v>
+        <v>Capital FM and XG</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Sienna Spiro - Die On This Hill (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>XG - Something Ain’t Right (Live at Capital's Summertime Ball 2026) | Capital - Capital FM and XG</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>RAYE - Where Is My Husband? (Live at Capital's Summertime Ball 2026)</v>
+        <v>Freya Ridings - Wild Horse (Official Lyric Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>3 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=Z_HR2ZYY1VA</v>
+        <v>https://www.youtube.com/watch?v=IpkgL5oZbbU</v>
       </c>
       <c r="D21" t="str">
         <v>2026-06-10</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>3 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>Capital FM</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>RAYE - Where Is My Husband? (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Freya Ridings - Wild Horse (Official Lyric Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>RAYE - Escapism (Live at Capital's Summertime Ball 2026)</v>
+        <v>Myles Smith - Hold Me In The Dark (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B22" t="str">
-        <v>3 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=ywplqaIeHeQ</v>
+        <v>https://www.youtube.com/watch?v=uVh2WwmC7Sw</v>
       </c>
       <c r="D22" t="str">
         <v>2026-06-10</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>3 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>RAYE - Escapism (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Myles Smith - Hold Me In The Dark (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Take That - Never Forget (Live at Capital's Summertime Ball 2026)</v>
+        <v>Niall Horan - Heaven (Live at Capital's Summertime Ball 2026) | Capital</v>
       </c>
       <c r="B23" t="str">
-        <v>3 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=9S61JkOZLe8</v>
+        <v>https://www.youtube.com/watch?v=CTmWK2o3mXY</v>
       </c>
       <c r="D23" t="str">
         <v>2026-06-10</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>3 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>Capital FM and Take That</v>
+        <v>Capital FM</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Take That - Never Forget (Live at Capital's Summertime Ball 2026) - Capital FM and Take That</v>
+        <v>Niall Horan - Heaven (Live at Capital's Summertime Ball 2026) | Capital - Capital FM</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Robyn - Dancing On My Own (Live at Capital's Summertime Ball 2026)</v>
+        <v>Strange AI Art Installations</v>
       </c>
       <c r="B24" t="str">
-        <v>3 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=_4SfgNPngbo</v>
+        <v>https://www.youtube.com/watch?v=KnOVECFvkMM</v>
       </c>
       <c r="D24" t="str">
         <v>2026-06-10</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>3 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>Capital FM</v>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Robyn - Dancing On My Own (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Strange AI Art Installations - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Take That - Patience (Live at Capital's Summertime Ball 2026)</v>
+        <v>Robyn - Talk To Me (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B25" t="str">
-        <v>3 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=_I9qIxmrDuI</v>
+        <v>https://www.youtube.com/watch?v=KQigrpSdFPY</v>
       </c>
       <c r="D25" t="str">
         <v>2026-06-10</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>3 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>Capital FM and Take That</v>
+        <v>Capital FM</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Take That - Patience (Live at Capital's Summertime Ball 2026) - Capital FM and Take That</v>
+        <v>Robyn - Talk To Me (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Mis-Teeq - Full Set (Live at Capital's Summertime Ball 2026)</v>
+        <v>Nora Fatehi, Vegedream, Sanjoy, FIFA Sound - Siir Siir (FIFA World Cup 2026™) [Official Music Video]</v>
       </c>
       <c r="B26" t="str">
-        <v>3 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=5AyQM_coDb8</v>
+        <v>https://www.youtube.com/watch?v=afiNbSxg7aw</v>
       </c>
       <c r="D26" t="str">
         <v>2026-06-10</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>3 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>Capital FM</v>
+        <v>FIFA and 3 more</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Mis-Teeq - Full Set (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Nora Fatehi, Vegedream, Sanjoy, FIFA Sound - Siir Siir (FIFA World Cup 2026™) [Official Music Video] - FIFA and 3 more</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Myles Smith - Stay (Live at Capital's Summertime Ball 2026)</v>
+        <v>Jason Derulo - Want To Want Me (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B27" t="str">
-        <v>3 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=2ekY7Cb7CKs</v>
+        <v>https://www.youtube.com/watch?v=QprQP1fdrDM</v>
       </c>
       <c r="D27" t="str">
         <v>2026-06-10</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>3 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Myles Smith - Stay (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Jason Derulo - Want To Want Me (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Take That - Rule The World (Live at Capital's Summertime Ball 2026)</v>
+        <v>Jason Derulo - The Other Side (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B28" t="str">
-        <v>3 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=0nc-qdhh6eU</v>
+        <v>https://www.youtube.com/watch?v=ym-h0EIlL3A</v>
       </c>
       <c r="D28" t="str">
         <v>2026-06-10</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>3 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>Capital FM and Take That</v>
+        <v>Capital FM</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Take That - Rule The World (Live at Capital's Summertime Ball 2026) - Capital FM and Take That</v>
+        <v>Jason Derulo - The Other Side (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Sienna Spiro - Material Lover (Live at Capital's Summertime Ball 2026)</v>
+        <v>Stephen Sanchez - Be More (Live at Capital's Summertime Ball 2026) | Capital</v>
       </c>
       <c r="B29" t="str">
-        <v>3 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=dZjAtTc9DBQ</v>
+        <v>https://www.youtube.com/watch?v=bIwcNmu-rAg</v>
       </c>
       <c r="D29" t="str">
         <v>2026-06-10</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>3 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Sienna Spiro - Material Lover (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Stephen Sanchez - Be More (Live at Capital's Summertime Ball 2026) | Capital - Capital FM</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Take That - Shine (Live at Capital's Summertime Ball 2026)</v>
+        <v>Jason Derulo - Take You Dancing (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B30" t="str">
-        <v>3 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=T6TmxqOGIf0</v>
+        <v>https://www.youtube.com/watch?v=oLzj8E8fHRQ</v>
       </c>
       <c r="D30" t="str">
         <v>2026-06-10</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>3 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Take That - Shine (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Jason Derulo - Take You Dancing (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>MEEK - Dracula (Tame Impala Cover) (Live at Capital's Summertime Ball 2026)</v>
+        <v>Sekou - Someone Like You (Adele Cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B31" t="str">
-        <v>3 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=4jnM--XhsC0</v>
+        <v>https://www.youtube.com/watch?v=YIy2g4enMiY</v>
       </c>
       <c r="D31" t="str">
         <v>2026-06-10</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>3 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>MEEK - Dracula (Tame Impala Cover) (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Sekou - Someone Like You (Adele Cover) (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>MEEK - Fabulous (Live at Capital's Summertime Ball 2026)</v>
+        <v>Sienna Spiro - He's Not My Baby, I'm His (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B32" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=kKSlraqNMhI</v>
+        <v>https://www.youtube.com/watch?v=NhuPT6MR2XU</v>
       </c>
       <c r="D32" t="str">
         <v>2026-06-10</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>MEEK - Fabulous (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Sienna Spiro - He's Not My Baby, I'm His (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Lola Young - Messy (Live at Capital's Summertime Ball 2026)</v>
+        <v>DEEP PURPLE - DIABLO (Official Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=cUvsaKkjHYQ</v>
+        <v>https://www.youtube.com/watch?v=Z4RpBEg5uis</v>
       </c>
       <c r="D33" t="str">
         <v>2026-06-10</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>Capital FM and Lola Young</v>
+        <v>earMUSIC and Deep Purple Official</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Lola Young - Messy (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
+        <v>DEEP PURPLE - DIABLO (Official Video) - earMUSIC and Deep Purple Official</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Stephen Sanchez - Until I Found You (Live at Capital's Summertime Ball 2026)</v>
+        <v>Reba McEntire - You Never Gave Up On Me</v>
       </c>
       <c r="B34" t="str">
-        <v>3 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=oKKNK0OCpQk</v>
+        <v>https://www.youtube.com/watch?v=AUCRUStLmJM</v>
       </c>
       <c r="D34" t="str">
         <v>2026-06-10</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>3 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Capital FM</v>
+        <v>Reba McEntire</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Stephen Sanchez - Until I Found You (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Reba McEntire - You Never Gave Up On Me - Reba McEntire</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Lola Young - D£aler (Live at Capital's Summertime Ball 2026)</v>
+        <v>elijah woods - Wonder (Official Lyric Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=ymvr4RCN-WE</v>
+        <v>https://www.youtube.com/watch?v=sDDbD4R-xD4</v>
       </c>
       <c r="D35" t="str">
         <v>2026-06-10</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>Capital FM and Lola Young</v>
+        <v>elijah woods</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Lola Young - D£aler (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
+        <v>elijah woods - Wonder (Official Lyric Video) - elijah woods</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Lola Young - One Thing (Live at Capital's Summertime Ball 2026)</v>
+        <v>XG - Flowers (Sweet Female Attitude Cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B36" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=nhL2l4HCiRg</v>
+        <v>https://www.youtube.com/watch?v=MxJQoyKh8TQ</v>
       </c>
       <c r="D36" t="str">
         <v>2026-06-10</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>Capital FM and Lola Young</v>
+        <v>Capital FM and XG</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Lola Young - One Thing (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
+        <v>XG - Flowers (Sweet Female Attitude Cover) (Live at Capital's Summertime Ball 2026) - Capital FM and XG</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Bebe Rexha - Sad Girls (Live at Capital's Summertime Ball 2026)</v>
+        <v>Niall Horan - Nice To Meet Ya (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B37" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=e0PkSQNMcGs</v>
+        <v>https://www.youtube.com/watch?v=-UIkkGxMQG8</v>
       </c>
       <c r="D37" t="str">
         <v>2026-06-10</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Bebe Rexha - Sad Girls (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Niall Horan - Nice To Meet Ya (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Robyn - Dopamine (Live at Capital's Summertime Ball 2026)</v>
+        <v>Niall Horan - Steal My Girl (One Direction cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B38" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=-7mPIus0U5Y</v>
+        <v>https://www.youtube.com/watch?v=b_uO5ROpk_0</v>
       </c>
       <c r="D38" t="str">
         <v>2026-06-10</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Robyn - Dopamine (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Niall Horan - Steal My Girl (One Direction cover) (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Jason Derulo - Ridin' Solo (Live at Capital's Summertime Ball 2026)</v>
+        <v>Niall Horan - Dinner Party (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B39" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=G6jhovaAz3U</v>
+        <v>https://www.youtube.com/watch?v=hSJfAFpdllk</v>
       </c>
       <c r="D39" t="str">
         <v>2026-06-10</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Jason Derulo - Ridin' Solo (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Niall Horan - Dinner Party (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Jason Derulo - Trumpets (Live at Capital's Summertime Ball 2026)</v>
+        <v>Niall Horan - Slow Hands (Live at Capital's Summertime Ball 2026) | Capital</v>
       </c>
       <c r="B40" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=QkCKENp-4Rs</v>
+        <v>https://www.youtube.com/watch?v=vdMK2DvnWJI</v>
       </c>
       <c r="D40" t="str">
         <v>2026-06-10</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Jason Derulo - Trumpets (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Niall Horan - Slow Hands (Live at Capital's Summertime Ball 2026) | Capital - Capital FM</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Jason Derulo - Whatcha Say (Live at Capital's Summertime Ball 2026)</v>
+        <v>RAYE - Joy (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B41" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=jsFekVlEaSA</v>
+        <v>https://www.youtube.com/watch?v=5gvhRAGaOUo</v>
       </c>
       <c r="D41" t="str">
         <v>2026-06-10</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Jason Derulo - Whatcha Say (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>RAYE - Joy (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Bebe Rexha - New Religion (Live at Capital's Summertime Ball 2026)</v>
+        <v>Myles Smith - Stargazing (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B42" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=nfDKQ09bY_w</v>
+        <v>https://www.youtube.com/watch?v=2AIMnAPxqfw</v>
       </c>
       <c r="D42" t="str">
         <v>2026-06-10</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Bebe Rexha - New Religion (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Myles Smith - Stargazing (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Bebe Rexha - I'm Good (Live at Capital's Summertime Ball 2026)</v>
+        <v>Lola Young - From Down Here (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B43" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=eqceDkaK3PU</v>
+        <v>https://www.youtube.com/watch?v=UD7HkkAbnVA</v>
       </c>
       <c r="D43" t="str">
         <v>2026-06-10</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>Capital FM</v>
+        <v>Capital FM and Lola Young</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Bebe Rexha - I'm Good (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Lola Young - From Down Here (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Bebe Rexha - In The Name Of Love (Live at Capital's Summertime Ball 2026)</v>
+        <v>XG - Hypnotize (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B44" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=UlP9zTLUeLw</v>
+        <v>https://www.youtube.com/watch?v=c5u3ur4vLo0</v>
       </c>
       <c r="D44" t="str">
         <v>2026-06-10</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>Capital FM</v>
+        <v>Capital FM and XG</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Bebe Rexha - In The Name Of Love (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>XG - Hypnotize (Live at Capital's Summertime Ball 2026) - Capital FM and XG</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Strange Surreal AI - In Here - Kelly Boesch | 4K</v>
+        <v>Sienna Spiro - Die On This Hill (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B45" t="str">
-        <v>4 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=QCNwFDTkfYU</v>
+        <v>https://www.youtube.com/watch?v=UhWumamExiI</v>
       </c>
       <c r="D45" t="str">
         <v>2026-06-10</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>4 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>Kelly Boesch AI Art</v>
+        <v>Capital FM</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Strange Surreal AI - In Here - Kelly Boesch | 4K - Kelly Boesch AI Art</v>
+        <v>Sienna Spiro - Die On This Hill (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>The Cranberries - Scenes From 'Linger' (The Only Color Reel)</v>
+        <v>RAYE - Where Is My Husband? (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B46" t="str">
-        <v>4 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=5-peG8H-lqE</v>
+        <v>https://www.youtube.com/watch?v=Z_HR2ZYY1VA</v>
       </c>
       <c r="D46" t="str">
         <v>2026-06-10</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>4 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>TheCranberriesTV</v>
+        <v>Capital FM</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>The Cranberries - Scenes From 'Linger' (The Only Color Reel) - TheCranberriesTV</v>
+        <v>RAYE - Where Is My Husband? (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Jordana Bryant - Too Little Too Late (Official Lyric Video)</v>
+        <v>Take That - Never Forget (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B47" t="str">
-        <v>4 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=P26-NjdBmbU</v>
+        <v>https://www.youtube.com/watch?v=9S61JkOZLe8</v>
       </c>
       <c r="D47" t="str">
         <v>2026-06-10</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>4 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>Jordana Bryant</v>
+        <v>Capital FM and Take That</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Jordana Bryant - Too Little Too Late (Official Lyric Video) - Jordana Bryant</v>
+        <v>Take That - Never Forget (Live at Capital's Summertime Ball 2026) - Capital FM and Take That</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Grace Enger - "Running Back To You" (Official Music Video)</v>
+        <v>Robyn - Dancing On My Own (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B48" t="str">
-        <v>4 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=BON1BSWLntE</v>
+        <v>https://www.youtube.com/watch?v=_4SfgNPngbo</v>
       </c>
       <c r="D48" t="str">
         <v>2026-06-10</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>4 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>Grace Enger</v>
+        <v>Capital FM</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Grace Enger - "Running Back To You" (Official Music Video) - Grace Enger</v>
+        <v>Robyn - Dancing On My Own (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>The Offspring - Gone Away | Live at BeachLife Festival 2026</v>
+        <v>Take That - Patience (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B49" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=UTw106Ivz8o</v>
+        <v>https://www.youtube.com/watch?v=_I9qIxmrDuI</v>
       </c>
       <c r="D49" t="str">
         <v>2026-06-10</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>The Offspring</v>
+        <v>Capital FM and Take That</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>The Offspring - Gone Away | Live at BeachLife Festival 2026 - The Offspring</v>
+        <v>Take That - Patience (Live at Capital's Summertime Ball 2026) - Capital FM and Take That</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Lola Young – From Down Here (From The Pool)</v>
+        <v>Mis-Teeq - Full Set (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B50" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=YFhpMpONGUY</v>
+        <v>https://www.youtube.com/watch?v=5AyQM_coDb8</v>
       </c>
       <c r="D50" t="str">
         <v>2026-06-10</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>Lola Young</v>
+        <v>Capital FM</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Lola Young – From Down Here (From The Pool) - Lola Young</v>
+        <v>Mis-Teeq - Full Set (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>CAIN - Living Water (Music Video)</v>
+        <v>Take That - Rule The World (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B51" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=WrsXAfnTAdA</v>
+        <v>https://www.youtube.com/watch?v=0nc-qdhh6eU</v>
       </c>
       <c r="D51" t="str">
         <v>2026-06-10</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>CAIN</v>
+        <v>Capital FM and Take That</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>CAIN - Living Water (Music Video) - CAIN</v>
+        <v>Take That - Rule The World (Live at Capital's Summertime Ball 2026) - Capital FM and Take That</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>B.B. King &amp; Eric Clapton - Riding With The King (Official Music Video)</v>
+        <v>Sienna Spiro - Material Lover (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B52" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=L7Ls8ceHxhc</v>
+        <v>https://www.youtube.com/watch?v=dZjAtTc9DBQ</v>
       </c>
       <c r="D52" t="str">
         <v>2026-06-10</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>Eric Clapton</v>
+        <v>Capital FM</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>B.B. King &amp; Eric Clapton - Riding With The King (Official Music Video) - Eric Clapton</v>
+        <v>Sienna Spiro - Material Lover (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Blu DeTiger - Whisper (Official Music Video)</v>
+        <v>Take That - Shine (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B53" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=OfcBfPnskG4</v>
+        <v>https://www.youtube.com/watch?v=T6TmxqOGIf0</v>
       </c>
       <c r="D53" t="str">
         <v>2026-06-10</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>Blu DeTiger</v>
+        <v>Capital FM</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Blu DeTiger - Whisper (Official Music Video) - Blu DeTiger</v>
+        <v>Take That - Shine (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Romeo Santos, Prince Royce - Ay! San Miguel (Official Video)</v>
+        <v>MEEK - Dracula (Tame Impala Cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B54" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=-uvNvVtUidc</v>
+        <v>https://www.youtube.com/watch?v=4jnM--XhsC0</v>
       </c>
       <c r="D54" t="str">
         <v>2026-06-10</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>Romeo Santos and Prince Royce</v>
+        <v>Capital FM</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Romeo Santos, Prince Royce - Ay! San Miguel (Official Video) - Romeo Santos and Prince Royce</v>
+        <v>MEEK - Dracula (Tame Impala Cover) (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Pink Floyd - Pigs on the Wing (8-Track Version - Official Audio)</v>
+        <v>Lola Young - Messy (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B55" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=WZUKJ90i6Tw</v>
+        <v>https://www.youtube.com/watch?v=cUvsaKkjHYQ</v>
       </c>
       <c r="D55" t="str">
         <v>2026-06-10</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>Pink Floyd</v>
+        <v>Capital FM and Lola Young</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Pink Floyd - Pigs on the Wing (8-Track Version - Official Audio) - Pink Floyd</v>
+        <v>Lola Young - Messy (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Holly Humberstone - it’s just White Noise</v>
+        <v>Stephen Sanchez - Until I Found You (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B56" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=KeRZtPUjl8g</v>
+        <v>https://www.youtube.com/watch?v=oKKNK0OCpQk</v>
       </c>
       <c r="D56" t="str">
         <v>2026-06-10</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>Holly Humberstone</v>
+        <v>Capital FM</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Holly Humberstone - it’s just White Noise - Holly Humberstone</v>
+        <v>Stephen Sanchez - Until I Found You (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Freya Ridings - Mother Of Pearl (Official Video)</v>
+        <v>Lola Young - One Thing (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B57" t="str">
-        <v>5 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=So5gx12fCsA</v>
+        <v>https://www.youtube.com/watch?v=nhL2l4HCiRg</v>
       </c>
       <c r="D57" t="str">
         <v>2026-06-10</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>5 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>Freya Ridings</v>
+        <v>Capital FM and Lola Young</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Freya Ridings - Mother Of Pearl (Official Video) - Freya Ridings</v>
+        <v>Lola Young - One Thing (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>MUSE - Nightshift Superstar (Official Music Video)</v>
+        <v>Bebe Rexha - Sad Girls (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B58" t="str">
-        <v>5 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=p--xk9n1eIM</v>
+        <v>https://www.youtube.com/watch?v=e0PkSQNMcGs</v>
       </c>
       <c r="D58" t="str">
         <v>2026-06-10</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>5 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>Muse</v>
+        <v>Capital FM</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>MUSE - Nightshift Superstar (Official Music Video) - Muse</v>
+        <v>Bebe Rexha - Sad Girls (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Ellie Goulding - Black Prada Dress (Visualiser)</v>
+        <v>Robyn - Dopamine (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B59" t="str">
-        <v>5 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=zr9CYpgPueI</v>
+        <v>https://www.youtube.com/watch?v=-7mPIus0U5Y</v>
       </c>
       <c r="D59" t="str">
         <v>2026-06-10</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>5 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>Ellie Goulding</v>
+        <v>Capital FM</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Ellie Goulding - Black Prada Dress (Visualiser) - Ellie Goulding</v>
+        <v>Robyn - Dopamine (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Evanescence - Sanctuary (Official Visualizer)</v>
+        <v>Jason Derulo - Trumpets (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B60" t="str">
-        <v>5 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=E64jOWeVfpg</v>
+        <v>https://www.youtube.com/watch?v=QkCKENp-4Rs</v>
       </c>
       <c r="D60" t="str">
         <v>2026-06-10</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>5 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>Evanescence</v>
+        <v>Capital FM</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Evanescence - Sanctuary (Official Visualizer) - Evanescence</v>
+        <v>Jason Derulo - Trumpets (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>The Beaches - Perfect 10 (Official Visualizer)</v>
+        <v>Jason Derulo - Whatcha Say (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B61" t="str">
-        <v>5 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=N7TOR_l-CM8</v>
+        <v>https://www.youtube.com/watch?v=jsFekVlEaSA</v>
       </c>
       <c r="D61" t="str">
         <v>2026-06-10</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>5 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>The Beaches</v>
+        <v>Capital FM</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>The Beaches - Perfect 10 (Official Visualizer) - The Beaches</v>
+        <v>Jason Derulo - Whatcha Say (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Bella White - Stuff (Official Music Video)</v>
+        <v>Bebe Rexha - New Religion (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B62" t="str">
-        <v>5 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=7QZtxsGBTks</v>
+        <v>https://www.youtube.com/watch?v=nfDKQ09bY_w</v>
       </c>
       <c r="D62" t="str">
         <v>2026-06-10</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>5 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>Bella White</v>
+        <v>Capital FM</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Bella White - Stuff (Official Music Video) - Bella White</v>
+        <v>Bebe Rexha - New Religion (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Meduza, Rani - Silence (Official Visualizer)</v>
+        <v>Bebe Rexha - I'm Good (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B63" t="str">
-        <v>5 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=cIdqz-WMod4</v>
+        <v>https://www.youtube.com/watch?v=eqceDkaK3PU</v>
       </c>
       <c r="D63" t="str">
         <v>2026-06-10</v>
@@ -2769,13 +2769,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>5 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>Meduza and 2 more</v>
+        <v>Capital FM</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Meduza, Rani - Silence (Official Visualizer) - Meduza and 2 more</v>
+        <v>Bebe Rexha - I'm Good (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>CAIN - Living Water (Lyric Video)</v>
+        <v>Strange Surreal AI - In Here - Kelly Boesch | 4K</v>
       </c>
       <c r="B64" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=Hv-8CM5NIPM</v>
+        <v>https://www.youtube.com/watch?v=QCNwFDTkfYU</v>
       </c>
       <c r="D64" t="str">
         <v>2026-06-10</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>CAIN</v>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>CAIN - Living Water (Lyric Video) - CAIN</v>
+        <v>Strange Surreal AI - In Here - Kelly Boesch | 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Fitz and the Tantrums - Greenlight (Official Visualizer)</v>
+        <v>The Cranberries - Scenes From 'Linger' (The Only Color Reel)</v>
       </c>
       <c r="B65" t="str">
-        <v>5 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=Zx-ZPBbcA58</v>
+        <v>https://www.youtube.com/watch?v=5-peG8H-lqE</v>
       </c>
       <c r="D65" t="str">
         <v>2026-06-10</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>5 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>Fitz and the Tantrums</v>
+        <v>TheCranberriesTV</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Fitz and the Tantrums - Greenlight (Official Visualizer) - Fitz and the Tantrums</v>
+        <v>The Cranberries - Scenes From 'Linger' (The Only Color Reel) - TheCranberriesTV</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Jeremy Camp - Reflector (Official Music Video)</v>
+        <v>Jordana Bryant - Too Little Too Late (Official Lyric Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=SR-4q1yiYNA</v>
+        <v>https://www.youtube.com/watch?v=P26-NjdBmbU</v>
       </c>
       <c r="D66" t="str">
         <v>2026-06-10</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>Jeremy Camp</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Jeremy Camp - Reflector (Official Music Video) - Jeremy Camp</v>
+        <v>Jordana Bryant - Too Little Too Late (Official Lyric Video) - Jordana Bryant</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Alesso, OneRepublic - In Your Eyes (Visualizer)</v>
+        <v>Grace Enger - "Running Back To You" (Official Music Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=bS9C1ipyMy8</v>
+        <v>https://www.youtube.com/watch?v=BON1BSWLntE</v>
       </c>
       <c r="D67" t="str">
         <v>2026-06-10</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>Alesso</v>
+        <v>Grace Enger</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Alesso, OneRepublic - In Your Eyes (Visualizer) - Alesso</v>
+        <v>Grace Enger - "Running Back To You" (Official Music Video) - Grace Enger</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Malcolm Todd - Free.99 (Official Visualizer)</v>
+        <v>The Offspring - Gone Away | Live at BeachLife Festival 2026</v>
       </c>
       <c r="B68" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=wBBQptUsOhw</v>
+        <v>https://www.youtube.com/watch?v=UTw106Ivz8o</v>
       </c>
       <c r="D68" t="str">
         <v>2026-06-10</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>Malcolm Todd</v>
+        <v>The Offspring</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Malcolm Todd - Free.99 (Official Visualizer) - Malcolm Todd</v>
+        <v>The Offspring - Gone Away | Live at BeachLife Festival 2026 - The Offspring</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Isabel LaRosa - Every Life (Visualizer)</v>
+        <v>Lola Young – From Down Here (From The Pool)</v>
       </c>
       <c r="B69" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=tIQDAtwNAY4</v>
+        <v>https://www.youtube.com/watch?v=YFhpMpONGUY</v>
       </c>
       <c r="D69" t="str">
         <v>2026-06-10</v>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>Isabel LaRosa</v>
+        <v>Lola Young</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Isabel LaRosa - Every Life (Visualizer) - Isabel LaRosa</v>
+        <v>Lola Young – From Down Here (From The Pool) - Lola Young</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Wyatt Flores - Half The Man (Official Music Video)</v>
+        <v>CAIN - Living Water (Music Video)</v>
       </c>
       <c r="B70" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=2ChzcWHryFM</v>
+        <v>https://www.youtube.com/watch?v=WrsXAfnTAdA</v>
       </c>
       <c r="D70" t="str">
         <v>2026-06-10</v>
@@ -3035,13 +3035,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>Wyatt Flores</v>
+        <v>CAIN</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Wyatt Flores - Half The Man (Official Music Video) - Wyatt Flores</v>
+        <v>CAIN - Living Water (Music Video) - CAIN</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Mckenna Grace - Ugly and Rotten (Official Music Video)</v>
+        <v>B.B. King &amp; Eric Clapton - Riding With The King (Official Music Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=4yXFVgy7laM</v>
+        <v>https://www.youtube.com/watch?v=L7Ls8ceHxhc</v>
       </c>
       <c r="D71" t="str">
         <v>2026-06-10</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>Mckenna Grace</v>
+        <v>Eric Clapton</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Mckenna Grace - Ugly and Rotten (Official Music Video) - Mckenna Grace</v>
+        <v>B.B. King &amp; Eric Clapton - Riding With The King (Official Music Video) - Eric Clapton</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Robert Grace - If You Were Gone ft. Bob Grace (OFFICIAL LYRIC VIDEO)</v>
+        <v>Blu DeTiger - Whisper (Official Music Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=fbpQjMi3Hco</v>
+        <v>https://www.youtube.com/watch?v=OfcBfPnskG4</v>
       </c>
       <c r="D72" t="str">
         <v>2026-06-10</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>Robert Grace</v>
+        <v>Blu DeTiger</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Robert Grace - If You Were Gone ft. Bob Grace (OFFICIAL LYRIC VIDEO) - Robert Grace</v>
+        <v>Blu DeTiger - Whisper (Official Music Video) - Blu DeTiger</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Boyzone - No Matter What (Live)</v>
+        <v>Romeo Santos, Prince Royce - Ay! San Miguel (Official Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=CEy96_jHw-Q</v>
+        <v>https://www.youtube.com/watch?v=-uvNvVtUidc</v>
       </c>
       <c r="D73" t="str">
         <v>2026-06-10</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>Boyzone</v>
+        <v>Romeo Santos and Prince Royce</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Boyzone - No Matter What (Live) - Boyzone</v>
+        <v>Romeo Santos, Prince Royce - Ay! San Miguel (Official Video) - Romeo Santos and Prince Royce</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Florrie - The Times (Official Video)</v>
+        <v>Pink Floyd - Pigs on the Wing (8-Track Version - Official Audio)</v>
       </c>
       <c r="B74" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=6yBlNUaW7r4</v>
+        <v>https://www.youtube.com/watch?v=WZUKJ90i6Tw</v>
       </c>
       <c r="D74" t="str">
         <v>2026-06-10</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>florriemusic</v>
+        <v>Pink Floyd</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Florrie - The Times (Official Video) - florriemusic</v>
+        <v>Pink Floyd - Pigs on the Wing (8-Track Version - Official Audio) - Pink Floyd</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Madonna - Love Sensation (Official Visualizer)</v>
+        <v>Holly Humberstone - it’s just White Noise</v>
       </c>
       <c r="B75" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=88fD-UtG_yo</v>
+        <v>https://www.youtube.com/watch?v=KeRZtPUjl8g</v>
       </c>
       <c r="D75" t="str">
         <v>2026-06-10</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>Madonna</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Madonna - Love Sensation (Official Visualizer) - Madonna</v>
+        <v>Holly Humberstone - it’s just White Noise - Holly Humberstone</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>DMA'S - Hurracane (Official Video)</v>
+        <v>Freya Ridings - Mother Of Pearl (Official Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>6 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=-zTB57LiXPk</v>
+        <v>https://www.youtube.com/watch?v=So5gx12fCsA</v>
       </c>
       <c r="D76" t="str">
         <v>2026-06-10</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>6 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>DMA'S</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>DMA'S - Hurracane (Official Video) - DMA'S</v>
+        <v>Freya Ridings - Mother Of Pearl (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Lainey Wilson and John Mayer - Phone, Keys, Wallet (Official Audio)</v>
+        <v>MUSE - Nightshift Superstar (Official Music Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>6 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=JzW6RnzeF9A</v>
+        <v>https://www.youtube.com/watch?v=p--xk9n1eIM</v>
       </c>
       <c r="D77" t="str">
         <v>2026-06-10</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>6 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>Lainey Wilson and John Mayer</v>
+        <v>Muse</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Lainey Wilson and John Mayer - Phone, Keys, Wallet (Official Audio) - Lainey Wilson and John Mayer</v>
+        <v>MUSE - Nightshift Superstar (Official Music Video) - Muse</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>ROLE MODEL - High Hopes 3000 (Official Music Video)</v>
+        <v>Ellie Goulding - Black Prada Dress (Visualiser)</v>
       </c>
       <c r="B78" t="str">
-        <v>6 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=D_KTG0BzRiI</v>
+        <v>https://www.youtube.com/watch?v=zr9CYpgPueI</v>
       </c>
       <c r="D78" t="str">
         <v>2026-06-10</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>6 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>ROLE MODEL</v>
+        <v>Ellie Goulding</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>ROLE MODEL - High Hopes 3000 (Official Music Video) - ROLE MODEL</v>
+        <v>Ellie Goulding - Black Prada Dress (Visualiser) - Ellie Goulding</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Shawn Mendes - Treat You Better (Live from New York)</v>
+        <v>Evanescence - Sanctuary (Official Visualizer)</v>
       </c>
       <c r="B79" t="str">
-        <v>6 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=29bfaHc1XiY</v>
+        <v>https://www.youtube.com/watch?v=E64jOWeVfpg</v>
       </c>
       <c r="D79" t="str">
         <v>2026-06-10</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>6 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>Shawn Mendes</v>
+        <v>Evanescence</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Shawn Mendes - Treat You Better (Live from New York) - Shawn Mendes</v>
+        <v>Evanescence - Sanctuary (Official Visualizer) - Evanescence</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>SIENNA SPIRO - The Visitor (Official Music Video)</v>
+        <v>The Beaches - Perfect 10 (Official Visualizer)</v>
       </c>
       <c r="B80" t="str">
-        <v>6 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=LiYb4WGbp5Y</v>
+        <v>https://www.youtube.com/watch?v=N7TOR_l-CM8</v>
       </c>
       <c r="D80" t="str">
         <v>2026-06-10</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>6 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>The Beaches</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>SIENNA SPIRO - The Visitor (Official Music Video) - SIENNA SPIRO</v>
+        <v>The Beaches - Perfect 10 (Official Visualizer) - The Beaches</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Just Slide Official Music Video | Kelly Boesch | 4K</v>
+        <v>Bella White - Stuff (Official Music Video)</v>
       </c>
       <c r="B81" t="str">
-        <v>6 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=lC14fuU8aPc</v>
+        <v>https://www.youtube.com/watch?v=7QZtxsGBTks</v>
       </c>
       <c r="D81" t="str">
         <v>2026-06-10</v>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>6 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>Kelly Boesch AI Art</v>
+        <v>Bella White</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Just Slide Official Music Video | Kelly Boesch | 4K - Kelly Boesch AI Art</v>
+        <v>Bella White - Stuff (Official Music Video) - Bella White</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Europe - The Cult of Ignorance (Official Video)</v>
+        <v>Meduza, Rani - Silence (Official Visualizer)</v>
       </c>
       <c r="B82" t="str">
-        <v>7 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=p-IOsjOJpnA</v>
+        <v>https://www.youtube.com/watch?v=cIdqz-WMod4</v>
       </c>
       <c r="D82" t="str">
         <v>2026-06-10</v>
@@ -3491,13 +3491,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>7 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>Europe</v>
+        <v>Meduza and 2 more</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Europe - The Cult of Ignorance (Official Video) - Europe</v>
+        <v>Meduza, Rani - Silence (Official Visualizer) - Meduza and 2 more</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Air Supply - Sweet Dreams (Official Lyric Video)</v>
+        <v>CAIN - Living Water (Lyric Video)</v>
       </c>
       <c r="B83" t="str">
-        <v>7 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=axiK2vYjXio</v>
+        <v>https://www.youtube.com/watch?v=Hv-8CM5NIPM</v>
       </c>
       <c r="D83" t="str">
         <v>2026-06-10</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>7 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>Air Supply</v>
+        <v>CAIN</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Air Supply - Sweet Dreams (Official Lyric Video) - Air Supply</v>
+        <v>CAIN - Living Water (Lyric Video) - CAIN</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Julia Cole - Treat Me Like Dirt (Official Lyric Video)</v>
+        <v>Fitz and the Tantrums - Greenlight (Official Visualizer)</v>
       </c>
       <c r="B84" t="str">
-        <v>7 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=TS2Mgp5F0cs</v>
+        <v>https://www.youtube.com/watch?v=Zx-ZPBbcA58</v>
       </c>
       <c r="D84" t="str">
         <v>2026-06-10</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>7 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>Julia Cole Music</v>
+        <v>Fitz and the Tantrums</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Julia Cole - Treat Me Like Dirt (Official Lyric Video) - Julia Cole Music</v>
+        <v>Fitz and the Tantrums - Greenlight (Official Visualizer) - Fitz and the Tantrums</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Allen Stone - A Fathers Song - Placeholder Sessions</v>
+        <v>Jeremy Camp - Reflector (Official Music Video)</v>
       </c>
       <c r="B85" t="str">
-        <v>7 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=JPetpt4QMPE</v>
+        <v>https://www.youtube.com/watch?v=SR-4q1yiYNA</v>
       </c>
       <c r="D85" t="str">
         <v>2026-06-10</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>7 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>Allen Stone and Placeholder Sessions</v>
+        <v>Jeremy Camp</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Allen Stone - A Fathers Song - Placeholder Sessions - Allen Stone and Placeholder Sessions</v>
+        <v>Jeremy Camp - Reflector (Official Music Video) - Jeremy Camp</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Morgan Wallen - Don't We (Live From Tuscaloosa)</v>
+        <v>Alesso, OneRepublic - In Your Eyes (Visualizer)</v>
       </c>
       <c r="B86" t="str">
-        <v>7 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=qhmWM3uXPAU</v>
+        <v>https://www.youtube.com/watch?v=bS9C1ipyMy8</v>
       </c>
       <c r="D86" t="str">
         <v>2026-06-10</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>7 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>Morgan Wallen</v>
+        <v>Alesso</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Morgan Wallen - Don't We (Live From Tuscaloosa) - Morgan Wallen</v>
+        <v>Alesso, OneRepublic - In Your Eyes (Visualizer) - Alesso</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Billy Idol - John Wayne feat. Alison Mosshart (Official Music Video)</v>
+        <v>Malcolm Todd - Free.99 (Official Visualizer)</v>
       </c>
       <c r="B87" t="str">
-        <v>7 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=47LNk7oiTVI</v>
+        <v>https://www.youtube.com/watch?v=wBBQptUsOhw</v>
       </c>
       <c r="D87" t="str">
         <v>2026-06-10</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>7 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>Billy Idol</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Billy Idol - John Wayne feat. Alison Mosshart (Official Music Video) - Billy Idol</v>
+        <v>Malcolm Todd - Free.99 (Official Visualizer) - Malcolm Todd</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>'It's Unusual' Official Music Video - Kelly Boesch | 4K</v>
+        <v>Isabel LaRosa - Every Life (Visualizer)</v>
       </c>
       <c r="B88" t="str">
-        <v>11 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=Ru3fB2l1RSo</v>
+        <v>https://www.youtube.com/watch?v=tIQDAtwNAY4</v>
       </c>
       <c r="D88" t="str">
         <v>2026-06-10</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>11 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>Kelly Boesch AI Art</v>
+        <v>Isabel LaRosa</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>'It's Unusual' Official Music Video - Kelly Boesch | 4K - Kelly Boesch AI Art</v>
+        <v>Isabel LaRosa - Every Life (Visualizer) - Isabel LaRosa</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Icona Pop - Butterfly Feelings (Official Video)</v>
+        <v>Wyatt Flores - Half The Man (Official Music Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>7 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=AMW1Zq9RbIU</v>
+        <v>https://www.youtube.com/watch?v=2ChzcWHryFM</v>
       </c>
       <c r="D89" t="str">
         <v>2026-06-10</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>7 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>Icona Pop</v>
+        <v>Wyatt Flores</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Icona Pop - Butterfly Feelings (Official Video) - Icona Pop</v>
+        <v>Wyatt Flores - Half The Man (Official Music Video) - Wyatt Flores</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Hippo Campus - South</v>
+        <v>Mckenna Grace - Ugly and Rotten (Official Music Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>8 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=FYOmFfV7Ojo</v>
+        <v>https://www.youtube.com/watch?v=4yXFVgy7laM</v>
       </c>
       <c r="D90" t="str">
         <v>2026-06-10</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>8 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>Hippo Campus</v>
+        <v>Mckenna Grace</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Hippo Campus - South - Hippo Campus</v>
+        <v>Mckenna Grace - Ugly and Rotten (Official Music Video) - Mckenna Grace</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>elijah woods - Old (Treehouse Sessions)</v>
+        <v>Robert Grace - If You Were Gone ft. Bob Grace (OFFICIAL LYRIC VIDEO)</v>
       </c>
       <c r="B91" t="str">
-        <v>8 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=yDlkPdR_6zM</v>
+        <v>https://www.youtube.com/watch?v=fbpQjMi3Hco</v>
       </c>
       <c r="D91" t="str">
         <v>2026-06-10</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>8 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>elijah woods</v>
+        <v>Robert Grace</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>elijah woods - Old (Treehouse Sessions) - elijah woods</v>
+        <v>Robert Grace - If You Were Gone ft. Bob Grace (OFFICIAL LYRIC VIDEO) - Robert Grace</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Nothing But Thieves - Evolution (Official Video)</v>
+        <v>Boyzone - No Matter What (Live)</v>
       </c>
       <c r="B92" t="str">
-        <v>8 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=hmjfuuuRRYU</v>
+        <v>https://www.youtube.com/watch?v=CEy96_jHw-Q</v>
       </c>
       <c r="D92" t="str">
         <v>2026-06-10</v>
@@ -3871,13 +3871,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>8 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Boyzone</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Nothing But Thieves - Evolution (Official Video) - Nothing But Thieves</v>
+        <v>Boyzone - No Matter What (Live) - Boyzone</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Ariana Grande - hate that i made you love me (official music video)</v>
+        <v>Florrie - The Times (Official Video)</v>
       </c>
       <c r="B93" t="str">
-        <v>8 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=82-jTNka3uc</v>
+        <v>https://www.youtube.com/watch?v=6yBlNUaW7r4</v>
       </c>
       <c r="D93" t="str">
         <v>2026-06-10</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>8 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>Ariana Grande</v>
+        <v>florriemusic</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Ariana Grande - hate that i made you love me (official music video) - Ariana Grande</v>
+        <v>Florrie - The Times (Official Video) - florriemusic</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>LAUREL - Fire Breather</v>
+        <v>Madonna - Love Sensation (Official Visualizer)</v>
       </c>
       <c r="B94" t="str">
-        <v>8 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=rtyavLIJjy0</v>
+        <v>https://www.youtube.com/watch?v=88fD-UtG_yo</v>
       </c>
       <c r="D94" t="str">
         <v>2026-06-10</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>8 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>LAUREL</v>
+        <v>Madonna</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>LAUREL - Fire Breather - LAUREL</v>
+        <v>Madonna - Love Sensation (Official Visualizer) - Madonna</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>The Warning - Ego (Performance Video)</v>
+        <v>DMA'S - Hurracane (Official Video)</v>
       </c>
       <c r="B95" t="str">
-        <v>10 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=7PApWObImjo</v>
+        <v>https://www.youtube.com/watch?v=-zTB57LiXPk</v>
       </c>
       <c r="D95" t="str">
         <v>2026-06-10</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>10 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>The Warning</v>
+        <v>DMA'S</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>The Warning - Ego (Performance Video) - The Warning</v>
+        <v>DMA'S - Hurracane (Official Video) - DMA'S</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (feat. Gabito Ballesteros) [Official Lyric Video]</v>
+        <v>Lainey Wilson and John Mayer - Phone, Keys, Wallet (Official Audio)</v>
       </c>
       <c r="B96" t="str">
-        <v>10 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=vruZSAYJBe4</v>
+        <v>https://www.youtube.com/watch?v=JzW6RnzeF9A</v>
       </c>
       <c r="D96" t="str">
         <v>2026-06-10</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>10 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>Lainey Wilson and John Mayer</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (feat. Gabito Ballesteros) [Official Lyric Video] - David Guetta and Jennifer Lopez</v>
+        <v>Lainey Wilson and John Mayer - Phone, Keys, Wallet (Official Audio) - Lainey Wilson and John Mayer</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Armin van Buuren - Equanimity (from 'Piano' album) [Official Video]</v>
+        <v>ROLE MODEL - High Hopes 3000 (Official Music Video)</v>
       </c>
       <c r="B97" t="str">
-        <v>10 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=k93t10R-Qrg</v>
+        <v>https://www.youtube.com/watch?v=D_KTG0BzRiI</v>
       </c>
       <c r="D97" t="str">
         <v>2026-06-10</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>10 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>Armin van Buuren</v>
+        <v>ROLE MODEL</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Armin van Buuren - Equanimity (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>ROLE MODEL - High Hopes 3000 (Official Music Video) - ROLE MODEL</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>“I Didn’t Know What Time It Was” - Andrew Bird Jazz Trio (Live from The Green Mill)</v>
+        <v>Shawn Mendes - Treat You Better (Live from New York)</v>
       </c>
       <c r="B98" t="str">
-        <v>11 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=XyRgdfXo2nI</v>
+        <v>https://www.youtube.com/watch?v=29bfaHc1XiY</v>
       </c>
       <c r="D98" t="str">
         <v>2026-06-10</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>11 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>Andrew Bird</v>
+        <v>Shawn Mendes</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>“I Didn’t Know What Time It Was” - Andrew Bird Jazz Trio (Live from The Green Mill) - Andrew Bird</v>
+        <v>Shawn Mendes - Treat You Better (Live from New York) - Shawn Mendes</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Danny Gokey - God's Not (Official Music Video)</v>
+        <v>SIENNA SPIRO - The Visitor (Official Music Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>11 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=oGpKqX6ftcU</v>
+        <v>https://www.youtube.com/watch?v=LiYb4WGbp5Y</v>
       </c>
       <c r="D99" t="str">
         <v>2026-06-10</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>11 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>Danny Gokey</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Danny Gokey - God's Not (Official Music Video) - Danny Gokey</v>
+        <v>SIENNA SPIRO - The Visitor (Official Music Video) - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Armik - Brisas (2026 Remaster/Remix) (Exciting Rumba Flamenco, Spanish Guitar)</v>
+        <v>Just Slide Official Music Video | Kelly Boesch | 4K</v>
       </c>
       <c r="B100" t="str">
-        <v>11 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=51Zu2iU2z2Q</v>
+        <v>https://www.youtube.com/watch?v=lC14fuU8aPc</v>
       </c>
       <c r="D100" t="str">
         <v>2026-06-10</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>11 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>Armik</v>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Armik - Brisas (2026 Remaster/Remix) (Exciting Rumba Flamenco, Spanish Guitar) - Armik</v>
+        <v>Just Slide Official Music Video | Kelly Boesch | 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Holly Humberstone - Lucy (Free People Sessions)</v>
+        <v>Europe - The Cult of Ignorance (Official Video)</v>
       </c>
       <c r="B101" t="str">
-        <v>11 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=c1GR2TTs9W8</v>
+        <v>https://www.youtube.com/watch?v=p-IOsjOJpnA</v>
       </c>
       <c r="D101" t="str">
         <v>2026-06-10</v>
@@ -4213,13 +4213,13 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>11 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G101" t="str">
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Holly Humberstone and Free People</v>
+        <v>Europe</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,7 +4231,7 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Holly Humberstone - Lucy (Free People Sessions) - Holly Humberstone and Free People</v>
+        <v>Europe - The Cult of Ignorance (Official Video) - Europe</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-06-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-06-week02/titles.xlsx
@@ -439,19 +439,19 @@
         <v>Niall Horan feat. Myles Smith - Drive Safe (Live at Capital's Summertime Ball 2026) | Capital</v>
       </c>
       <c r="B2" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=mmu5Vh4hMu0</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,19 +477,19 @@
         <v>Gia Ford - At Least For Now</v>
       </c>
       <c r="B3" t="str">
-        <v>14h ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=u2U0gUeCE5M</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>14h ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,19 +515,19 @@
         <v>Emilia Tarrant - The Three Words / Better Together (Live at Bread &amp; Butter Lounge)</v>
       </c>
       <c r="B4" t="str">
-        <v>18h ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=pE5wZRhY0P0</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>18h ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,19 +553,19 @@
         <v>Rodrigo y Gabriela - Monster (Official Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>18h ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=Wolzo63vons</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>18h ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,19 +591,19 @@
         <v>Max McNown - Done For (Performance Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>18h ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=L1SxYiMiZEM</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E6" t="str">
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>18h ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,19 +629,19 @@
         <v>Julia Cole - Big Picture (Official Lyric Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>23h ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=M7LF0hhoPoc</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E7" t="str">
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>23h ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -667,19 +667,19 @@
         <v>Joalin - On A Day Like This</v>
       </c>
       <c r="B8" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=VWLPWi9edlQ</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E8" t="str">
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,19 +705,19 @@
         <v>RAYE - Click Clack Symphony (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B9" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=_TUh78OrzSM</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -743,19 +743,19 @@
         <v>Vera Blue - Rituals (Official Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=zJ2HNWcNauU</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E10" t="str">
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -781,19 +781,19 @@
         <v>Wishy - Lovesick (Official Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=q_WXgLn8sVw</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E11" t="str">
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -819,19 +819,19 @@
         <v>Jason Derulo - In My Head (Live at Capital's Summertime Ball 2026) | Capital</v>
       </c>
       <c r="B12" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=LudSER6wECQ</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E12" t="str">
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -857,19 +857,19 @@
         <v>RAYE - Beware.. The South London Lover Boy. (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B13" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=TxlMo7pbCOs</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E13" t="str">
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -895,19 +895,19 @@
         <v>Niall Horan - This Town (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B14" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=6TO_ITkIgBI</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E14" t="str">
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -933,19 +933,19 @@
         <v>Soft Cell - Danceteria (Official Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=P4kE8CNvoOw</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E15" t="str">
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,19 +971,19 @@
         <v>Take That - Greatest Day (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B16" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=3dwS84ONnZ0</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E16" t="str">
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1009,19 +1009,19 @@
         <v>Take That - You're A Superstar (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B17" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=g_KsWUl-nxw</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E17" t="str">
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1047,19 +1047,19 @@
         <v>Jessie J - CALIFORNIA (Official Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=tN1mV6mCJ3k</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E18" t="str">
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1085,19 +1085,19 @@
         <v>Olivia Rodrigo - the cure (performance video)</v>
       </c>
       <c r="B19" t="str">
-        <v>1d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=OA2YUsJyQI0</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E19" t="str">
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>1d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,19 +1123,19 @@
         <v>XG - Something Ain’t Right (Live at Capital's Summertime Ball 2026) | Capital</v>
       </c>
       <c r="B20" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=BWASDZZtO6w</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E20" t="str">
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1161,19 +1161,19 @@
         <v>Freya Ridings - Wild Horse (Official Lyric Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=IpkgL5oZbbU</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E21" t="str">
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1199,19 +1199,19 @@
         <v>Myles Smith - Hold Me In The Dark (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B22" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=uVh2WwmC7Sw</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E22" t="str">
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1237,19 +1237,19 @@
         <v>Niall Horan - Heaven (Live at Capital's Summertime Ball 2026) | Capital</v>
       </c>
       <c r="B23" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=CTmWK2o3mXY</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E23" t="str">
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1275,19 +1275,19 @@
         <v>Strange AI Art Installations</v>
       </c>
       <c r="B24" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=KnOVECFvkMM</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E24" t="str">
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1313,19 +1313,19 @@
         <v>Robyn - Talk To Me (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B25" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=KQigrpSdFPY</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E25" t="str">
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1351,19 +1351,19 @@
         <v>Nora Fatehi, Vegedream, Sanjoy, FIFA Sound - Siir Siir (FIFA World Cup 2026™) [Official Music Video]</v>
       </c>
       <c r="B26" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=afiNbSxg7aw</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E26" t="str">
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1389,19 +1389,19 @@
         <v>Jason Derulo - Want To Want Me (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B27" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=QprQP1fdrDM</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E27" t="str">
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1427,19 +1427,19 @@
         <v>Jason Derulo - The Other Side (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B28" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=ym-h0EIlL3A</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E28" t="str">
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1465,19 +1465,19 @@
         <v>Stephen Sanchez - Be More (Live at Capital's Summertime Ball 2026) | Capital</v>
       </c>
       <c r="B29" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=bIwcNmu-rAg</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E29" t="str">
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1503,19 +1503,19 @@
         <v>Jason Derulo - Take You Dancing (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B30" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=oLzj8E8fHRQ</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E30" t="str">
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1541,19 +1541,19 @@
         <v>Sekou - Someone Like You (Adele Cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B31" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=YIy2g4enMiY</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E31" t="str">
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1579,19 +1579,19 @@
         <v>Sienna Spiro - He's Not My Baby, I'm His (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B32" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=NhuPT6MR2XU</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E32" t="str">
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1617,19 +1617,19 @@
         <v>DEEP PURPLE - DIABLO (Official Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=Z4RpBEg5uis</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E33" t="str">
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1655,19 +1655,19 @@
         <v>Reba McEntire - You Never Gave Up On Me</v>
       </c>
       <c r="B34" t="str">
-        <v>2d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=AUCRUStLmJM</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E34" t="str">
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>2d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1693,19 +1693,19 @@
         <v>elijah woods - Wonder (Official Lyric Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=sDDbD4R-xD4</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E35" t="str">
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1731,19 +1731,19 @@
         <v>XG - Flowers (Sweet Female Attitude Cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B36" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=MxJQoyKh8TQ</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E36" t="str">
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1769,19 +1769,19 @@
         <v>Niall Horan - Nice To Meet Ya (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B37" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=-UIkkGxMQG8</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E37" t="str">
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1807,19 +1807,19 @@
         <v>Niall Horan - Steal My Girl (One Direction cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B38" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=b_uO5ROpk_0</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E38" t="str">
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1845,19 +1845,19 @@
         <v>Niall Horan - Dinner Party (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B39" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=hSJfAFpdllk</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E39" t="str">
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1883,19 +1883,19 @@
         <v>Niall Horan - Slow Hands (Live at Capital's Summertime Ball 2026) | Capital</v>
       </c>
       <c r="B40" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=vdMK2DvnWJI</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E40" t="str">
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1921,19 +1921,19 @@
         <v>RAYE - Joy (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B41" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=5gvhRAGaOUo</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E41" t="str">
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1959,19 +1959,19 @@
         <v>Myles Smith - Stargazing (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B42" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=2AIMnAPxqfw</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E42" t="str">
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -1997,19 +1997,19 @@
         <v>Lola Young - From Down Here (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B43" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=UD7HkkAbnVA</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E43" t="str">
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2035,19 +2035,19 @@
         <v>XG - Hypnotize (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B44" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=c5u3ur4vLo0</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E44" t="str">
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2073,19 +2073,19 @@
         <v>Sienna Spiro - Die On This Hill (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B45" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=UhWumamExiI</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E45" t="str">
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2111,19 +2111,19 @@
         <v>RAYE - Where Is My Husband? (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B46" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=Z_HR2ZYY1VA</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E46" t="str">
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2149,19 +2149,19 @@
         <v>Take That - Never Forget (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B47" t="str">
-        <v>3d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=9S61JkOZLe8</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E47" t="str">
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>3d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2187,19 +2187,19 @@
         <v>Robyn - Dancing On My Own (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B48" t="str">
-        <v>3d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=_4SfgNPngbo</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E48" t="str">
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>3d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2225,19 +2225,19 @@
         <v>Take That - Patience (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B49" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=_I9qIxmrDuI</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E49" t="str">
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2263,19 +2263,19 @@
         <v>Mis-Teeq - Full Set (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B50" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=5AyQM_coDb8</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E50" t="str">
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2301,19 +2301,19 @@
         <v>Take That - Rule The World (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B51" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=0nc-qdhh6eU</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E51" t="str">
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2339,19 +2339,19 @@
         <v>Sienna Spiro - Material Lover (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B52" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=dZjAtTc9DBQ</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E52" t="str">
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2377,19 +2377,19 @@
         <v>Take That - Shine (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B53" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=T6TmxqOGIf0</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E53" t="str">
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2415,19 +2415,19 @@
         <v>MEEK - Dracula (Tame Impala Cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B54" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=4jnM--XhsC0</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E54" t="str">
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2453,19 +2453,19 @@
         <v>Lola Young - Messy (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B55" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=cUvsaKkjHYQ</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E55" t="str">
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2491,19 +2491,19 @@
         <v>Stephen Sanchez - Until I Found You (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B56" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=oKKNK0OCpQk</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E56" t="str">
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2529,19 +2529,19 @@
         <v>Lola Young - One Thing (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B57" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=nhL2l4HCiRg</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E57" t="str">
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2567,19 +2567,19 @@
         <v>Bebe Rexha - Sad Girls (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B58" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=e0PkSQNMcGs</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E58" t="str">
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2605,19 +2605,19 @@
         <v>Robyn - Dopamine (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B59" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=-7mPIus0U5Y</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E59" t="str">
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2643,19 +2643,19 @@
         <v>Jason Derulo - Trumpets (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B60" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=QkCKENp-4Rs</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E60" t="str">
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2681,19 +2681,19 @@
         <v>Jason Derulo - Whatcha Say (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B61" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=jsFekVlEaSA</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E61" t="str">
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2719,19 +2719,19 @@
         <v>Bebe Rexha - New Religion (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B62" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=nfDKQ09bY_w</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E62" t="str">
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2757,19 +2757,19 @@
         <v>Bebe Rexha - I'm Good (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B63" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=eqceDkaK3PU</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E63" t="str">
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2795,19 +2795,19 @@
         <v>Strange Surreal AI - In Here - Kelly Boesch | 4K</v>
       </c>
       <c r="B64" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=QCNwFDTkfYU</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E64" t="str">
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2833,19 +2833,19 @@
         <v>The Cranberries - Scenes From 'Linger' (The Only Color Reel)</v>
       </c>
       <c r="B65" t="str">
-        <v>4d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=5-peG8H-lqE</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E65" t="str">
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>4d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2871,19 +2871,19 @@
         <v>Jordana Bryant - Too Little Too Late (Official Lyric Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=P26-NjdBmbU</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E66" t="str">
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2909,19 +2909,19 @@
         <v>Grace Enger - "Running Back To You" (Official Music Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=BON1BSWLntE</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E67" t="str">
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2947,19 +2947,19 @@
         <v>The Offspring - Gone Away | Live at BeachLife Festival 2026</v>
       </c>
       <c r="B68" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=UTw106Ivz8o</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E68" t="str">
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -2985,19 +2985,19 @@
         <v>Lola Young – From Down Here (From The Pool)</v>
       </c>
       <c r="B69" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=YFhpMpONGUY</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E69" t="str">
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3023,19 +3023,19 @@
         <v>CAIN - Living Water (Music Video)</v>
       </c>
       <c r="B70" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=WrsXAfnTAdA</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E70" t="str">
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3061,19 +3061,19 @@
         <v>B.B. King &amp; Eric Clapton - Riding With The King (Official Music Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=L7Ls8ceHxhc</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E71" t="str">
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3099,19 +3099,19 @@
         <v>Blu DeTiger - Whisper (Official Music Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=OfcBfPnskG4</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E72" t="str">
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3137,19 +3137,19 @@
         <v>Romeo Santos, Prince Royce - Ay! San Miguel (Official Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=-uvNvVtUidc</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E73" t="str">
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3175,19 +3175,19 @@
         <v>Pink Floyd - Pigs on the Wing (8-Track Version - Official Audio)</v>
       </c>
       <c r="B74" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=WZUKJ90i6Tw</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E74" t="str">
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3213,19 +3213,19 @@
         <v>Holly Humberstone - it’s just White Noise</v>
       </c>
       <c r="B75" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=KeRZtPUjl8g</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E75" t="str">
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3251,19 +3251,19 @@
         <v>Freya Ridings - Mother Of Pearl (Official Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=So5gx12fCsA</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E76" t="str">
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3289,19 +3289,19 @@
         <v>MUSE - Nightshift Superstar (Official Music Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=p--xk9n1eIM</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E77" t="str">
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -3327,19 +3327,19 @@
         <v>Ellie Goulding - Black Prada Dress (Visualiser)</v>
       </c>
       <c r="B78" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=zr9CYpgPueI</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E78" t="str">
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -3365,19 +3365,19 @@
         <v>Evanescence - Sanctuary (Official Visualizer)</v>
       </c>
       <c r="B79" t="str">
-        <v>5d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=E64jOWeVfpg</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E79" t="str">
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>5d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -3403,19 +3403,19 @@
         <v>The Beaches - Perfect 10 (Official Visualizer)</v>
       </c>
       <c r="B80" t="str">
-        <v>5d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=N7TOR_l-CM8</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E80" t="str">
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>5d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -3441,19 +3441,19 @@
         <v>Bella White - Stuff (Official Music Video)</v>
       </c>
       <c r="B81" t="str">
-        <v>5d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=7QZtxsGBTks</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E81" t="str">
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>5d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -3479,19 +3479,19 @@
         <v>Meduza, Rani - Silence (Official Visualizer)</v>
       </c>
       <c r="B82" t="str">
-        <v>5d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=cIdqz-WMod4</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E82" t="str">
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>5d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -3517,19 +3517,19 @@
         <v>CAIN - Living Water (Lyric Video)</v>
       </c>
       <c r="B83" t="str">
-        <v>5d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=Hv-8CM5NIPM</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E83" t="str">
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>5d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -3555,19 +3555,19 @@
         <v>Fitz and the Tantrums - Greenlight (Official Visualizer)</v>
       </c>
       <c r="B84" t="str">
-        <v>5d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=Zx-ZPBbcA58</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E84" t="str">
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>5d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -3593,19 +3593,19 @@
         <v>Jeremy Camp - Reflector (Official Music Video)</v>
       </c>
       <c r="B85" t="str">
-        <v>5d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=SR-4q1yiYNA</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E85" t="str">
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>5d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -3631,19 +3631,19 @@
         <v>Alesso, OneRepublic - In Your Eyes (Visualizer)</v>
       </c>
       <c r="B86" t="str">
-        <v>5d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=bS9C1ipyMy8</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E86" t="str">
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>5d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -3669,19 +3669,19 @@
         <v>Malcolm Todd - Free.99 (Official Visualizer)</v>
       </c>
       <c r="B87" t="str">
-        <v>5d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=wBBQptUsOhw</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E87" t="str">
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>5d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -3707,19 +3707,19 @@
         <v>Isabel LaRosa - Every Life (Visualizer)</v>
       </c>
       <c r="B88" t="str">
-        <v>5d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=tIQDAtwNAY4</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E88" t="str">
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>5d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -3745,19 +3745,19 @@
         <v>Wyatt Flores - Half The Man (Official Music Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>5d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=2ChzcWHryFM</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E89" t="str">
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>5d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -3783,19 +3783,19 @@
         <v>Mckenna Grace - Ugly and Rotten (Official Music Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>5d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=4yXFVgy7laM</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E90" t="str">
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>5d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -3821,19 +3821,19 @@
         <v>Robert Grace - If You Were Gone ft. Bob Grace (OFFICIAL LYRIC VIDEO)</v>
       </c>
       <c r="B91" t="str">
-        <v>5d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=fbpQjMi3Hco</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E91" t="str">
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>5d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -3859,19 +3859,19 @@
         <v>Boyzone - No Matter What (Live)</v>
       </c>
       <c r="B92" t="str">
-        <v>5d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=CEy96_jHw-Q</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E92" t="str">
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>5d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -3897,19 +3897,19 @@
         <v>Florrie - The Times (Official Video)</v>
       </c>
       <c r="B93" t="str">
-        <v>5d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=6yBlNUaW7r4</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E93" t="str">
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>5d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -3935,19 +3935,19 @@
         <v>Madonna - Love Sensation (Official Visualizer)</v>
       </c>
       <c r="B94" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=88fD-UtG_yo</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E94" t="str">
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -3973,19 +3973,19 @@
         <v>DMA'S - Hurracane (Official Video)</v>
       </c>
       <c r="B95" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C95" t="str">
         <v>https://www.youtube.com/watch?v=-zTB57LiXPk</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E95" t="str">
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -4011,19 +4011,19 @@
         <v>Lainey Wilson and John Mayer - Phone, Keys, Wallet (Official Audio)</v>
       </c>
       <c r="B96" t="str">
-        <v>6d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C96" t="str">
         <v>https://www.youtube.com/watch?v=JzW6RnzeF9A</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E96" t="str">
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>6d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -4049,19 +4049,19 @@
         <v>ROLE MODEL - High Hopes 3000 (Official Music Video)</v>
       </c>
       <c r="B97" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=D_KTG0BzRiI</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E97" t="str">
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -4087,19 +4087,19 @@
         <v>Shawn Mendes - Treat You Better (Live from New York)</v>
       </c>
       <c r="B98" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=29bfaHc1XiY</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E98" t="str">
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -4125,19 +4125,19 @@
         <v>SIENNA SPIRO - The Visitor (Official Music Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C99" t="str">
         <v>https://www.youtube.com/watch?v=LiYb4WGbp5Y</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E99" t="str">
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
@@ -4163,19 +4163,19 @@
         <v>Just Slide Official Music Video | Kelly Boesch | 4K</v>
       </c>
       <c r="B100" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=lC14fuU8aPc</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E100" t="str">
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -4201,19 +4201,19 @@
         <v>Europe - The Cult of Ignorance (Official Video)</v>
       </c>
       <c r="B101" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=p-IOsjOJpnA</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E101" t="str">
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G101" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-06-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-06-week02/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Niall Horan feat. Myles Smith - Drive Safe (Live at Capital's Summertime Ball 2026) | Capital</v>
       </c>
       <c r="B2" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=mmu5Vh4hMu0</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,7 +477,7 @@
         <v>Gia Ford - At Least For Now</v>
       </c>
       <c r="B3" t="str">
-        <v>20 hours ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=u2U0gUeCE5M</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>20 hours ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,7 +515,7 @@
         <v>Emilia Tarrant - The Three Words / Better Together (Live at Bread &amp; Butter Lounge)</v>
       </c>
       <c r="B4" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=pE5wZRhY0P0</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>Rodrigo y Gabriela - Monster (Official Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=Wolzo63vons</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,7 +591,7 @@
         <v>Max McNown - Done For (Performance Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=L1SxYiMiZEM</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,7 +629,7 @@
         <v>Julia Cole - Big Picture (Official Lyric Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=M7LF0hhoPoc</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>Joalin - On A Day Like This</v>
       </c>
       <c r="B8" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=VWLPWi9edlQ</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,7 +705,7 @@
         <v>RAYE - Click Clack Symphony (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B9" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=_TUh78OrzSM</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -743,7 +743,7 @@
         <v>Vera Blue - Rituals (Official Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=zJ2HNWcNauU</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -781,7 +781,7 @@
         <v>Wishy - Lovesick (Official Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=q_WXgLn8sVw</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -819,7 +819,7 @@
         <v>Jason Derulo - In My Head (Live at Capital's Summertime Ball 2026) | Capital</v>
       </c>
       <c r="B12" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=LudSER6wECQ</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -857,7 +857,7 @@
         <v>RAYE - Beware.. The South London Lover Boy. (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B13" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=TxlMo7pbCOs</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -895,7 +895,7 @@
         <v>Niall Horan - This Town (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B14" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=6TO_ITkIgBI</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -933,7 +933,7 @@
         <v>Soft Cell - Danceteria (Official Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=P4kE8CNvoOw</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,7 +971,7 @@
         <v>Take That - Greatest Day (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B16" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=3dwS84ONnZ0</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1009,7 +1009,7 @@
         <v>Take That - You're A Superstar (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B17" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=g_KsWUl-nxw</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1047,7 +1047,7 @@
         <v>Jessie J - CALIFORNIA (Official Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=tN1mV6mCJ3k</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1085,7 +1085,7 @@
         <v>Olivia Rodrigo - the cure (performance video)</v>
       </c>
       <c r="B19" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=OA2YUsJyQI0</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,7 +1123,7 @@
         <v>XG - Something Ain’t Right (Live at Capital's Summertime Ball 2026) | Capital</v>
       </c>
       <c r="B20" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=BWASDZZtO6w</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1161,7 +1161,7 @@
         <v>Freya Ridings - Wild Horse (Official Lyric Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=IpkgL5oZbbU</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1199,7 +1199,7 @@
         <v>Myles Smith - Hold Me In The Dark (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B22" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=uVh2WwmC7Sw</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1237,7 +1237,7 @@
         <v>Niall Horan - Heaven (Live at Capital's Summertime Ball 2026) | Capital</v>
       </c>
       <c r="B23" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=CTmWK2o3mXY</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1275,7 +1275,7 @@
         <v>Strange AI Art Installations</v>
       </c>
       <c r="B24" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=KnOVECFvkMM</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1313,7 +1313,7 @@
         <v>Robyn - Talk To Me (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B25" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=KQigrpSdFPY</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1351,7 +1351,7 @@
         <v>Nora Fatehi, Vegedream, Sanjoy, FIFA Sound - Siir Siir (FIFA World Cup 2026™) [Official Music Video]</v>
       </c>
       <c r="B26" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=afiNbSxg7aw</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1389,7 +1389,7 @@
         <v>Jason Derulo - Want To Want Me (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B27" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=QprQP1fdrDM</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1427,7 +1427,7 @@
         <v>Jason Derulo - The Other Side (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B28" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=ym-h0EIlL3A</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1465,7 +1465,7 @@
         <v>Stephen Sanchez - Be More (Live at Capital's Summertime Ball 2026) | Capital</v>
       </c>
       <c r="B29" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=bIwcNmu-rAg</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1503,7 +1503,7 @@
         <v>Jason Derulo - Take You Dancing (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B30" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=oLzj8E8fHRQ</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1541,7 +1541,7 @@
         <v>Sekou - Someone Like You (Adele Cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B31" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=YIy2g4enMiY</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1579,7 +1579,7 @@
         <v>Sienna Spiro - He's Not My Baby, I'm His (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B32" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=NhuPT6MR2XU</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1617,7 +1617,7 @@
         <v>DEEP PURPLE - DIABLO (Official Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=Z4RpBEg5uis</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1655,7 +1655,7 @@
         <v>Reba McEntire - You Never Gave Up On Me</v>
       </c>
       <c r="B34" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=AUCRUStLmJM</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1693,7 +1693,7 @@
         <v>elijah woods - Wonder (Official Lyric Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=sDDbD4R-xD4</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1731,7 +1731,7 @@
         <v>XG - Flowers (Sweet Female Attitude Cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B36" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=MxJQoyKh8TQ</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1769,7 +1769,7 @@
         <v>Niall Horan - Nice To Meet Ya (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B37" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=-UIkkGxMQG8</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1807,7 +1807,7 @@
         <v>Niall Horan - Steal My Girl (One Direction cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B38" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=b_uO5ROpk_0</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1845,7 +1845,7 @@
         <v>Niall Horan - Dinner Party (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B39" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=hSJfAFpdllk</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1883,7 +1883,7 @@
         <v>Niall Horan - Slow Hands (Live at Capital's Summertime Ball 2026) | Capital</v>
       </c>
       <c r="B40" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=vdMK2DvnWJI</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1921,7 +1921,7 @@
         <v>RAYE - Joy (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B41" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=5gvhRAGaOUo</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1959,7 +1959,7 @@
         <v>Myles Smith - Stargazing (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B42" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=2AIMnAPxqfw</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -1997,7 +1997,7 @@
         <v>Lola Young - From Down Here (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B43" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=UD7HkkAbnVA</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2035,7 +2035,7 @@
         <v>XG - Hypnotize (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B44" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=c5u3ur4vLo0</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2073,7 +2073,7 @@
         <v>Sienna Spiro - Die On This Hill (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B45" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=UhWumamExiI</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2111,7 +2111,7 @@
         <v>RAYE - Where Is My Husband? (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B46" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=Z_HR2ZYY1VA</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2149,7 +2149,7 @@
         <v>Take That - Never Forget (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B47" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=9S61JkOZLe8</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2187,7 +2187,7 @@
         <v>Robyn - Dancing On My Own (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B48" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=_4SfgNPngbo</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2225,7 +2225,7 @@
         <v>Take That - Patience (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B49" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=_I9qIxmrDuI</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2263,7 +2263,7 @@
         <v>Mis-Teeq - Full Set (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B50" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=5AyQM_coDb8</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2301,7 +2301,7 @@
         <v>Take That - Rule The World (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B51" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=0nc-qdhh6eU</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2339,7 +2339,7 @@
         <v>Sienna Spiro - Material Lover (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B52" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=dZjAtTc9DBQ</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2377,7 +2377,7 @@
         <v>Take That - Shine (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B53" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=T6TmxqOGIf0</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2415,7 +2415,7 @@
         <v>MEEK - Dracula (Tame Impala Cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B54" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=4jnM--XhsC0</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2453,7 +2453,7 @@
         <v>Lola Young - Messy (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B55" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=cUvsaKkjHYQ</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2491,7 +2491,7 @@
         <v>Stephen Sanchez - Until I Found You (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B56" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=oKKNK0OCpQk</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2529,7 +2529,7 @@
         <v>Lola Young - One Thing (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B57" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=nhL2l4HCiRg</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2567,7 +2567,7 @@
         <v>Bebe Rexha - Sad Girls (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B58" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=e0PkSQNMcGs</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2605,7 +2605,7 @@
         <v>Robyn - Dopamine (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B59" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=-7mPIus0U5Y</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2643,7 +2643,7 @@
         <v>Jason Derulo - Trumpets (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B60" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=QkCKENp-4Rs</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2681,7 +2681,7 @@
         <v>Jason Derulo - Whatcha Say (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B61" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=jsFekVlEaSA</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2719,7 +2719,7 @@
         <v>Bebe Rexha - New Religion (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B62" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=nfDKQ09bY_w</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2757,7 +2757,7 @@
         <v>Bebe Rexha - I'm Good (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B63" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=eqceDkaK3PU</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2795,7 +2795,7 @@
         <v>Strange Surreal AI - In Here - Kelly Boesch | 4K</v>
       </c>
       <c r="B64" t="str">
-        <v>5 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=QCNwFDTkfYU</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>5 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2833,7 +2833,7 @@
         <v>The Cranberries - Scenes From 'Linger' (The Only Color Reel)</v>
       </c>
       <c r="B65" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=5-peG8H-lqE</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2871,7 +2871,7 @@
         <v>Jordana Bryant - Too Little Too Late (Official Lyric Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=P26-NjdBmbU</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2909,7 +2909,7 @@
         <v>Grace Enger - "Running Back To You" (Official Music Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=BON1BSWLntE</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2947,7 +2947,7 @@
         <v>The Offspring - Gone Away | Live at BeachLife Festival 2026</v>
       </c>
       <c r="B68" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=UTw106Ivz8o</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -2985,7 +2985,7 @@
         <v>Lola Young – From Down Here (From The Pool)</v>
       </c>
       <c r="B69" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=YFhpMpONGUY</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3023,7 +3023,7 @@
         <v>CAIN - Living Water (Music Video)</v>
       </c>
       <c r="B70" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=WrsXAfnTAdA</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3061,7 +3061,7 @@
         <v>B.B. King &amp; Eric Clapton - Riding With The King (Official Music Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>5 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=L7Ls8ceHxhc</v>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>5 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3099,7 +3099,7 @@
         <v>Blu DeTiger - Whisper (Official Music Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>5 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=OfcBfPnskG4</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>5 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3137,7 +3137,7 @@
         <v>Romeo Santos, Prince Royce - Ay! San Miguel (Official Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>5 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=-uvNvVtUidc</v>
@@ -3149,7 +3149,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>5 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3175,7 +3175,7 @@
         <v>Pink Floyd - Pigs on the Wing (8-Track Version - Official Audio)</v>
       </c>
       <c r="B74" t="str">
-        <v>5 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=WZUKJ90i6Tw</v>
@@ -3187,7 +3187,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>5 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3213,7 +3213,7 @@
         <v>Holly Humberstone - it’s just White Noise</v>
       </c>
       <c r="B75" t="str">
-        <v>5 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=KeRZtPUjl8g</v>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>5 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3251,7 +3251,7 @@
         <v>Freya Ridings - Mother Of Pearl (Official Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>5 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=So5gx12fCsA</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>5 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3289,7 +3289,7 @@
         <v>MUSE - Nightshift Superstar (Official Music Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>5 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=p--xk9n1eIM</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>5 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -3327,7 +3327,7 @@
         <v>Ellie Goulding - Black Prada Dress (Visualiser)</v>
       </c>
       <c r="B78" t="str">
-        <v>5 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=zr9CYpgPueI</v>
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>5 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -3365,7 +3365,7 @@
         <v>Evanescence - Sanctuary (Official Visualizer)</v>
       </c>
       <c r="B79" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=E64jOWeVfpg</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -3403,7 +3403,7 @@
         <v>The Beaches - Perfect 10 (Official Visualizer)</v>
       </c>
       <c r="B80" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=N7TOR_l-CM8</v>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -3441,7 +3441,7 @@
         <v>Bella White - Stuff (Official Music Video)</v>
       </c>
       <c r="B81" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=7QZtxsGBTks</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -3479,7 +3479,7 @@
         <v>Meduza, Rani - Silence (Official Visualizer)</v>
       </c>
       <c r="B82" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=cIdqz-WMod4</v>
@@ -3491,7 +3491,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -3517,7 +3517,7 @@
         <v>CAIN - Living Water (Lyric Video)</v>
       </c>
       <c r="B83" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=Hv-8CM5NIPM</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -3555,7 +3555,7 @@
         <v>Fitz and the Tantrums - Greenlight (Official Visualizer)</v>
       </c>
       <c r="B84" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=Zx-ZPBbcA58</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -3593,7 +3593,7 @@
         <v>Jeremy Camp - Reflector (Official Music Video)</v>
       </c>
       <c r="B85" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=SR-4q1yiYNA</v>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -3631,7 +3631,7 @@
         <v>Alesso, OneRepublic - In Your Eyes (Visualizer)</v>
       </c>
       <c r="B86" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=bS9C1ipyMy8</v>
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -3669,7 +3669,7 @@
         <v>Malcolm Todd - Free.99 (Official Visualizer)</v>
       </c>
       <c r="B87" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=wBBQptUsOhw</v>
@@ -3681,7 +3681,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -3707,7 +3707,7 @@
         <v>Isabel LaRosa - Every Life (Visualizer)</v>
       </c>
       <c r="B88" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=tIQDAtwNAY4</v>
@@ -3719,7 +3719,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -3745,7 +3745,7 @@
         <v>Wyatt Flores - Half The Man (Official Music Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=2ChzcWHryFM</v>
@@ -3757,7 +3757,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -3783,7 +3783,7 @@
         <v>Mckenna Grace - Ugly and Rotten (Official Music Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=4yXFVgy7laM</v>
@@ -3795,7 +3795,7 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -3821,7 +3821,7 @@
         <v>Robert Grace - If You Were Gone ft. Bob Grace (OFFICIAL LYRIC VIDEO)</v>
       </c>
       <c r="B91" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=fbpQjMi3Hco</v>
@@ -3833,7 +3833,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -3859,7 +3859,7 @@
         <v>Boyzone - No Matter What (Live)</v>
       </c>
       <c r="B92" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=CEy96_jHw-Q</v>
@@ -3871,7 +3871,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -3897,7 +3897,7 @@
         <v>Florrie - The Times (Official Video)</v>
       </c>
       <c r="B93" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=6yBlNUaW7r4</v>
@@ -3909,7 +3909,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -3935,7 +3935,7 @@
         <v>Madonna - Love Sensation (Official Visualizer)</v>
       </c>
       <c r="B94" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=88fD-UtG_yo</v>
@@ -3947,7 +3947,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -3973,7 +3973,7 @@
         <v>DMA'S - Hurracane (Official Video)</v>
       </c>
       <c r="B95" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C95" t="str">
         <v>https://www.youtube.com/watch?v=-zTB57LiXPk</v>
@@ -3985,7 +3985,7 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -4011,7 +4011,7 @@
         <v>Lainey Wilson and John Mayer - Phone, Keys, Wallet (Official Audio)</v>
       </c>
       <c r="B96" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C96" t="str">
         <v>https://www.youtube.com/watch?v=JzW6RnzeF9A</v>
@@ -4023,7 +4023,7 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -4049,7 +4049,7 @@
         <v>ROLE MODEL - High Hopes 3000 (Official Music Video)</v>
       </c>
       <c r="B97" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=D_KTG0BzRiI</v>
@@ -4061,7 +4061,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -4087,7 +4087,7 @@
         <v>Shawn Mendes - Treat You Better (Live from New York)</v>
       </c>
       <c r="B98" t="str">
-        <v>7 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=29bfaHc1XiY</v>
@@ -4099,7 +4099,7 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>7 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -4125,7 +4125,7 @@
         <v>SIENNA SPIRO - The Visitor (Official Music Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>7 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C99" t="str">
         <v>https://www.youtube.com/watch?v=LiYb4WGbp5Y</v>
@@ -4137,7 +4137,7 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>7 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
@@ -4163,7 +4163,7 @@
         <v>Just Slide Official Music Video | Kelly Boesch | 4K</v>
       </c>
       <c r="B100" t="str">
-        <v>7 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=lC14fuU8aPc</v>
@@ -4175,7 +4175,7 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>7 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -4201,7 +4201,7 @@
         <v>Europe - The Cult of Ignorance (Official Video)</v>
       </c>
       <c r="B101" t="str">
-        <v>7 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=p-IOsjOJpnA</v>
@@ -4213,7 +4213,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>7 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G101" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-06-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/youtube-playlist/2026-06-week02/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Niall Horan feat. Myles Smith - Drive Safe (Live at Capital's Summertime Ball 2026) | Capital</v>
+        <v>Train - Pennsylvania Turnpike (Official Music Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>2d ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=mmu5Vh4hMu0</v>
+        <v>https://www.youtube.com/watch?v=4hbRnRtIKS8</v>
       </c>
       <c r="D2" t="str">
         <v>2026-06-11</v>
@@ -451,13 +451,13 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>2d ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>Capital FM</v>
+        <v>Train</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Niall Horan feat. Myles Smith - Drive Safe (Live at Capital's Summertime Ball 2026) | Capital - Capital FM</v>
+        <v>Train - Pennsylvania Turnpike (Official Music Video) - Train</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Gia Ford - At Least For Now</v>
+        <v>Colorful Surreal Scenes - Art In Motion - Kelly Boesch - 4K</v>
       </c>
       <c r="B3" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=u2U0gUeCE5M</v>
+        <v>https://www.youtube.com/watch?v=Ng0ifYxPAYA</v>
       </c>
       <c r="D3" t="str">
         <v>2026-06-11</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>Gia Ford</v>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Gia Ford - At Least For Now - Gia Ford</v>
+        <v>Colorful Surreal Scenes - Art In Motion - Kelly Boesch - 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Emilia Tarrant - The Three Words / Better Together (Live at Bread &amp; Butter Lounge)</v>
+        <v>Mumford &amp; Sons - Here (Amazon Music Songline)</v>
       </c>
       <c r="B4" t="str">
-        <v>1d ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=pE5wZRhY0P0</v>
+        <v>https://www.youtube.com/watch?v=TkMKLVr0QZ0</v>
       </c>
       <c r="D4" t="str">
         <v>2026-06-11</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>1d ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>Emilia Tarrant</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Emilia Tarrant - The Three Words / Better Together (Live at Bread &amp; Butter Lounge) - Emilia Tarrant</v>
+        <v>Mumford &amp; Sons - Here (Amazon Music Songline) - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Rodrigo y Gabriela - Monster (Official Video)</v>
+        <v>Calvin Harris, Jazzy - Satisfy (Official Visualiser)</v>
       </c>
       <c r="B5" t="str">
-        <v>1d ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=Wolzo63vons</v>
+        <v>https://www.youtube.com/watch?v=GEqcQnf05cw</v>
       </c>
       <c r="D5" t="str">
         <v>2026-06-11</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>1d ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>Rodrigo y Gabriela</v>
+        <v>Calvin Harris</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Rodrigo y Gabriela - Monster (Official Video) - Rodrigo y Gabriela</v>
+        <v>Calvin Harris, Jazzy - Satisfy (Official Visualiser) - Calvin Harris</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Max McNown - Done For (Performance Video)</v>
+        <v>Towa Bird - Dog [Live From Sid The Cat]</v>
       </c>
       <c r="B6" t="str">
-        <v>1d ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=L1SxYiMiZEM</v>
+        <v>https://www.youtube.com/watch?v=t7am4WvgSRk</v>
       </c>
       <c r="D6" t="str">
         <v>2026-06-11</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>1d ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>Max McNown</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Max McNown - Done For (Performance Video) - Max McNown</v>
+        <v>Towa Bird - Dog [Live From Sid The Cat] - Towa Bird</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Julia Cole - Big Picture (Official Lyric Video)</v>
+        <v>Olivia Rodrigo - the cure (Jimmy Kimmel Live! 2026)</v>
       </c>
       <c r="B7" t="str">
-        <v>1d ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=M7LF0hhoPoc</v>
+        <v>https://www.youtube.com/watch?v=_wHO8QJRTSQ</v>
       </c>
       <c r="D7" t="str">
         <v>2026-06-11</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>1d ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>Julia Cole Music</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Julia Cole - Big Picture (Official Lyric Video) - Julia Cole Music</v>
+        <v>Olivia Rodrigo - the cure (Jimmy Kimmel Live! 2026) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Joalin - On A Day Like This</v>
+        <v>Gretta Ray - Swimming, Crying (Scene X)</v>
       </c>
       <c r="B8" t="str">
-        <v>1d ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=VWLPWi9edlQ</v>
+        <v>https://www.youtube.com/watch?v=3v4sQ08PqRg</v>
       </c>
       <c r="D8" t="str">
         <v>2026-06-11</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>1d ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>Joalin</v>
+        <v>Gretta Ray</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Joalin - On A Day Like This - Joalin</v>
+        <v>Gretta Ray - Swimming, Crying (Scene X) - Gretta Ray</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>RAYE - Click Clack Symphony (Live at Capital's Summertime Ball 2026)</v>
+        <v>Sting, Shaggy - All This Time/The Last Ship (Live On GMA)</v>
       </c>
       <c r="B9" t="str">
-        <v>1d ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=_TUh78OrzSM</v>
+        <v>https://www.youtube.com/watch?v=_Vo7tSfTmi4</v>
       </c>
       <c r="D9" t="str">
         <v>2026-06-11</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>1d ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>Capital FM</v>
+        <v>Sting</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>RAYE - Click Clack Symphony (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Sting, Shaggy - All This Time/The Last Ship (Live On GMA) - Sting</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Vera Blue - Rituals (Official Video)</v>
+        <v>The Kid LAROI - GIRLS (Live)</v>
       </c>
       <c r="B10" t="str">
-        <v>2d ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=zJ2HNWcNauU</v>
+        <v>https://www.youtube.com/watch?v=0gMLEFf_VH8</v>
       </c>
       <c r="D10" t="str">
         <v>2026-06-11</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>2d ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>Vera Blue</v>
+        <v>The Kid LAROI.</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Vera Blue - Rituals (Official Video) - Vera Blue</v>
+        <v>The Kid LAROI - GIRLS (Live) - The Kid LAROI.</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Wishy - Lovesick (Official Video)</v>
+        <v>Shaboozey - Cowgirl (Official Lyric Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>2d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=q_WXgLn8sVw</v>
+        <v>https://www.youtube.com/watch?v=i8ORixSVKSw</v>
       </c>
       <c r="D11" t="str">
         <v>2026-06-11</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>2d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>Wishy</v>
+        <v>Shaboozey</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Wishy - Lovesick (Official Video) - Wishy</v>
+        <v>Shaboozey - Cowgirl (Official Lyric Video) - Shaboozey</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Jason Derulo - In My Head (Live at Capital's Summertime Ball 2026) | Capital</v>
+        <v>David Guetta, Alok, Stick Figure – Run Run River (Angels Above Me) (Official Lyric Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>2d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=LudSER6wECQ</v>
+        <v>https://www.youtube.com/watch?v=pXdGKRENTKM</v>
       </c>
       <c r="D12" t="str">
         <v>2026-06-11</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>2d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>Capital FM</v>
+        <v>Alok and 2 more</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Jason Derulo - In My Head (Live at Capital's Summertime Ball 2026) | Capital - Capital FM</v>
+        <v>David Guetta, Alok, Stick Figure – Run Run River (Angels Above Me) (Official Lyric Video) - Alok and 2 more</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>RAYE - Beware.. The South London Lover Boy. (Live at Capital's Summertime Ball 2026)</v>
+        <v>Switchfoot - Fake Plastic Trees Live (Radiohead Cover)</v>
       </c>
       <c r="B13" t="str">
-        <v>2d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=TxlMo7pbCOs</v>
+        <v>https://www.youtube.com/watch?v=kJOeENtJzDI</v>
       </c>
       <c r="D13" t="str">
         <v>2026-06-11</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>2d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>Capital FM</v>
+        <v>Switchfoot</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>RAYE - Beware.. The South London Lover Boy. (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Switchfoot - Fake Plastic Trees Live (Radiohead Cover) - Switchfoot</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Niall Horan - This Town (Live at Capital's Summertime Ball 2026)</v>
+        <v>The Rose (더로즈) - Utopia | Official Audio</v>
       </c>
       <c r="B14" t="str">
-        <v>2d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=6TO_ITkIgBI</v>
+        <v>https://www.youtube.com/watch?v=ORUXIjzL_Rg</v>
       </c>
       <c r="D14" t="str">
         <v>2026-06-11</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>2d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>Capital FM</v>
+        <v>The Rose</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Niall Horan - This Town (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>The Rose (더로즈) - Utopia | Official Audio - The Rose</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Soft Cell - Danceteria (Official Video)</v>
+        <v>Niall Horan feat. Myles Smith - Drive Safe (Live at Capital's Summertime Ball 2026) | Capital</v>
       </c>
       <c r="B15" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=P4kE8CNvoOw</v>
+        <v>https://www.youtube.com/watch?v=mmu5Vh4hMu0</v>
       </c>
       <c r="D15" t="str">
         <v>2026-06-11</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>Soft Cell</v>
+        <v>Capital FM</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Soft Cell - Danceteria (Official Video) - Soft Cell</v>
+        <v>Niall Horan feat. Myles Smith - Drive Safe (Live at Capital's Summertime Ball 2026) | Capital - Capital FM</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Take That - Greatest Day (Live at Capital's Summertime Ball 2026)</v>
+        <v>Gia Ford - At Least For Now</v>
       </c>
       <c r="B16" t="str">
-        <v>2d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=3dwS84ONnZ0</v>
+        <v>https://www.youtube.com/watch?v=u2U0gUeCE5M</v>
       </c>
       <c r="D16" t="str">
         <v>2026-06-11</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>2d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>Capital FM</v>
+        <v>Gia Ford</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Take That - Greatest Day (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Gia Ford - At Least For Now - Gia Ford</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Take That - You're A Superstar (Live at Capital's Summertime Ball 2026)</v>
+        <v>Emilia Tarrant - The Three Words / Better Together (Live at Bread &amp; Butter Lounge)</v>
       </c>
       <c r="B17" t="str">
-        <v>2d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=g_KsWUl-nxw</v>
+        <v>https://www.youtube.com/watch?v=pE5wZRhY0P0</v>
       </c>
       <c r="D17" t="str">
         <v>2026-06-11</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>2d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>Capital FM</v>
+        <v>Emilia Tarrant</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Take That - You're A Superstar (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Emilia Tarrant - The Three Words / Better Together (Live at Bread &amp; Butter Lounge) - Emilia Tarrant</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Jessie J - CALIFORNIA (Official Video)</v>
+        <v>Rodrigo y Gabriela - Monster (Official Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>2d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=tN1mV6mCJ3k</v>
+        <v>https://www.youtube.com/watch?v=Wolzo63vons</v>
       </c>
       <c r="D18" t="str">
         <v>2026-06-11</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>2d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>Jessie J</v>
+        <v>Rodrigo y Gabriela</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Jessie J - CALIFORNIA (Official Video) - Jessie J</v>
+        <v>Rodrigo y Gabriela - Monster (Official Video) - Rodrigo y Gabriela</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Olivia Rodrigo - the cure (performance video)</v>
+        <v>Max McNown - Done For (Performance Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>2d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=OA2YUsJyQI0</v>
+        <v>https://www.youtube.com/watch?v=L1SxYiMiZEM</v>
       </c>
       <c r="D19" t="str">
         <v>2026-06-11</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>2d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>Max McNown</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Olivia Rodrigo - the cure (performance video) - Olivia Rodrigo</v>
+        <v>Max McNown - Done For (Performance Video) - Max McNown</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>XG - Something Ain’t Right (Live at Capital's Summertime Ball 2026) | Capital</v>
+        <v>Julia Cole - Big Picture (Official Lyric Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>2d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=BWASDZZtO6w</v>
+        <v>https://www.youtube.com/watch?v=M7LF0hhoPoc</v>
       </c>
       <c r="D20" t="str">
         <v>2026-06-11</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>2d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>Capital FM and XG</v>
+        <v>Julia Cole Music</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>XG - Something Ain’t Right (Live at Capital's Summertime Ball 2026) | Capital - Capital FM and XG</v>
+        <v>Julia Cole - Big Picture (Official Lyric Video) - Julia Cole Music</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Freya Ridings - Wild Horse (Official Lyric Video)</v>
+        <v>Joalin - On A Day Like This</v>
       </c>
       <c r="B21" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=IpkgL5oZbbU</v>
+        <v>https://www.youtube.com/watch?v=VWLPWi9edlQ</v>
       </c>
       <c r="D21" t="str">
         <v>2026-06-11</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>Freya Ridings</v>
+        <v>Joalin</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Freya Ridings - Wild Horse (Official Lyric Video) - Freya Ridings</v>
+        <v>Joalin - On A Day Like This - Joalin</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Myles Smith - Hold Me In The Dark (Live at Capital's Summertime Ball 2026)</v>
+        <v>RAYE - Click Clack Symphony (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B22" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=uVh2WwmC7Sw</v>
+        <v>https://www.youtube.com/watch?v=_TUh78OrzSM</v>
       </c>
       <c r="D22" t="str">
         <v>2026-06-11</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Myles Smith - Hold Me In The Dark (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>RAYE - Click Clack Symphony (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Niall Horan - Heaven (Live at Capital's Summertime Ball 2026) | Capital</v>
+        <v>Vera Blue - Rituals (Official Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=CTmWK2o3mXY</v>
+        <v>https://www.youtube.com/watch?v=zJ2HNWcNauU</v>
       </c>
       <c r="D23" t="str">
         <v>2026-06-11</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>Capital FM</v>
+        <v>Vera Blue</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Niall Horan - Heaven (Live at Capital's Summertime Ball 2026) | Capital - Capital FM</v>
+        <v>Vera Blue - Rituals (Official Video) - Vera Blue</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Strange AI Art Installations</v>
+        <v>Wishy - Lovesick (Official Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>3d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=KnOVECFvkMM</v>
+        <v>https://www.youtube.com/watch?v=q_WXgLn8sVw</v>
       </c>
       <c r="D24" t="str">
         <v>2026-06-11</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>3d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>Kelly Boesch AI Art</v>
+        <v>Wishy</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Strange AI Art Installations - Kelly Boesch AI Art</v>
+        <v>Wishy - Lovesick (Official Video) - Wishy</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Robyn - Talk To Me (Live at Capital's Summertime Ball 2026)</v>
+        <v>Jason Derulo - In My Head (Live at Capital's Summertime Ball 2026) | Capital</v>
       </c>
       <c r="B25" t="str">
-        <v>3d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=KQigrpSdFPY</v>
+        <v>https://www.youtube.com/watch?v=LudSER6wECQ</v>
       </c>
       <c r="D25" t="str">
         <v>2026-06-11</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>3d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Robyn - Talk To Me (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Jason Derulo - In My Head (Live at Capital's Summertime Ball 2026) | Capital - Capital FM</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Nora Fatehi, Vegedream, Sanjoy, FIFA Sound - Siir Siir (FIFA World Cup 2026™) [Official Music Video]</v>
+        <v>RAYE - Beware.. The South London Lover Boy. (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B26" t="str">
-        <v>3d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=afiNbSxg7aw</v>
+        <v>https://www.youtube.com/watch?v=TxlMo7pbCOs</v>
       </c>
       <c r="D26" t="str">
         <v>2026-06-11</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>3d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>FIFA and 3 more</v>
+        <v>Capital FM</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Nora Fatehi, Vegedream, Sanjoy, FIFA Sound - Siir Siir (FIFA World Cup 2026™) [Official Music Video] - FIFA and 3 more</v>
+        <v>RAYE - Beware.. The South London Lover Boy. (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Jason Derulo - Want To Want Me (Live at Capital's Summertime Ball 2026)</v>
+        <v>Niall Horan - This Town (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B27" t="str">
-        <v>3d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=QprQP1fdrDM</v>
+        <v>https://www.youtube.com/watch?v=6TO_ITkIgBI</v>
       </c>
       <c r="D27" t="str">
         <v>2026-06-11</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>3d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Jason Derulo - Want To Want Me (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Niall Horan - This Town (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Jason Derulo - The Other Side (Live at Capital's Summertime Ball 2026)</v>
+        <v>Soft Cell - Danceteria (Official Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>3d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=ym-h0EIlL3A</v>
+        <v>https://www.youtube.com/watch?v=P4kE8CNvoOw</v>
       </c>
       <c r="D28" t="str">
         <v>2026-06-11</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>3d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>Capital FM</v>
+        <v>Soft Cell</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Jason Derulo - The Other Side (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Soft Cell - Danceteria (Official Video) - Soft Cell</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Stephen Sanchez - Be More (Live at Capital's Summertime Ball 2026) | Capital</v>
+        <v>Take That - Greatest Day (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B29" t="str">
-        <v>3d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=bIwcNmu-rAg</v>
+        <v>https://www.youtube.com/watch?v=3dwS84ONnZ0</v>
       </c>
       <c r="D29" t="str">
         <v>2026-06-11</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>3d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Stephen Sanchez - Be More (Live at Capital's Summertime Ball 2026) | Capital - Capital FM</v>
+        <v>Take That - Greatest Day (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Jason Derulo - Take You Dancing (Live at Capital's Summertime Ball 2026)</v>
+        <v>Take That - You're A Superstar (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B30" t="str">
-        <v>3d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=oLzj8E8fHRQ</v>
+        <v>https://www.youtube.com/watch?v=g_KsWUl-nxw</v>
       </c>
       <c r="D30" t="str">
         <v>2026-06-11</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>3d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Jason Derulo - Take You Dancing (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Take That - You're A Superstar (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Sekou - Someone Like You (Adele Cover) (Live at Capital's Summertime Ball 2026)</v>
+        <v>Jessie J - CALIFORNIA (Official Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>3d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=YIy2g4enMiY</v>
+        <v>https://www.youtube.com/watch?v=tN1mV6mCJ3k</v>
       </c>
       <c r="D31" t="str">
         <v>2026-06-11</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>3d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>Capital FM</v>
+        <v>Jessie J</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Sekou - Someone Like You (Adele Cover) (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Jessie J - CALIFORNIA (Official Video) - Jessie J</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Sienna Spiro - He's Not My Baby, I'm His (Live at Capital's Summertime Ball 2026)</v>
+        <v>Olivia Rodrigo - the cure (performance video)</v>
       </c>
       <c r="B32" t="str">
-        <v>3d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=NhuPT6MR2XU</v>
+        <v>https://www.youtube.com/watch?v=OA2YUsJyQI0</v>
       </c>
       <c r="D32" t="str">
         <v>2026-06-11</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>3d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>Capital FM</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Sienna Spiro - He's Not My Baby, I'm His (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Olivia Rodrigo - the cure (performance video) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>DEEP PURPLE - DIABLO (Official Video)</v>
+        <v>XG - Something Ain’t Right (Live at Capital's Summertime Ball 2026) | Capital</v>
       </c>
       <c r="B33" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=Z4RpBEg5uis</v>
+        <v>https://www.youtube.com/watch?v=BWASDZZtO6w</v>
       </c>
       <c r="D33" t="str">
         <v>2026-06-11</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>earMUSIC and Deep Purple Official</v>
+        <v>Capital FM and XG</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>DEEP PURPLE - DIABLO (Official Video) - earMUSIC and Deep Purple Official</v>
+        <v>XG - Something Ain’t Right (Live at Capital's Summertime Ball 2026) | Capital - Capital FM and XG</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Reba McEntire - You Never Gave Up On Me</v>
+        <v>Freya Ridings - Wild Horse (Official Lyric Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=AUCRUStLmJM</v>
+        <v>https://www.youtube.com/watch?v=IpkgL5oZbbU</v>
       </c>
       <c r="D34" t="str">
         <v>2026-06-11</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Reba McEntire</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Reba McEntire - You Never Gave Up On Me - Reba McEntire</v>
+        <v>Freya Ridings - Wild Horse (Official Lyric Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>elijah woods - Wonder (Official Lyric Video)</v>
+        <v>Myles Smith - Hold Me In The Dark (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B35" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=sDDbD4R-xD4</v>
+        <v>https://www.youtube.com/watch?v=uVh2WwmC7Sw</v>
       </c>
       <c r="D35" t="str">
         <v>2026-06-11</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>elijah woods</v>
+        <v>Capital FM</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>elijah woods - Wonder (Official Lyric Video) - elijah woods</v>
+        <v>Myles Smith - Hold Me In The Dark (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>XG - Flowers (Sweet Female Attitude Cover) (Live at Capital's Summertime Ball 2026)</v>
+        <v>Niall Horan - Heaven (Live at Capital's Summertime Ball 2026) | Capital</v>
       </c>
       <c r="B36" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=MxJQoyKh8TQ</v>
+        <v>https://www.youtube.com/watch?v=CTmWK2o3mXY</v>
       </c>
       <c r="D36" t="str">
         <v>2026-06-11</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>Capital FM and XG</v>
+        <v>Capital FM</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>XG - Flowers (Sweet Female Attitude Cover) (Live at Capital's Summertime Ball 2026) - Capital FM and XG</v>
+        <v>Niall Horan - Heaven (Live at Capital's Summertime Ball 2026) | Capital - Capital FM</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Niall Horan - Nice To Meet Ya (Live at Capital's Summertime Ball 2026)</v>
+        <v>Strange AI Art Installations</v>
       </c>
       <c r="B37" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=-UIkkGxMQG8</v>
+        <v>https://www.youtube.com/watch?v=KnOVECFvkMM</v>
       </c>
       <c r="D37" t="str">
         <v>2026-06-11</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>Capital FM</v>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Niall Horan - Nice To Meet Ya (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Strange AI Art Installations - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Niall Horan - Steal My Girl (One Direction cover) (Live at Capital's Summertime Ball 2026)</v>
+        <v>Robyn - Talk To Me (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B38" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=b_uO5ROpk_0</v>
+        <v>https://www.youtube.com/watch?v=KQigrpSdFPY</v>
       </c>
       <c r="D38" t="str">
         <v>2026-06-11</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Niall Horan - Steal My Girl (One Direction cover) (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Robyn - Talk To Me (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Niall Horan - Dinner Party (Live at Capital's Summertime Ball 2026)</v>
+        <v>Nora Fatehi, Vegedream, Sanjoy, FIFA Sound - Siir Siir (FIFA World Cup 2026™) [Official Music Video]</v>
       </c>
       <c r="B39" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=hSJfAFpdllk</v>
+        <v>https://www.youtube.com/watch?v=afiNbSxg7aw</v>
       </c>
       <c r="D39" t="str">
         <v>2026-06-11</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>Capital FM</v>
+        <v>FIFA and 3 more</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Niall Horan - Dinner Party (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Nora Fatehi, Vegedream, Sanjoy, FIFA Sound - Siir Siir (FIFA World Cup 2026™) [Official Music Video] - FIFA and 3 more</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Niall Horan - Slow Hands (Live at Capital's Summertime Ball 2026) | Capital</v>
+        <v>Jason Derulo - Want To Want Me (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B40" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=vdMK2DvnWJI</v>
+        <v>https://www.youtube.com/watch?v=QprQP1fdrDM</v>
       </c>
       <c r="D40" t="str">
         <v>2026-06-11</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Niall Horan - Slow Hands (Live at Capital's Summertime Ball 2026) | Capital - Capital FM</v>
+        <v>Jason Derulo - Want To Want Me (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>RAYE - Joy (Live at Capital's Summertime Ball 2026)</v>
+        <v>Jason Derulo - The Other Side (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B41" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=5gvhRAGaOUo</v>
+        <v>https://www.youtube.com/watch?v=ym-h0EIlL3A</v>
       </c>
       <c r="D41" t="str">
         <v>2026-06-11</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>RAYE - Joy (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Jason Derulo - The Other Side (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Myles Smith - Stargazing (Live at Capital's Summertime Ball 2026)</v>
+        <v>Stephen Sanchez - Be More (Live at Capital's Summertime Ball 2026) | Capital</v>
       </c>
       <c r="B42" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=2AIMnAPxqfw</v>
+        <v>https://www.youtube.com/watch?v=bIwcNmu-rAg</v>
       </c>
       <c r="D42" t="str">
         <v>2026-06-11</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Myles Smith - Stargazing (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Stephen Sanchez - Be More (Live at Capital's Summertime Ball 2026) | Capital - Capital FM</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Lola Young - From Down Here (Live at Capital's Summertime Ball 2026)</v>
+        <v>Jason Derulo - Take You Dancing (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B43" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=UD7HkkAbnVA</v>
+        <v>https://www.youtube.com/watch?v=oLzj8E8fHRQ</v>
       </c>
       <c r="D43" t="str">
         <v>2026-06-11</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>Capital FM and Lola Young</v>
+        <v>Capital FM</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Lola Young - From Down Here (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
+        <v>Jason Derulo - Take You Dancing (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>XG - Hypnotize (Live at Capital's Summertime Ball 2026)</v>
+        <v>Sekou - Someone Like You (Adele Cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B44" t="str">
-        <v>4d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=c5u3ur4vLo0</v>
+        <v>https://www.youtube.com/watch?v=YIy2g4enMiY</v>
       </c>
       <c r="D44" t="str">
         <v>2026-06-11</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>4d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>Capital FM and XG</v>
+        <v>Capital FM</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>XG - Hypnotize (Live at Capital's Summertime Ball 2026) - Capital FM and XG</v>
+        <v>Sekou - Someone Like You (Adele Cover) (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Sienna Spiro - Die On This Hill (Live at Capital's Summertime Ball 2026)</v>
+        <v>Sienna Spiro - He's Not My Baby, I'm His (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B45" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=UhWumamExiI</v>
+        <v>https://www.youtube.com/watch?v=NhuPT6MR2XU</v>
       </c>
       <c r="D45" t="str">
         <v>2026-06-11</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Sienna Spiro - Die On This Hill (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Sienna Spiro - He's Not My Baby, I'm His (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>RAYE - Where Is My Husband? (Live at Capital's Summertime Ball 2026)</v>
+        <v>DEEP PURPLE - DIABLO (Official Video)</v>
       </c>
       <c r="B46" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=Z_HR2ZYY1VA</v>
+        <v>https://www.youtube.com/watch?v=Z4RpBEg5uis</v>
       </c>
       <c r="D46" t="str">
         <v>2026-06-11</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>Capital FM</v>
+        <v>earMUSIC and Deep Purple Official</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>RAYE - Where Is My Husband? (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>DEEP PURPLE - DIABLO (Official Video) - earMUSIC and Deep Purple Official</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Take That - Never Forget (Live at Capital's Summertime Ball 2026)</v>
+        <v>Reba McEntire - You Never Gave Up On Me</v>
       </c>
       <c r="B47" t="str">
-        <v>4d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=9S61JkOZLe8</v>
+        <v>https://www.youtube.com/watch?v=AUCRUStLmJM</v>
       </c>
       <c r="D47" t="str">
         <v>2026-06-11</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>4d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>Capital FM and Take That</v>
+        <v>Reba McEntire</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Take That - Never Forget (Live at Capital's Summertime Ball 2026) - Capital FM and Take That</v>
+        <v>Reba McEntire - You Never Gave Up On Me - Reba McEntire</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Robyn - Dancing On My Own (Live at Capital's Summertime Ball 2026)</v>
+        <v>elijah woods - Wonder (Official Lyric Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=_4SfgNPngbo</v>
+        <v>https://www.youtube.com/watch?v=sDDbD4R-xD4</v>
       </c>
       <c r="D48" t="str">
         <v>2026-06-11</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>Capital FM</v>
+        <v>elijah woods</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Robyn - Dancing On My Own (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>elijah woods - Wonder (Official Lyric Video) - elijah woods</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Take That - Patience (Live at Capital's Summertime Ball 2026)</v>
+        <v>XG - Flowers (Sweet Female Attitude Cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B49" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=_I9qIxmrDuI</v>
+        <v>https://www.youtube.com/watch?v=MxJQoyKh8TQ</v>
       </c>
       <c r="D49" t="str">
         <v>2026-06-11</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>Capital FM and Take That</v>
+        <v>Capital FM and XG</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Take That - Patience (Live at Capital's Summertime Ball 2026) - Capital FM and Take That</v>
+        <v>XG - Flowers (Sweet Female Attitude Cover) (Live at Capital's Summertime Ball 2026) - Capital FM and XG</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Mis-Teeq - Full Set (Live at Capital's Summertime Ball 2026)</v>
+        <v>Niall Horan - Nice To Meet Ya (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B50" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=5AyQM_coDb8</v>
+        <v>https://www.youtube.com/watch?v=-UIkkGxMQG8</v>
       </c>
       <c r="D50" t="str">
         <v>2026-06-11</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Mis-Teeq - Full Set (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Niall Horan - Nice To Meet Ya (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Take That - Rule The World (Live at Capital's Summertime Ball 2026)</v>
+        <v>Niall Horan - Steal My Girl (One Direction cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B51" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=0nc-qdhh6eU</v>
+        <v>https://www.youtube.com/watch?v=b_uO5ROpk_0</v>
       </c>
       <c r="D51" t="str">
         <v>2026-06-11</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>Capital FM and Take That</v>
+        <v>Capital FM</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Take That - Rule The World (Live at Capital's Summertime Ball 2026) - Capital FM and Take That</v>
+        <v>Niall Horan - Steal My Girl (One Direction cover) (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Sienna Spiro - Material Lover (Live at Capital's Summertime Ball 2026)</v>
+        <v>Niall Horan - Dinner Party (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B52" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=dZjAtTc9DBQ</v>
+        <v>https://www.youtube.com/watch?v=hSJfAFpdllk</v>
       </c>
       <c r="D52" t="str">
         <v>2026-06-11</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Sienna Spiro - Material Lover (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Niall Horan - Dinner Party (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Take That - Shine (Live at Capital's Summertime Ball 2026)</v>
+        <v>Niall Horan - Slow Hands (Live at Capital's Summertime Ball 2026) | Capital</v>
       </c>
       <c r="B53" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=T6TmxqOGIf0</v>
+        <v>https://www.youtube.com/watch?v=vdMK2DvnWJI</v>
       </c>
       <c r="D53" t="str">
         <v>2026-06-11</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Take That - Shine (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Niall Horan - Slow Hands (Live at Capital's Summertime Ball 2026) | Capital - Capital FM</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>MEEK - Dracula (Tame Impala Cover) (Live at Capital's Summertime Ball 2026)</v>
+        <v>RAYE - Joy (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B54" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=4jnM--XhsC0</v>
+        <v>https://www.youtube.com/watch?v=5gvhRAGaOUo</v>
       </c>
       <c r="D54" t="str">
         <v>2026-06-11</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>MEEK - Dracula (Tame Impala Cover) (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>RAYE - Joy (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Lola Young - Messy (Live at Capital's Summertime Ball 2026)</v>
+        <v>Myles Smith - Stargazing (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B55" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=cUvsaKkjHYQ</v>
+        <v>https://www.youtube.com/watch?v=2AIMnAPxqfw</v>
       </c>
       <c r="D55" t="str">
         <v>2026-06-11</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>Capital FM and Lola Young</v>
+        <v>Capital FM</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Lola Young - Messy (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
+        <v>Myles Smith - Stargazing (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Stephen Sanchez - Until I Found You (Live at Capital's Summertime Ball 2026)</v>
+        <v>Lola Young - From Down Here (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B56" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=oKKNK0OCpQk</v>
+        <v>https://www.youtube.com/watch?v=UD7HkkAbnVA</v>
       </c>
       <c r="D56" t="str">
         <v>2026-06-11</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>Capital FM</v>
+        <v>Capital FM and Lola Young</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Stephen Sanchez - Until I Found You (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Lola Young - From Down Here (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Lola Young - One Thing (Live at Capital's Summertime Ball 2026)</v>
+        <v>XG - Hypnotize (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B57" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=nhL2l4HCiRg</v>
+        <v>https://www.youtube.com/watch?v=c5u3ur4vLo0</v>
       </c>
       <c r="D57" t="str">
         <v>2026-06-11</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>Capital FM and Lola Young</v>
+        <v>Capital FM and XG</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Lola Young - One Thing (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
+        <v>XG - Hypnotize (Live at Capital's Summertime Ball 2026) - Capital FM and XG</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Bebe Rexha - Sad Girls (Live at Capital's Summertime Ball 2026)</v>
+        <v>Sienna Spiro - Die On This Hill (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B58" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=e0PkSQNMcGs</v>
+        <v>https://www.youtube.com/watch?v=UhWumamExiI</v>
       </c>
       <c r="D58" t="str">
         <v>2026-06-11</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Bebe Rexha - Sad Girls (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Sienna Spiro - Die On This Hill (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Robyn - Dopamine (Live at Capital's Summertime Ball 2026)</v>
+        <v>RAYE - Where Is My Husband? (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B59" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=-7mPIus0U5Y</v>
+        <v>https://www.youtube.com/watch?v=Z_HR2ZYY1VA</v>
       </c>
       <c r="D59" t="str">
         <v>2026-06-11</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Robyn - Dopamine (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>RAYE - Where Is My Husband? (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Jason Derulo - Trumpets (Live at Capital's Summertime Ball 2026)</v>
+        <v>Take That - Never Forget (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B60" t="str">
-        <v>4d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=QkCKENp-4Rs</v>
+        <v>https://www.youtube.com/watch?v=9S61JkOZLe8</v>
       </c>
       <c r="D60" t="str">
         <v>2026-06-11</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>4d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>Capital FM</v>
+        <v>Capital FM and Take That</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Jason Derulo - Trumpets (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Take That - Never Forget (Live at Capital's Summertime Ball 2026) - Capital FM and Take That</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Jason Derulo - Whatcha Say (Live at Capital's Summertime Ball 2026)</v>
+        <v>Robyn - Dancing On My Own (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B61" t="str">
-        <v>4d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=jsFekVlEaSA</v>
+        <v>https://www.youtube.com/watch?v=_4SfgNPngbo</v>
       </c>
       <c r="D61" t="str">
         <v>2026-06-11</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>4d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Jason Derulo - Whatcha Say (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Robyn - Dancing On My Own (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Bebe Rexha - New Religion (Live at Capital's Summertime Ball 2026)</v>
+        <v>Take That - Patience (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B62" t="str">
-        <v>4d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=nfDKQ09bY_w</v>
+        <v>https://www.youtube.com/watch?v=_I9qIxmrDuI</v>
       </c>
       <c r="D62" t="str">
         <v>2026-06-11</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>4d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>Capital FM</v>
+        <v>Capital FM and Take That</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Bebe Rexha - New Religion (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Take That - Patience (Live at Capital's Summertime Ball 2026) - Capital FM and Take That</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Bebe Rexha - I'm Good (Live at Capital's Summertime Ball 2026)</v>
+        <v>Mis-Teeq - Full Set (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B63" t="str">
-        <v>4d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=eqceDkaK3PU</v>
+        <v>https://www.youtube.com/watch?v=5AyQM_coDb8</v>
       </c>
       <c r="D63" t="str">
         <v>2026-06-11</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>4d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Bebe Rexha - I'm Good (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Mis-Teeq - Full Set (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Strange Surreal AI - In Here - Kelly Boesch | 4K</v>
+        <v>Take That - Rule The World (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B64" t="str">
-        <v>6d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=QCNwFDTkfYU</v>
+        <v>https://www.youtube.com/watch?v=0nc-qdhh6eU</v>
       </c>
       <c r="D64" t="str">
         <v>2026-06-11</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>6d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>Kelly Boesch AI Art</v>
+        <v>Capital FM and Take That</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Strange Surreal AI - In Here - Kelly Boesch | 4K - Kelly Boesch AI Art</v>
+        <v>Take That - Rule The World (Live at Capital's Summertime Ball 2026) - Capital FM and Take That</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>The Cranberries - Scenes From 'Linger' (The Only Color Reel)</v>
+        <v>Sienna Spiro - Material Lover (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B65" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=5-peG8H-lqE</v>
+        <v>https://www.youtube.com/watch?v=dZjAtTc9DBQ</v>
       </c>
       <c r="D65" t="str">
         <v>2026-06-11</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>TheCranberriesTV</v>
+        <v>Capital FM</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>The Cranberries - Scenes From 'Linger' (The Only Color Reel) - TheCranberriesTV</v>
+        <v>Sienna Spiro - Material Lover (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Jordana Bryant - Too Little Too Late (Official Lyric Video)</v>
+        <v>Take That - Shine (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B66" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=P26-NjdBmbU</v>
+        <v>https://www.youtube.com/watch?v=T6TmxqOGIf0</v>
       </c>
       <c r="D66" t="str">
         <v>2026-06-11</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>Jordana Bryant</v>
+        <v>Capital FM</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Jordana Bryant - Too Little Too Late (Official Lyric Video) - Jordana Bryant</v>
+        <v>Take That - Shine (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Grace Enger - "Running Back To You" (Official Music Video)</v>
+        <v>MEEK - Dracula (Tame Impala Cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B67" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=BON1BSWLntE</v>
+        <v>https://www.youtube.com/watch?v=4jnM--XhsC0</v>
       </c>
       <c r="D67" t="str">
         <v>2026-06-11</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>Grace Enger</v>
+        <v>Capital FM</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Grace Enger - "Running Back To You" (Official Music Video) - Grace Enger</v>
+        <v>MEEK - Dracula (Tame Impala Cover) (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>The Offspring - Gone Away | Live at BeachLife Festival 2026</v>
+        <v>Lola Young - Messy (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B68" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=UTw106Ivz8o</v>
+        <v>https://www.youtube.com/watch?v=cUvsaKkjHYQ</v>
       </c>
       <c r="D68" t="str">
         <v>2026-06-11</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>The Offspring</v>
+        <v>Capital FM and Lola Young</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>The Offspring - Gone Away | Live at BeachLife Festival 2026 - The Offspring</v>
+        <v>Lola Young - Messy (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Lola Young – From Down Here (From The Pool)</v>
+        <v>Stephen Sanchez - Until I Found You (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B69" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=YFhpMpONGUY</v>
+        <v>https://www.youtube.com/watch?v=oKKNK0OCpQk</v>
       </c>
       <c r="D69" t="str">
         <v>2026-06-11</v>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>Lola Young</v>
+        <v>Capital FM</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Lola Young – From Down Here (From The Pool) - Lola Young</v>
+        <v>Stephen Sanchez - Until I Found You (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>CAIN - Living Water (Music Video)</v>
+        <v>Lola Young - One Thing (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B70" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=WrsXAfnTAdA</v>
+        <v>https://www.youtube.com/watch?v=nhL2l4HCiRg</v>
       </c>
       <c r="D70" t="str">
         <v>2026-06-11</v>
@@ -3035,13 +3035,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>CAIN</v>
+        <v>Capital FM and Lola Young</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>CAIN - Living Water (Music Video) - CAIN</v>
+        <v>Lola Young - One Thing (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>B.B. King &amp; Eric Clapton - Riding With The King (Official Music Video)</v>
+        <v>Bebe Rexha - Sad Girls (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B71" t="str">
-        <v>6d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=L7Ls8ceHxhc</v>
+        <v>https://www.youtube.com/watch?v=e0PkSQNMcGs</v>
       </c>
       <c r="D71" t="str">
         <v>2026-06-11</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>6d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>Eric Clapton</v>
+        <v>Capital FM</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>B.B. King &amp; Eric Clapton - Riding With The King (Official Music Video) - Eric Clapton</v>
+        <v>Bebe Rexha - Sad Girls (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Blu DeTiger - Whisper (Official Music Video)</v>
+        <v>Robyn - Dopamine (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B72" t="str">
-        <v>6d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=OfcBfPnskG4</v>
+        <v>https://www.youtube.com/watch?v=-7mPIus0U5Y</v>
       </c>
       <c r="D72" t="str">
         <v>2026-06-11</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>6d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>Blu DeTiger</v>
+        <v>Capital FM</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Blu DeTiger - Whisper (Official Music Video) - Blu DeTiger</v>
+        <v>Robyn - Dopamine (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Romeo Santos, Prince Royce - Ay! San Miguel (Official Video)</v>
+        <v>Jason Derulo - Trumpets (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B73" t="str">
-        <v>6d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=-uvNvVtUidc</v>
+        <v>https://www.youtube.com/watch?v=QkCKENp-4Rs</v>
       </c>
       <c r="D73" t="str">
         <v>2026-06-11</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>6d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>Romeo Santos and Prince Royce</v>
+        <v>Capital FM</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Romeo Santos, Prince Royce - Ay! San Miguel (Official Video) - Romeo Santos and Prince Royce</v>
+        <v>Jason Derulo - Trumpets (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Pink Floyd - Pigs on the Wing (8-Track Version - Official Audio)</v>
+        <v>Jason Derulo - Whatcha Say (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B74" t="str">
-        <v>6d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=WZUKJ90i6Tw</v>
+        <v>https://www.youtube.com/watch?v=jsFekVlEaSA</v>
       </c>
       <c r="D74" t="str">
         <v>2026-06-11</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>6d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>Pink Floyd</v>
+        <v>Capital FM</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Pink Floyd - Pigs on the Wing (8-Track Version - Official Audio) - Pink Floyd</v>
+        <v>Jason Derulo - Whatcha Say (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Holly Humberstone - it’s just White Noise</v>
+        <v>Bebe Rexha - New Religion (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B75" t="str">
-        <v>6d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=KeRZtPUjl8g</v>
+        <v>https://www.youtube.com/watch?v=nfDKQ09bY_w</v>
       </c>
       <c r="D75" t="str">
         <v>2026-06-11</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>6d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>Holly Humberstone</v>
+        <v>Capital FM</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Holly Humberstone - it’s just White Noise - Holly Humberstone</v>
+        <v>Bebe Rexha - New Religion (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Freya Ridings - Mother Of Pearl (Official Video)</v>
+        <v>Bebe Rexha - I'm Good (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B76" t="str">
-        <v>6d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=So5gx12fCsA</v>
+        <v>https://www.youtube.com/watch?v=eqceDkaK3PU</v>
       </c>
       <c r="D76" t="str">
         <v>2026-06-11</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>6d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>Freya Ridings</v>
+        <v>Capital FM</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Freya Ridings - Mother Of Pearl (Official Video) - Freya Ridings</v>
+        <v>Bebe Rexha - I'm Good (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>MUSE - Nightshift Superstar (Official Music Video)</v>
+        <v>Strange Surreal AI - In Here - Kelly Boesch | 4K</v>
       </c>
       <c r="B77" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=p--xk9n1eIM</v>
+        <v>https://www.youtube.com/watch?v=QCNwFDTkfYU</v>
       </c>
       <c r="D77" t="str">
         <v>2026-06-11</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>Muse</v>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>MUSE - Nightshift Superstar (Official Music Video) - Muse</v>
+        <v>Strange Surreal AI - In Here - Kelly Boesch | 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Ellie Goulding - Black Prada Dress (Visualiser)</v>
+        <v>The Cranberries - Scenes From 'Linger' (The Only Color Reel)</v>
       </c>
       <c r="B78" t="str">
-        <v>6d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=zr9CYpgPueI</v>
+        <v>https://www.youtube.com/watch?v=5-peG8H-lqE</v>
       </c>
       <c r="D78" t="str">
         <v>2026-06-11</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>6d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>Ellie Goulding</v>
+        <v>TheCranberriesTV</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Ellie Goulding - Black Prada Dress (Visualiser) - Ellie Goulding</v>
+        <v>The Cranberries - Scenes From 'Linger' (The Only Color Reel) - TheCranberriesTV</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Evanescence - Sanctuary (Official Visualizer)</v>
+        <v>Jordana Bryant - Too Little Too Late (Official Lyric Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=E64jOWeVfpg</v>
+        <v>https://www.youtube.com/watch?v=P26-NjdBmbU</v>
       </c>
       <c r="D79" t="str">
         <v>2026-06-11</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>Evanescence</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Evanescence - Sanctuary (Official Visualizer) - Evanescence</v>
+        <v>Jordana Bryant - Too Little Too Late (Official Lyric Video) - Jordana Bryant</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>The Beaches - Perfect 10 (Official Visualizer)</v>
+        <v>Grace Enger - "Running Back To You" (Official Music Video)</v>
       </c>
       <c r="B80" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=N7TOR_l-CM8</v>
+        <v>https://www.youtube.com/watch?v=BON1BSWLntE</v>
       </c>
       <c r="D80" t="str">
         <v>2026-06-11</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>The Beaches</v>
+        <v>Grace Enger</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>The Beaches - Perfect 10 (Official Visualizer) - The Beaches</v>
+        <v>Grace Enger - "Running Back To You" (Official Music Video) - Grace Enger</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Bella White - Stuff (Official Music Video)</v>
+        <v>The Offspring - Gone Away | Live at BeachLife Festival 2026</v>
       </c>
       <c r="B81" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=7QZtxsGBTks</v>
+        <v>https://www.youtube.com/watch?v=UTw106Ivz8o</v>
       </c>
       <c r="D81" t="str">
         <v>2026-06-11</v>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>Bella White</v>
+        <v>The Offspring</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Bella White - Stuff (Official Music Video) - Bella White</v>
+        <v>The Offspring - Gone Away | Live at BeachLife Festival 2026 - The Offspring</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Meduza, Rani - Silence (Official Visualizer)</v>
+        <v>Lola Young – From Down Here (From The Pool)</v>
       </c>
       <c r="B82" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=cIdqz-WMod4</v>
+        <v>https://www.youtube.com/watch?v=YFhpMpONGUY</v>
       </c>
       <c r="D82" t="str">
         <v>2026-06-11</v>
@@ -3491,13 +3491,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>Meduza and 2 more</v>
+        <v>Lola Young</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Meduza, Rani - Silence (Official Visualizer) - Meduza and 2 more</v>
+        <v>Lola Young – From Down Here (From The Pool) - Lola Young</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>CAIN - Living Water (Lyric Video)</v>
+        <v>CAIN - Living Water (Music Video)</v>
       </c>
       <c r="B83" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=Hv-8CM5NIPM</v>
+        <v>https://www.youtube.com/watch?v=WrsXAfnTAdA</v>
       </c>
       <c r="D83" t="str">
         <v>2026-06-11</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>CAIN - Living Water (Lyric Video) - CAIN</v>
+        <v>CAIN - Living Water (Music Video) - CAIN</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Fitz and the Tantrums - Greenlight (Official Visualizer)</v>
+        <v>B.B. King &amp; Eric Clapton - Riding With The King (Official Music Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=Zx-ZPBbcA58</v>
+        <v>https://www.youtube.com/watch?v=L7Ls8ceHxhc</v>
       </c>
       <c r="D84" t="str">
         <v>2026-06-11</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>Fitz and the Tantrums</v>
+        <v>Eric Clapton</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Fitz and the Tantrums - Greenlight (Official Visualizer) - Fitz and the Tantrums</v>
+        <v>B.B. King &amp; Eric Clapton - Riding With The King (Official Music Video) - Eric Clapton</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Jeremy Camp - Reflector (Official Music Video)</v>
+        <v>Blu DeTiger - Whisper (Official Music Video)</v>
       </c>
       <c r="B85" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=SR-4q1yiYNA</v>
+        <v>https://www.youtube.com/watch?v=OfcBfPnskG4</v>
       </c>
       <c r="D85" t="str">
         <v>2026-06-11</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>Jeremy Camp</v>
+        <v>Blu DeTiger</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Jeremy Camp - Reflector (Official Music Video) - Jeremy Camp</v>
+        <v>Blu DeTiger - Whisper (Official Music Video) - Blu DeTiger</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Alesso, OneRepublic - In Your Eyes (Visualizer)</v>
+        <v>Romeo Santos, Prince Royce - Ay! San Miguel (Official Video)</v>
       </c>
       <c r="B86" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=bS9C1ipyMy8</v>
+        <v>https://www.youtube.com/watch?v=-uvNvVtUidc</v>
       </c>
       <c r="D86" t="str">
         <v>2026-06-11</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>Alesso</v>
+        <v>Romeo Santos and Prince Royce</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Alesso, OneRepublic - In Your Eyes (Visualizer) - Alesso</v>
+        <v>Romeo Santos, Prince Royce - Ay! San Miguel (Official Video) - Romeo Santos and Prince Royce</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Malcolm Todd - Free.99 (Official Visualizer)</v>
+        <v>Pink Floyd - Pigs on the Wing (8-Track Version - Official Audio)</v>
       </c>
       <c r="B87" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=wBBQptUsOhw</v>
+        <v>https://www.youtube.com/watch?v=WZUKJ90i6Tw</v>
       </c>
       <c r="D87" t="str">
         <v>2026-06-11</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>Malcolm Todd</v>
+        <v>Pink Floyd</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Malcolm Todd - Free.99 (Official Visualizer) - Malcolm Todd</v>
+        <v>Pink Floyd - Pigs on the Wing (8-Track Version - Official Audio) - Pink Floyd</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Isabel LaRosa - Every Life (Visualizer)</v>
+        <v>Holly Humberstone - it’s just White Noise</v>
       </c>
       <c r="B88" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=tIQDAtwNAY4</v>
+        <v>https://www.youtube.com/watch?v=KeRZtPUjl8g</v>
       </c>
       <c r="D88" t="str">
         <v>2026-06-11</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>Isabel LaRosa</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Isabel LaRosa - Every Life (Visualizer) - Isabel LaRosa</v>
+        <v>Holly Humberstone - it’s just White Noise - Holly Humberstone</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Wyatt Flores - Half The Man (Official Music Video)</v>
+        <v>Freya Ridings - Mother Of Pearl (Official Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=2ChzcWHryFM</v>
+        <v>https://www.youtube.com/watch?v=So5gx12fCsA</v>
       </c>
       <c r="D89" t="str">
         <v>2026-06-11</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>Wyatt Flores</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Wyatt Flores - Half The Man (Official Music Video) - Wyatt Flores</v>
+        <v>Freya Ridings - Mother Of Pearl (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Mckenna Grace - Ugly and Rotten (Official Music Video)</v>
+        <v>MUSE - Nightshift Superstar (Official Music Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=4yXFVgy7laM</v>
+        <v>https://www.youtube.com/watch?v=p--xk9n1eIM</v>
       </c>
       <c r="D90" t="str">
         <v>2026-06-11</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>Mckenna Grace</v>
+        <v>Muse</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Mckenna Grace - Ugly and Rotten (Official Music Video) - Mckenna Grace</v>
+        <v>MUSE - Nightshift Superstar (Official Music Video) - Muse</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Robert Grace - If You Were Gone ft. Bob Grace (OFFICIAL LYRIC VIDEO)</v>
+        <v>Ellie Goulding - Black Prada Dress (Visualiser)</v>
       </c>
       <c r="B91" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=fbpQjMi3Hco</v>
+        <v>https://www.youtube.com/watch?v=zr9CYpgPueI</v>
       </c>
       <c r="D91" t="str">
         <v>2026-06-11</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>Robert Grace</v>
+        <v>Ellie Goulding</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Robert Grace - If You Were Gone ft. Bob Grace (OFFICIAL LYRIC VIDEO) - Robert Grace</v>
+        <v>Ellie Goulding - Black Prada Dress (Visualiser) - Ellie Goulding</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Boyzone - No Matter What (Live)</v>
+        <v>Evanescence - Sanctuary (Official Visualizer)</v>
       </c>
       <c r="B92" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=CEy96_jHw-Q</v>
+        <v>https://www.youtube.com/watch?v=E64jOWeVfpg</v>
       </c>
       <c r="D92" t="str">
         <v>2026-06-11</v>
@@ -3871,13 +3871,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>Boyzone</v>
+        <v>Evanescence</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Boyzone - No Matter What (Live) - Boyzone</v>
+        <v>Evanescence - Sanctuary (Official Visualizer) - Evanescence</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Florrie - The Times (Official Video)</v>
+        <v>The Beaches - Perfect 10 (Official Visualizer)</v>
       </c>
       <c r="B93" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=6yBlNUaW7r4</v>
+        <v>https://www.youtube.com/watch?v=N7TOR_l-CM8</v>
       </c>
       <c r="D93" t="str">
         <v>2026-06-11</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>florriemusic</v>
+        <v>The Beaches</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Florrie - The Times (Official Video) - florriemusic</v>
+        <v>The Beaches - Perfect 10 (Official Visualizer) - The Beaches</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Madonna - Love Sensation (Official Visualizer)</v>
+        <v>Bella White - Stuff (Official Music Video)</v>
       </c>
       <c r="B94" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=88fD-UtG_yo</v>
+        <v>https://www.youtube.com/watch?v=7QZtxsGBTks</v>
       </c>
       <c r="D94" t="str">
         <v>2026-06-11</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>Madonna</v>
+        <v>Bella White</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Madonna - Love Sensation (Official Visualizer) - Madonna</v>
+        <v>Bella White - Stuff (Official Music Video) - Bella White</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>DMA'S - Hurracane (Official Video)</v>
+        <v>Meduza, Rani - Silence (Official Visualizer)</v>
       </c>
       <c r="B95" t="str">
-        <v>7d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=-zTB57LiXPk</v>
+        <v>https://www.youtube.com/watch?v=cIdqz-WMod4</v>
       </c>
       <c r="D95" t="str">
         <v>2026-06-11</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>7d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>DMA'S</v>
+        <v>Meduza and 2 more</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>DMA'S - Hurracane (Official Video) - DMA'S</v>
+        <v>Meduza, Rani - Silence (Official Visualizer) - Meduza and 2 more</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Lainey Wilson and John Mayer - Phone, Keys, Wallet (Official Audio)</v>
+        <v>CAIN - Living Water (Lyric Video)</v>
       </c>
       <c r="B96" t="str">
-        <v>7d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=JzW6RnzeF9A</v>
+        <v>https://www.youtube.com/watch?v=Hv-8CM5NIPM</v>
       </c>
       <c r="D96" t="str">
         <v>2026-06-11</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>7d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>Lainey Wilson and John Mayer</v>
+        <v>CAIN</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Lainey Wilson and John Mayer - Phone, Keys, Wallet (Official Audio) - Lainey Wilson and John Mayer</v>
+        <v>CAIN - Living Water (Lyric Video) - CAIN</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>ROLE MODEL - High Hopes 3000 (Official Music Video)</v>
+        <v>Fitz and the Tantrums - Greenlight (Official Visualizer)</v>
       </c>
       <c r="B97" t="str">
-        <v>7d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=D_KTG0BzRiI</v>
+        <v>https://www.youtube.com/watch?v=Zx-ZPBbcA58</v>
       </c>
       <c r="D97" t="str">
         <v>2026-06-11</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>7d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>ROLE MODEL</v>
+        <v>Fitz and the Tantrums</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>ROLE MODEL - High Hopes 3000 (Official Music Video) - ROLE MODEL</v>
+        <v>Fitz and the Tantrums - Greenlight (Official Visualizer) - Fitz and the Tantrums</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Shawn Mendes - Treat You Better (Live from New York)</v>
+        <v>Jeremy Camp - Reflector (Official Music Video)</v>
       </c>
       <c r="B98" t="str">
-        <v>8d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=29bfaHc1XiY</v>
+        <v>https://www.youtube.com/watch?v=SR-4q1yiYNA</v>
       </c>
       <c r="D98" t="str">
         <v>2026-06-11</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>8d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>Shawn Mendes</v>
+        <v>Jeremy Camp</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Shawn Mendes - Treat You Better (Live from New York) - Shawn Mendes</v>
+        <v>Jeremy Camp - Reflector (Official Music Video) - Jeremy Camp</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>SIENNA SPIRO - The Visitor (Official Music Video)</v>
+        <v>Alesso, OneRepublic - In Your Eyes (Visualizer)</v>
       </c>
       <c r="B99" t="str">
-        <v>8d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=LiYb4WGbp5Y</v>
+        <v>https://www.youtube.com/watch?v=bS9C1ipyMy8</v>
       </c>
       <c r="D99" t="str">
         <v>2026-06-11</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>8d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Alesso</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>SIENNA SPIRO - The Visitor (Official Music Video) - SIENNA SPIRO</v>
+        <v>Alesso, OneRepublic - In Your Eyes (Visualizer) - Alesso</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Just Slide Official Music Video | Kelly Boesch | 4K</v>
+        <v>Malcolm Todd - Free.99 (Official Visualizer)</v>
       </c>
       <c r="B100" t="str">
-        <v>8d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=lC14fuU8aPc</v>
+        <v>https://www.youtube.com/watch?v=wBBQptUsOhw</v>
       </c>
       <c r="D100" t="str">
         <v>2026-06-11</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>8d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>Kelly Boesch AI Art</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Just Slide Official Music Video | Kelly Boesch | 4K - Kelly Boesch AI Art</v>
+        <v>Malcolm Todd - Free.99 (Official Visualizer) - Malcolm Todd</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Europe - The Cult of Ignorance (Official Video)</v>
+        <v>Isabel LaRosa - Every Life (Visualizer)</v>
       </c>
       <c r="B101" t="str">
-        <v>8d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=p-IOsjOJpnA</v>
+        <v>https://www.youtube.com/watch?v=tIQDAtwNAY4</v>
       </c>
       <c r="D101" t="str">
         <v>2026-06-11</v>
@@ -4213,13 +4213,13 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>8d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G101" t="str">
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Europe</v>
+        <v>Isabel LaRosa</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,7 +4231,7 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Europe - The Cult of Ignorance (Official Video) - Europe</v>
+        <v>Isabel LaRosa - Every Life (Visualizer) - Isabel LaRosa</v>
       </c>
     </row>
   </sheetData>
